--- a/dokumentumok/Ütemterv.xlsx
+++ b/dokumentumok/Ütemterv.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BFD0DE-118A-4D7B-9298-CBF13025BD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FC4893-D2E6-411A-B8CC-47A2BD697856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projekttervező" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -44,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Válassza ki a kiemelendő időszakot a jobb oldalon.  A diagram jelmagyarázata következik.</t>
   </si>
@@ -224,6 +221,15 @@
   </si>
   <si>
     <t>Funkciók teljes működése</t>
+  </si>
+  <si>
+    <t>Backend tesztesetek</t>
+  </si>
+  <si>
+    <t>Frontend tesztesetek</t>
+  </si>
+  <si>
+    <t>PPT megkezdése &amp; bemutatása</t>
   </si>
 </sst>
 </file>
@@ -537,7 +543,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -604,9 +610,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -619,9 +622,6 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="3" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="7" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -633,9 +633,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
@@ -679,6 +676,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="% kész" xfId="16" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -704,30 +719,54 @@
   <dxfs count="106">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -752,28 +791,71 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -793,7 +875,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
-          <bgColor theme="9"/>
+          <bgColor theme="7"/>
         </patternFill>
       </fill>
       <border>
@@ -806,41 +888,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -867,7 +921,87 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -893,67 +1027,13 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -980,7 +1060,33 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor auto="1"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -1006,67 +1112,13 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1091,6 +1143,86 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
@@ -1100,86 +1232,6 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1204,6 +1256,114 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
@@ -1213,86 +1373,6 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1317,45 +1397,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor theme="9"/>
@@ -1469,6 +1510,32 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor theme="9"/>
@@ -1482,43 +1549,28 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1543,6 +1595,114 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
@@ -1552,86 +1712,6 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1656,6 +1736,86 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
@@ -1665,86 +1825,6 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1769,6 +1849,58 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
@@ -1778,86 +1910,6 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1882,6 +1934,60 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
@@ -1897,7 +2003,7 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
       <border>
@@ -1910,67 +2016,13 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1995,61 +2047,117 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
         </patternFill>
       </fill>
       <border>
@@ -2072,44 +2180,7 @@
           <color theme="9" tint="-0.24994659260841701"/>
         </right>
         <bottom style="thin">
-          <color theme="7"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="7"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
+          <color theme="9" tint="0.59996337778862885"/>
         </bottom>
         <vertical/>
         <horizontal/>
@@ -2129,75 +2200,19 @@
           <color theme="9" tint="-0.24994659260841701"/>
         </right>
         <bottom style="thin">
-          <color theme="9" tint="0.59996337778862885"/>
+          <color theme="7"/>
         </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+      <border>
+        <top style="thin">
+          <color theme="7"/>
+        </top>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
   </dxfs>
@@ -2445,7 +2460,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:HU31"/>
-  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="30.1" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
@@ -2456,15 +2471,103 @@
     <col min="7" max="7" width="17" style="3" customWidth="1"/>
     <col min="8" max="8" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="23" customWidth="1"/>
-    <col min="11" max="16" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="27" width="4.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="46" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="47" max="68" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="69" max="236" width="5.75" customWidth="1"/>
+    <col min="10" max="10" width="7.375" style="22" customWidth="1"/>
+    <col min="11" max="11" width="6.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="7" style="1" customWidth="1"/>
+    <col min="18" max="19" width="6.875" style="1" customWidth="1"/>
+    <col min="20" max="21" width="6.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="6.375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="6.125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="7.375" style="1" customWidth="1"/>
+    <col min="28" max="28" width="7.25" customWidth="1"/>
+    <col min="29" max="29" width="7.375" customWidth="1"/>
+    <col min="30" max="30" width="6.5" customWidth="1"/>
+    <col min="31" max="31" width="6.375" customWidth="1"/>
+    <col min="32" max="32" width="6.5" customWidth="1"/>
+    <col min="33" max="34" width="6.75" customWidth="1"/>
+    <col min="35" max="35" width="6.5" customWidth="1"/>
+    <col min="36" max="37" width="6.625" customWidth="1"/>
+    <col min="38" max="38" width="5.75" customWidth="1"/>
+    <col min="39" max="41" width="6.625" customWidth="1"/>
+    <col min="42" max="43" width="6.25" customWidth="1"/>
+    <col min="44" max="44" width="5.875" customWidth="1"/>
+    <col min="45" max="45" width="6.125" customWidth="1"/>
+    <col min="46" max="46" width="7" customWidth="1"/>
+    <col min="47" max="47" width="7.875" customWidth="1"/>
+    <col min="48" max="48" width="7.75" customWidth="1"/>
+    <col min="49" max="49" width="7.375" customWidth="1"/>
+    <col min="50" max="50" width="7.125" customWidth="1"/>
+    <col min="51" max="52" width="7.375" customWidth="1"/>
+    <col min="53" max="53" width="6.75" customWidth="1"/>
+    <col min="54" max="54" width="7" customWidth="1"/>
+    <col min="55" max="55" width="6.5" customWidth="1"/>
+    <col min="56" max="57" width="7.5" customWidth="1"/>
+    <col min="58" max="58" width="6.625" customWidth="1"/>
+    <col min="59" max="59" width="6.875" customWidth="1"/>
+    <col min="60" max="60" width="6.75" customWidth="1"/>
+    <col min="61" max="61" width="6.375" customWidth="1"/>
+    <col min="62" max="62" width="6.125" customWidth="1"/>
+    <col min="63" max="63" width="6.75" customWidth="1"/>
+    <col min="64" max="64" width="6.875" customWidth="1"/>
+    <col min="65" max="65" width="7.25" customWidth="1"/>
+    <col min="66" max="67" width="6.5" customWidth="1"/>
+    <col min="68" max="68" width="6.625" customWidth="1"/>
+    <col min="69" max="77" width="5.75" customWidth="1"/>
+    <col min="78" max="78" width="7.375" customWidth="1"/>
+    <col min="79" max="79" width="7" customWidth="1"/>
+    <col min="80" max="80" width="7.625" customWidth="1"/>
+    <col min="81" max="81" width="7.25" customWidth="1"/>
+    <col min="82" max="82" width="6.75" customWidth="1"/>
+    <col min="83" max="83" width="6.375" customWidth="1"/>
+    <col min="84" max="84" width="6.75" customWidth="1"/>
+    <col min="85" max="85" width="7" customWidth="1"/>
+    <col min="86" max="86" width="7.125" customWidth="1"/>
+    <col min="87" max="87" width="6.625" customWidth="1"/>
+    <col min="88" max="88" width="7.5" customWidth="1"/>
+    <col min="89" max="89" width="6.625" customWidth="1"/>
+    <col min="90" max="90" width="6.75" customWidth="1"/>
+    <col min="91" max="91" width="7.625" customWidth="1"/>
+    <col min="92" max="92" width="7.375" customWidth="1"/>
+    <col min="93" max="93" width="7.5" customWidth="1"/>
+    <col min="94" max="94" width="7.25" customWidth="1"/>
+    <col min="95" max="95" width="7" customWidth="1"/>
+    <col min="96" max="96" width="6.875" customWidth="1"/>
+    <col min="97" max="97" width="7" customWidth="1"/>
+    <col min="98" max="98" width="7.125" customWidth="1"/>
+    <col min="99" max="107" width="5.75" customWidth="1"/>
+    <col min="108" max="108" width="7.125" customWidth="1"/>
+    <col min="109" max="109" width="7.25" customWidth="1"/>
+    <col min="110" max="110" width="6.75" customWidth="1"/>
+    <col min="111" max="112" width="7.25" customWidth="1"/>
+    <col min="113" max="113" width="7.5" customWidth="1"/>
+    <col min="114" max="114" width="7.25" customWidth="1"/>
+    <col min="115" max="115" width="7.125" customWidth="1"/>
+    <col min="116" max="116" width="6.5" customWidth="1"/>
+    <col min="117" max="117" width="7" customWidth="1"/>
+    <col min="118" max="118" width="7.125" customWidth="1"/>
+    <col min="119" max="119" width="6.25" customWidth="1"/>
+    <col min="120" max="120" width="8.25" customWidth="1"/>
+    <col min="121" max="121" width="6.625" customWidth="1"/>
+    <col min="122" max="122" width="7.625" customWidth="1"/>
+    <col min="123" max="123" width="7.125" customWidth="1"/>
+    <col min="124" max="124" width="6.75" customWidth="1"/>
+    <col min="125" max="125" width="7.875" customWidth="1"/>
+    <col min="126" max="126" width="7.125" customWidth="1"/>
+    <col min="127" max="127" width="6.875" customWidth="1"/>
+    <col min="128" max="128" width="7.5" customWidth="1"/>
+    <col min="129" max="129" width="7.375" customWidth="1"/>
+    <col min="130" max="236" width="5.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:229" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="2:229" ht="59.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B1" s="13" t="s">
         <v>29</v>
       </c>
@@ -2474,7 +2577,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="2:229" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:229" ht="21.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
@@ -2488,73 +2591,73 @@
       <c r="H2" s="14">
         <v>1</v>
       </c>
-      <c r="J2" s="24"/>
-      <c r="K2" s="40" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="42"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="39"/>
       <c r="P2" s="15"/>
-      <c r="Q2" s="40" t="s">
+      <c r="Q2" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="42"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="39"/>
       <c r="V2" s="16"/>
-      <c r="W2" s="45" t="s">
+      <c r="W2" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="X2" s="46"/>
+      <c r="X2" s="43"/>
       <c r="Y2" s="21"/>
       <c r="Z2" s="17"/>
-      <c r="AA2" s="33" t="s">
+      <c r="AA2" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="44"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="41"/>
       <c r="AH2" s="18"/>
-      <c r="AI2" s="33" t="s">
+      <c r="AI2" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
-      <c r="AL2" s="34"/>
-      <c r="AM2" s="34"/>
-      <c r="AN2" s="34"/>
-      <c r="AO2" s="34"/>
-      <c r="AP2" s="34"/>
+      <c r="AJ2" s="31"/>
+      <c r="AK2" s="31"/>
+      <c r="AL2" s="31"/>
+      <c r="AM2" s="31"/>
+      <c r="AN2" s="31"/>
+      <c r="AO2" s="31"/>
+      <c r="AP2" s="31"/>
     </row>
-    <row r="3" spans="2:229" s="11" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
+    <row r="3" spans="2:229" s="11" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="36" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="19" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="J3" s="25"/>
+      <c r="J3" s="24"/>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
@@ -2573,700 +2676,700 @@
       <c r="Z3" s="10"/>
       <c r="AA3" s="10"/>
     </row>
-    <row r="4" spans="2:229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="36"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="28">
+    <row r="4" spans="2:229" ht="15.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="33"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="26">
         <v>45901</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="25">
         <v>45902</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="25">
         <v>45903</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="25">
         <v>45904</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="25">
         <v>45905</v>
       </c>
-      <c r="M4" s="26">
+      <c r="M4" s="25">
         <v>45906</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="25">
         <v>45907</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="25">
         <v>45908</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="25">
         <v>45909</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="25">
         <v>45910</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="25">
         <v>45911</v>
       </c>
-      <c r="S4" s="26">
+      <c r="S4" s="25">
         <v>45912</v>
       </c>
-      <c r="T4" s="26">
+      <c r="T4" s="25">
         <v>45913</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="25">
         <v>45914</v>
       </c>
-      <c r="V4" s="26">
+      <c r="V4" s="25">
         <v>45915</v>
       </c>
-      <c r="W4" s="26">
+      <c r="W4" s="25">
         <v>45916</v>
       </c>
-      <c r="X4" s="26">
+      <c r="X4" s="25">
         <v>45917</v>
       </c>
-      <c r="Y4" s="26">
+      <c r="Y4" s="25">
         <v>45918</v>
       </c>
-      <c r="Z4" s="26">
+      <c r="Z4" s="25">
         <v>45919</v>
       </c>
-      <c r="AA4" s="26">
+      <c r="AA4" s="25">
         <v>45920</v>
       </c>
-      <c r="AB4" s="26">
+      <c r="AB4" s="25">
         <v>45921</v>
       </c>
-      <c r="AC4" s="26">
+      <c r="AC4" s="25">
         <v>45922</v>
       </c>
-      <c r="AD4" s="26">
+      <c r="AD4" s="25">
         <v>45923</v>
       </c>
-      <c r="AE4" s="26">
+      <c r="AE4" s="25">
         <v>45924</v>
       </c>
-      <c r="AF4" s="26">
+      <c r="AF4" s="25">
         <v>45925</v>
       </c>
-      <c r="AG4" s="26">
+      <c r="AG4" s="25">
         <v>45926</v>
       </c>
-      <c r="AH4" s="26">
+      <c r="AH4" s="25">
         <v>45927</v>
       </c>
-      <c r="AI4" s="26">
+      <c r="AI4" s="25">
         <v>45928</v>
       </c>
-      <c r="AJ4" s="26">
+      <c r="AJ4" s="25">
         <v>45929</v>
       </c>
-      <c r="AK4" s="26">
+      <c r="AK4" s="25">
         <v>45930</v>
       </c>
-      <c r="AL4" s="26">
+      <c r="AL4" s="25">
         <v>45931</v>
       </c>
-      <c r="AM4" s="26">
+      <c r="AM4" s="25">
         <v>45932</v>
       </c>
-      <c r="AN4" s="26">
+      <c r="AN4" s="25">
         <v>45933</v>
       </c>
-      <c r="AO4" s="26">
+      <c r="AO4" s="25">
         <v>45934</v>
       </c>
-      <c r="AP4" s="26">
+      <c r="AP4" s="25">
         <v>45935</v>
       </c>
-      <c r="AQ4" s="26">
+      <c r="AQ4" s="25">
         <v>45936</v>
       </c>
-      <c r="AR4" s="26">
+      <c r="AR4" s="25">
         <v>45937</v>
       </c>
-      <c r="AS4" s="26">
+      <c r="AS4" s="25">
         <v>45938</v>
       </c>
-      <c r="AT4" s="26">
+      <c r="AT4" s="25">
         <v>45939</v>
       </c>
-      <c r="AU4" s="26">
+      <c r="AU4" s="25">
         <v>45940</v>
       </c>
-      <c r="AV4" s="26">
+      <c r="AV4" s="25">
         <v>45941</v>
       </c>
-      <c r="AW4" s="26">
+      <c r="AW4" s="25">
         <v>45942</v>
       </c>
-      <c r="AX4" s="26">
+      <c r="AX4" s="25">
         <v>45943</v>
       </c>
-      <c r="AY4" s="26">
+      <c r="AY4" s="25">
         <v>45944</v>
       </c>
-      <c r="AZ4" s="26">
+      <c r="AZ4" s="25">
         <v>45945</v>
       </c>
-      <c r="BA4" s="26">
+      <c r="BA4" s="25">
         <v>45946</v>
       </c>
-      <c r="BB4" s="26">
+      <c r="BB4" s="25">
         <v>45947</v>
       </c>
-      <c r="BC4" s="26">
+      <c r="BC4" s="25">
         <v>45948</v>
       </c>
-      <c r="BD4" s="26">
+      <c r="BD4" s="25">
         <v>45949</v>
       </c>
-      <c r="BE4" s="26">
+      <c r="BE4" s="25">
         <v>45950</v>
       </c>
-      <c r="BF4" s="26">
+      <c r="BF4" s="25">
         <v>45951</v>
       </c>
-      <c r="BG4" s="26">
+      <c r="BG4" s="25">
         <v>45952</v>
       </c>
-      <c r="BH4" s="26">
+      <c r="BH4" s="25">
         <v>45953</v>
       </c>
-      <c r="BI4" s="26">
+      <c r="BI4" s="25">
         <v>45954</v>
       </c>
-      <c r="BJ4" s="26">
+      <c r="BJ4" s="25">
         <v>45955</v>
       </c>
-      <c r="BK4" s="26">
+      <c r="BK4" s="25">
         <v>45956</v>
       </c>
-      <c r="BL4" s="26">
+      <c r="BL4" s="25">
         <v>45957</v>
       </c>
-      <c r="BM4" s="26">
+      <c r="BM4" s="25">
         <v>45958</v>
       </c>
-      <c r="BN4" s="26">
+      <c r="BN4" s="25">
         <v>45959</v>
       </c>
-      <c r="BO4" s="26">
+      <c r="BO4" s="25">
         <v>45960</v>
       </c>
-      <c r="BP4" s="26">
+      <c r="BP4" s="25">
         <v>45961</v>
       </c>
-      <c r="BQ4" s="26">
+      <c r="BQ4" s="25">
         <v>45962</v>
       </c>
-      <c r="BR4" s="26">
+      <c r="BR4" s="25">
         <v>45963</v>
       </c>
-      <c r="BS4" s="26">
+      <c r="BS4" s="25">
         <v>45964</v>
       </c>
-      <c r="BT4" s="26">
+      <c r="BT4" s="25">
         <v>45965</v>
       </c>
-      <c r="BU4" s="26">
+      <c r="BU4" s="25">
         <v>45966</v>
       </c>
-      <c r="BV4" s="26">
+      <c r="BV4" s="25">
         <v>45967</v>
       </c>
-      <c r="BW4" s="26">
+      <c r="BW4" s="25">
         <v>45968</v>
       </c>
-      <c r="BX4" s="26">
+      <c r="BX4" s="25">
         <v>45969</v>
       </c>
-      <c r="BY4" s="26">
+      <c r="BY4" s="25">
         <v>45970</v>
       </c>
-      <c r="BZ4" s="26">
+      <c r="BZ4" s="25">
         <v>45971</v>
       </c>
-      <c r="CA4" s="26">
+      <c r="CA4" s="25">
         <v>45972</v>
       </c>
-      <c r="CB4" s="26">
+      <c r="CB4" s="25">
         <v>45973</v>
       </c>
-      <c r="CC4" s="26">
+      <c r="CC4" s="25">
         <v>45974</v>
       </c>
-      <c r="CD4" s="26">
+      <c r="CD4" s="25">
         <v>45975</v>
       </c>
-      <c r="CE4" s="26">
+      <c r="CE4" s="25">
         <v>45976</v>
       </c>
-      <c r="CF4" s="26">
+      <c r="CF4" s="25">
         <v>45977</v>
       </c>
-      <c r="CG4" s="26">
+      <c r="CG4" s="25">
         <v>45978</v>
       </c>
-      <c r="CH4" s="26">
+      <c r="CH4" s="25">
         <v>45979</v>
       </c>
-      <c r="CI4" s="26">
+      <c r="CI4" s="25">
         <v>45980</v>
       </c>
-      <c r="CJ4" s="26">
+      <c r="CJ4" s="25">
         <v>45981</v>
       </c>
-      <c r="CK4" s="26">
+      <c r="CK4" s="25">
         <v>45982</v>
       </c>
-      <c r="CL4" s="26">
+      <c r="CL4" s="25">
         <v>45983</v>
       </c>
-      <c r="CM4" s="26">
+      <c r="CM4" s="25">
         <v>45984</v>
       </c>
-      <c r="CN4" s="26">
+      <c r="CN4" s="25">
         <v>45985</v>
       </c>
-      <c r="CO4" s="26">
+      <c r="CO4" s="25">
         <v>45986</v>
       </c>
-      <c r="CP4" s="26">
+      <c r="CP4" s="25">
         <v>45987</v>
       </c>
-      <c r="CQ4" s="26">
+      <c r="CQ4" s="25">
         <v>45988</v>
       </c>
-      <c r="CR4" s="26">
+      <c r="CR4" s="25">
         <v>45989</v>
       </c>
-      <c r="CS4" s="26">
+      <c r="CS4" s="25">
         <v>45990</v>
       </c>
-      <c r="CT4" s="26">
+      <c r="CT4" s="25">
         <v>45991</v>
       </c>
-      <c r="CU4" s="26">
+      <c r="CU4" s="25">
         <v>45992</v>
       </c>
-      <c r="CV4" s="26">
+      <c r="CV4" s="25">
         <v>45993</v>
       </c>
-      <c r="CW4" s="26">
+      <c r="CW4" s="25">
         <v>45994</v>
       </c>
-      <c r="CX4" s="26">
+      <c r="CX4" s="25">
         <v>45995</v>
       </c>
-      <c r="CY4" s="26">
+      <c r="CY4" s="25">
         <v>45996</v>
       </c>
-      <c r="CZ4" s="26">
+      <c r="CZ4" s="25">
         <v>45997</v>
       </c>
-      <c r="DA4" s="26">
+      <c r="DA4" s="25">
         <v>45998</v>
       </c>
-      <c r="DB4" s="26">
+      <c r="DB4" s="25">
         <v>45999</v>
       </c>
-      <c r="DC4" s="26">
+      <c r="DC4" s="25">
         <v>46000</v>
       </c>
-      <c r="DD4" s="26">
+      <c r="DD4" s="25">
         <v>46001</v>
       </c>
-      <c r="DE4" s="26">
+      <c r="DE4" s="25">
         <v>46002</v>
       </c>
-      <c r="DF4" s="26">
+      <c r="DF4" s="25">
         <v>46003</v>
       </c>
-      <c r="DG4" s="26">
+      <c r="DG4" s="25">
         <v>46004</v>
       </c>
-      <c r="DH4" s="26">
+      <c r="DH4" s="25">
         <v>46005</v>
       </c>
-      <c r="DI4" s="26">
+      <c r="DI4" s="25">
         <v>46006</v>
       </c>
-      <c r="DJ4" s="26">
+      <c r="DJ4" s="25">
         <v>46007</v>
       </c>
-      <c r="DK4" s="26">
+      <c r="DK4" s="25">
         <v>46008</v>
       </c>
-      <c r="DL4" s="26">
+      <c r="DL4" s="25">
         <v>46009</v>
       </c>
-      <c r="DM4" s="26">
+      <c r="DM4" s="25">
         <v>46010</v>
       </c>
-      <c r="DN4" s="26">
+      <c r="DN4" s="25">
         <v>46011</v>
       </c>
-      <c r="DO4" s="26">
+      <c r="DO4" s="25">
         <v>46012</v>
       </c>
-      <c r="DP4" s="26">
+      <c r="DP4" s="25">
         <v>46013</v>
       </c>
-      <c r="DQ4" s="26">
+      <c r="DQ4" s="25">
         <v>46014</v>
       </c>
-      <c r="DR4" s="26">
+      <c r="DR4" s="25">
         <v>46015</v>
       </c>
-      <c r="DS4" s="26">
+      <c r="DS4" s="25">
         <v>46016</v>
       </c>
-      <c r="DT4" s="26">
+      <c r="DT4" s="25">
         <v>46017</v>
       </c>
-      <c r="DU4" s="26">
+      <c r="DU4" s="25">
         <v>46018</v>
       </c>
-      <c r="DV4" s="26">
+      <c r="DV4" s="25">
         <v>46019</v>
       </c>
-      <c r="DW4" s="26">
+      <c r="DW4" s="25">
         <v>46020</v>
       </c>
-      <c r="DX4" s="26">
+      <c r="DX4" s="25">
         <v>46021</v>
       </c>
-      <c r="DY4" s="26">
+      <c r="DY4" s="25">
         <v>46022</v>
       </c>
-      <c r="DZ4" s="26">
+      <c r="DZ4" s="25">
         <v>46023</v>
       </c>
-      <c r="EA4" s="26">
+      <c r="EA4" s="25">
         <v>46024</v>
       </c>
-      <c r="EB4" s="26">
+      <c r="EB4" s="25">
         <v>46025</v>
       </c>
-      <c r="EC4" s="26">
+      <c r="EC4" s="25">
         <v>46026</v>
       </c>
-      <c r="ED4" s="26">
+      <c r="ED4" s="25">
         <v>46027</v>
       </c>
-      <c r="EE4" s="26">
+      <c r="EE4" s="25">
         <v>46028</v>
       </c>
-      <c r="EF4" s="26">
+      <c r="EF4" s="25">
         <v>46029</v>
       </c>
-      <c r="EG4" s="26">
+      <c r="EG4" s="25">
         <v>46030</v>
       </c>
-      <c r="EH4" s="26">
+      <c r="EH4" s="25">
         <v>46031</v>
       </c>
-      <c r="EI4" s="26">
+      <c r="EI4" s="25">
         <v>46032</v>
       </c>
-      <c r="EJ4" s="26">
+      <c r="EJ4" s="25">
         <v>46033</v>
       </c>
-      <c r="EK4" s="26">
+      <c r="EK4" s="25">
         <v>46034</v>
       </c>
-      <c r="EL4" s="26">
+      <c r="EL4" s="25">
         <v>46035</v>
       </c>
-      <c r="EM4" s="26">
+      <c r="EM4" s="25">
         <v>46036</v>
       </c>
-      <c r="EN4" s="26">
+      <c r="EN4" s="25">
         <v>46037</v>
       </c>
-      <c r="EO4" s="26">
+      <c r="EO4" s="25">
         <v>46038</v>
       </c>
-      <c r="EP4" s="26">
+      <c r="EP4" s="25">
         <v>46039</v>
       </c>
-      <c r="EQ4" s="26">
+      <c r="EQ4" s="25">
         <v>46040</v>
       </c>
-      <c r="ER4" s="26">
+      <c r="ER4" s="25">
         <v>46041</v>
       </c>
-      <c r="ES4" s="26">
+      <c r="ES4" s="25">
         <v>46042</v>
       </c>
-      <c r="ET4" s="26">
+      <c r="ET4" s="25">
         <v>46043</v>
       </c>
-      <c r="EU4" s="26">
+      <c r="EU4" s="25">
         <v>46044</v>
       </c>
-      <c r="EV4" s="26">
+      <c r="EV4" s="25">
         <v>46045</v>
       </c>
-      <c r="EW4" s="26">
+      <c r="EW4" s="25">
         <v>46046</v>
       </c>
-      <c r="EX4" s="26">
+      <c r="EX4" s="25">
         <v>46047</v>
       </c>
-      <c r="EY4" s="26">
+      <c r="EY4" s="25">
         <v>46048</v>
       </c>
-      <c r="EZ4" s="26">
+      <c r="EZ4" s="25">
         <v>46049</v>
       </c>
-      <c r="FA4" s="26">
+      <c r="FA4" s="25">
         <v>46050</v>
       </c>
-      <c r="FB4" s="26">
+      <c r="FB4" s="25">
         <v>46051</v>
       </c>
-      <c r="FC4" s="26">
+      <c r="FC4" s="25">
         <v>46052</v>
       </c>
-      <c r="FD4" s="26">
+      <c r="FD4" s="25">
         <v>46053</v>
       </c>
-      <c r="FE4" s="26">
+      <c r="FE4" s="25">
         <v>46054</v>
       </c>
-      <c r="FF4" s="26">
+      <c r="FF4" s="25">
         <v>46055</v>
       </c>
-      <c r="FG4" s="26">
+      <c r="FG4" s="25">
         <v>46056</v>
       </c>
-      <c r="FH4" s="26">
+      <c r="FH4" s="25">
         <v>46057</v>
       </c>
-      <c r="FI4" s="26">
+      <c r="FI4" s="25">
         <v>46058</v>
       </c>
-      <c r="FJ4" s="26">
+      <c r="FJ4" s="25">
         <v>46059</v>
       </c>
-      <c r="FK4" s="26">
+      <c r="FK4" s="25">
         <v>46060</v>
       </c>
-      <c r="FL4" s="26">
+      <c r="FL4" s="25">
         <v>46061</v>
       </c>
-      <c r="FM4" s="26">
+      <c r="FM4" s="25">
         <v>46062</v>
       </c>
-      <c r="FN4" s="26">
+      <c r="FN4" s="25">
         <v>46063</v>
       </c>
-      <c r="FO4" s="26">
+      <c r="FO4" s="25">
         <v>46064</v>
       </c>
-      <c r="FP4" s="26">
+      <c r="FP4" s="25">
         <v>46065</v>
       </c>
-      <c r="FQ4" s="26">
+      <c r="FQ4" s="25">
         <v>46066</v>
       </c>
-      <c r="FR4" s="26">
+      <c r="FR4" s="25">
         <v>46067</v>
       </c>
-      <c r="FS4" s="26">
+      <c r="FS4" s="25">
         <v>46068</v>
       </c>
-      <c r="FT4" s="26">
+      <c r="FT4" s="25">
         <v>46069</v>
       </c>
-      <c r="FU4" s="26">
+      <c r="FU4" s="25">
         <v>46070</v>
       </c>
-      <c r="FV4" s="26">
+      <c r="FV4" s="25">
         <v>46071</v>
       </c>
-      <c r="FW4" s="26">
+      <c r="FW4" s="25">
         <v>46072</v>
       </c>
-      <c r="FX4" s="26">
+      <c r="FX4" s="25">
         <v>46073</v>
       </c>
-      <c r="FY4" s="26">
+      <c r="FY4" s="25">
         <v>46074</v>
       </c>
-      <c r="FZ4" s="26">
+      <c r="FZ4" s="25">
         <v>46075</v>
       </c>
-      <c r="GA4" s="26">
+      <c r="GA4" s="25">
         <v>46076</v>
       </c>
-      <c r="GB4" s="26">
+      <c r="GB4" s="25">
         <v>46077</v>
       </c>
-      <c r="GC4" s="26">
+      <c r="GC4" s="25">
         <v>46078</v>
       </c>
-      <c r="GD4" s="26">
+      <c r="GD4" s="25">
         <v>46079</v>
       </c>
-      <c r="GE4" s="26">
+      <c r="GE4" s="25">
         <v>46080</v>
       </c>
-      <c r="GF4" s="26">
+      <c r="GF4" s="25">
         <v>46081</v>
       </c>
-      <c r="GG4" s="26">
+      <c r="GG4" s="25">
         <v>46082</v>
       </c>
-      <c r="GH4" s="26">
+      <c r="GH4" s="25">
         <v>46083</v>
       </c>
-      <c r="GI4" s="26">
+      <c r="GI4" s="25">
         <v>46084</v>
       </c>
-      <c r="GJ4" s="26">
+      <c r="GJ4" s="25">
         <v>46085</v>
       </c>
-      <c r="GK4" s="26">
+      <c r="GK4" s="25">
         <v>46086</v>
       </c>
-      <c r="GL4" s="26">
+      <c r="GL4" s="25">
         <v>46087</v>
       </c>
-      <c r="GM4" s="26">
+      <c r="GM4" s="25">
         <v>46088</v>
       </c>
-      <c r="GN4" s="26">
+      <c r="GN4" s="25">
         <v>46089</v>
       </c>
-      <c r="GO4" s="26">
+      <c r="GO4" s="25">
         <v>46090</v>
       </c>
-      <c r="GP4" s="26">
+      <c r="GP4" s="25">
         <v>46091</v>
       </c>
-      <c r="GQ4" s="26">
+      <c r="GQ4" s="25">
         <v>46092</v>
       </c>
-      <c r="GR4" s="26">
+      <c r="GR4" s="25">
         <v>46093</v>
       </c>
-      <c r="GS4" s="26">
+      <c r="GS4" s="25">
         <v>46094</v>
       </c>
-      <c r="GT4" s="26">
+      <c r="GT4" s="25">
         <v>46095</v>
       </c>
-      <c r="GU4" s="26">
+      <c r="GU4" s="25">
         <v>46096</v>
       </c>
-      <c r="GV4" s="26">
+      <c r="GV4" s="25">
         <v>46097</v>
       </c>
-      <c r="GW4" s="26">
+      <c r="GW4" s="25">
         <v>46098</v>
       </c>
-      <c r="GX4" s="26">
+      <c r="GX4" s="25">
         <v>46099</v>
       </c>
-      <c r="GY4" s="26">
+      <c r="GY4" s="25">
         <v>46100</v>
       </c>
-      <c r="GZ4" s="26">
+      <c r="GZ4" s="25">
         <v>46101</v>
       </c>
-      <c r="HA4" s="26">
+      <c r="HA4" s="25">
         <v>46102</v>
       </c>
-      <c r="HB4" s="26">
+      <c r="HB4" s="25">
         <v>46103</v>
       </c>
-      <c r="HC4" s="26">
+      <c r="HC4" s="25">
         <v>46104</v>
       </c>
-      <c r="HD4" s="26">
+      <c r="HD4" s="25">
         <v>46105</v>
       </c>
-      <c r="HE4" s="26">
+      <c r="HE4" s="25">
         <v>46106</v>
       </c>
-      <c r="HF4" s="26">
+      <c r="HF4" s="25">
         <v>46107</v>
       </c>
-      <c r="HG4" s="26">
+      <c r="HG4" s="25">
         <v>46108</v>
       </c>
-      <c r="HH4" s="26">
+      <c r="HH4" s="25">
         <v>46109</v>
       </c>
-      <c r="HI4" s="26">
+      <c r="HI4" s="25">
         <v>46110</v>
       </c>
-      <c r="HJ4" s="26">
+      <c r="HJ4" s="25">
         <v>46111</v>
       </c>
-      <c r="HK4" s="26">
+      <c r="HK4" s="25">
         <v>46112</v>
       </c>
-      <c r="HL4" s="26">
+      <c r="HL4" s="25">
         <v>46113</v>
       </c>
-      <c r="HM4" s="26">
+      <c r="HM4" s="25">
         <v>46114</v>
       </c>
-      <c r="HN4" s="26">
+      <c r="HN4" s="25">
         <v>46115</v>
       </c>
-      <c r="HO4" s="26">
+      <c r="HO4" s="25">
         <v>46116</v>
       </c>
-      <c r="HP4" s="26">
+      <c r="HP4" s="25">
         <v>46117</v>
       </c>
-      <c r="HQ4" s="26">
+      <c r="HQ4" s="25">
         <v>46118</v>
       </c>
-      <c r="HR4" s="26">
+      <c r="HR4" s="25">
         <v>46119</v>
       </c>
-      <c r="HS4" s="26">
+      <c r="HS4" s="25">
         <v>46120</v>
       </c>
-      <c r="HT4" s="26">
+      <c r="HT4" s="25">
         <v>46121</v>
       </c>
-      <c r="HU4" s="26">
+      <c r="HU4" s="25">
         <v>46122</v>
       </c>
     </row>
-    <row r="5" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="2:229" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="47">
         <v>45902</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="48">
         <v>35</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="47">
         <v>45903</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="48">
         <v>31</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="49">
         <v>1</v>
       </c>
-      <c r="H5" s="29"/>
+      <c r="H5" s="27"/>
       <c r="J5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -3471,26 +3574,26 @@
       <c r="HT5" s="1"/>
       <c r="HU5" s="1"/>
     </row>
-    <row r="6" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+    <row r="6" spans="2:229" ht="37.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="47">
         <v>45937</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="48">
         <v>32</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="47">
         <v>45938</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="48">
         <v>32</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="49">
         <v>1</v>
       </c>
-      <c r="H6" s="30"/>
+      <c r="H6" s="28"/>
       <c r="J6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
@@ -3695,26 +3798,26 @@
       <c r="HT6" s="1"/>
       <c r="HU6" s="1"/>
     </row>
-    <row r="7" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="27" t="s">
+    <row r="7" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="47">
         <v>45973</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="48">
         <v>14</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="47">
         <v>45975</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="48">
         <v>13</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="49">
         <v>1</v>
       </c>
-      <c r="H7" s="30"/>
+      <c r="H7" s="28"/>
       <c r="J7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
@@ -3919,26 +4022,26 @@
       <c r="HT7" s="1"/>
       <c r="HU7" s="1"/>
     </row>
-    <row r="8" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="2:229" ht="38.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="47">
         <v>45968</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="48">
         <v>36</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="47">
         <v>45969</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="48">
         <v>33</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="49">
         <v>1</v>
       </c>
-      <c r="H8" s="30"/>
+      <c r="H8" s="28"/>
       <c r="J8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -4143,24 +4246,26 @@
       <c r="HT8" s="1"/>
       <c r="HU8" s="1"/>
     </row>
-    <row r="9" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:229" ht="42.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="47">
         <v>46007</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="48">
         <v>47</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="47">
         <v>46007</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="30"/>
+      <c r="F9" s="48">
+        <v>47</v>
+      </c>
+      <c r="G9" s="49">
+        <v>1</v>
+      </c>
+      <c r="H9" s="28"/>
       <c r="J9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -4365,16 +4470,26 @@
       <c r="HT9" s="1"/>
       <c r="HU9" s="1"/>
     </row>
-    <row r="10" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="30"/>
+    <row r="10" spans="2:229" ht="42.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="47">
+        <v>46054</v>
+      </c>
+      <c r="D10" s="48">
+        <v>14</v>
+      </c>
+      <c r="E10" s="47">
+        <v>46054</v>
+      </c>
+      <c r="F10" s="48">
+        <v>14</v>
+      </c>
+      <c r="G10" s="49">
+        <v>1</v>
+      </c>
+      <c r="H10" s="28"/>
       <c r="J10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
@@ -4579,16 +4694,26 @@
       <c r="HT10" s="1"/>
       <c r="HU10" s="1"/>
     </row>
-    <row r="11" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="30"/>
+    <row r="11" spans="2:229" ht="37.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="47">
+        <v>46068</v>
+      </c>
+      <c r="D11" s="48">
+        <v>14</v>
+      </c>
+      <c r="E11" s="47">
+        <v>46068</v>
+      </c>
+      <c r="F11" s="48">
+        <v>14</v>
+      </c>
+      <c r="G11" s="49">
+        <v>1</v>
+      </c>
+      <c r="H11" s="28"/>
       <c r="J11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
@@ -4793,16 +4918,26 @@
       <c r="HT11" s="1"/>
       <c r="HU11" s="1"/>
     </row>
-    <row r="12" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="30"/>
+    <row r="12" spans="2:229" ht="35.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="47">
+        <v>46083</v>
+      </c>
+      <c r="D12" s="48">
+        <v>7</v>
+      </c>
+      <c r="E12" s="47">
+        <v>46083</v>
+      </c>
+      <c r="F12" s="48">
+        <v>7</v>
+      </c>
+      <c r="G12" s="49">
+        <v>1</v>
+      </c>
+      <c r="H12" s="28"/>
       <c r="J12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
@@ -5007,16 +5142,16 @@
       <c r="HT12" s="1"/>
       <c r="HU12" s="1"/>
     </row>
-    <row r="13" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7">
+    <row r="13" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="44"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="49">
         <v>0</v>
       </c>
-      <c r="H13" s="30"/>
+      <c r="H13" s="28"/>
       <c r="J13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
@@ -5221,16 +5356,16 @@
       <c r="HT13" s="1"/>
       <c r="HU13" s="1"/>
     </row>
-    <row r="14" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="27"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7">
+    <row r="14" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="45"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="49">
         <v>0</v>
       </c>
-      <c r="H14" s="30"/>
+      <c r="H14" s="28"/>
       <c r="J14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -5435,7 +5570,7 @@
       <c r="HT14" s="1"/>
       <c r="HU14" s="1"/>
     </row>
-    <row r="15" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>2</v>
       </c>
@@ -5454,160 +5589,160 @@
       <c r="G15" s="7">
         <v>0</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="BQ15" s="31"/>
-      <c r="BS15" s="31"/>
-      <c r="BU15" s="31"/>
-      <c r="BW15" s="31"/>
-      <c r="BY15" s="31"/>
-      <c r="CA15" s="31"/>
-      <c r="CC15" s="31"/>
-      <c r="CE15" s="31"/>
-      <c r="CG15" s="31"/>
-      <c r="CI15" s="31"/>
-      <c r="CK15" s="31"/>
-      <c r="CL15" s="31"/>
-      <c r="CM15" s="31"/>
-      <c r="CN15" s="31"/>
-      <c r="CO15" s="31"/>
-      <c r="CP15" s="31"/>
-      <c r="CQ15" s="31"/>
-      <c r="CR15" s="31"/>
-      <c r="CS15" s="31"/>
-      <c r="CT15" s="31"/>
-      <c r="CU15" s="31"/>
-      <c r="CV15" s="31"/>
-      <c r="CW15" s="31"/>
-      <c r="CX15" s="31"/>
-      <c r="CY15" s="31"/>
-      <c r="CZ15" s="31"/>
-      <c r="DA15" s="31"/>
-      <c r="DB15" s="31"/>
-      <c r="DC15" s="31"/>
-      <c r="DD15" s="31"/>
-      <c r="DE15" s="31"/>
-      <c r="DF15" s="31"/>
-      <c r="DG15" s="31"/>
-      <c r="DH15" s="31"/>
-      <c r="DI15" s="31"/>
-      <c r="DJ15" s="31"/>
-      <c r="DK15" s="31"/>
-      <c r="DL15" s="31"/>
-      <c r="DM15" s="31"/>
-      <c r="DN15" s="31"/>
-      <c r="DO15" s="31"/>
-      <c r="DP15" s="31"/>
-      <c r="DQ15" s="31"/>
-      <c r="DR15" s="31"/>
-      <c r="DS15" s="31"/>
-      <c r="DT15" s="31"/>
-      <c r="DU15" s="31"/>
-      <c r="DV15" s="31"/>
-      <c r="DW15" s="31"/>
-      <c r="DX15" s="31"/>
-      <c r="DY15" s="31"/>
-      <c r="DZ15" s="31"/>
-      <c r="EA15" s="31"/>
-      <c r="EB15" s="31"/>
-      <c r="EC15" s="31"/>
-      <c r="ED15" s="31"/>
-      <c r="EE15" s="31"/>
-      <c r="EF15" s="31"/>
-      <c r="EG15" s="31"/>
-      <c r="EH15" s="31"/>
-      <c r="EI15" s="31"/>
-      <c r="EJ15" s="31"/>
-      <c r="EK15" s="31"/>
-      <c r="EL15" s="31"/>
-      <c r="EM15" s="31"/>
-      <c r="EN15" s="31"/>
-      <c r="EO15" s="31"/>
-      <c r="EP15" s="31"/>
-      <c r="EQ15" s="31"/>
-      <c r="ER15" s="31"/>
-      <c r="ES15" s="31"/>
-      <c r="ET15" s="31"/>
-      <c r="EU15" s="31"/>
-      <c r="EV15" s="31"/>
-      <c r="EW15" s="31"/>
-      <c r="EX15" s="31"/>
-      <c r="EY15" s="31"/>
-      <c r="EZ15" s="31"/>
-      <c r="FA15" s="31"/>
-      <c r="FB15" s="31"/>
-      <c r="FC15" s="31"/>
-      <c r="FD15" s="31"/>
-      <c r="FE15" s="31"/>
-      <c r="FF15" s="31"/>
-      <c r="FG15" s="31"/>
-      <c r="FH15" s="31"/>
-      <c r="FI15" s="31"/>
-      <c r="FJ15" s="31"/>
-      <c r="FK15" s="31"/>
-      <c r="FL15" s="31"/>
-      <c r="FM15" s="31"/>
-      <c r="FN15" s="31"/>
-      <c r="FO15" s="31"/>
-      <c r="FP15" s="31"/>
-      <c r="FQ15" s="31"/>
-      <c r="FR15" s="31"/>
-      <c r="FS15" s="31"/>
-      <c r="FT15" s="31"/>
-      <c r="FU15" s="31"/>
-      <c r="FV15" s="31"/>
-      <c r="FW15" s="31"/>
-      <c r="FX15" s="31"/>
-      <c r="FY15" s="31"/>
-      <c r="FZ15" s="31"/>
-      <c r="GA15" s="31"/>
-      <c r="GB15" s="31"/>
-      <c r="GC15" s="31"/>
-      <c r="GD15" s="31"/>
-      <c r="GE15" s="31"/>
-      <c r="GF15" s="31"/>
-      <c r="GG15" s="31"/>
-      <c r="GH15" s="31"/>
-      <c r="GI15" s="31"/>
-      <c r="GJ15" s="31"/>
-      <c r="GK15" s="31"/>
-      <c r="GL15" s="31"/>
-      <c r="GM15" s="31"/>
-      <c r="GN15" s="31"/>
-      <c r="GO15" s="31"/>
-      <c r="GP15" s="31"/>
-      <c r="GQ15" s="31"/>
-      <c r="GR15" s="31"/>
-      <c r="GS15" s="31"/>
-      <c r="GT15" s="31"/>
-      <c r="GU15" s="31"/>
-      <c r="GV15" s="31"/>
-      <c r="GW15" s="31"/>
-      <c r="GX15" s="31"/>
-      <c r="GY15" s="31"/>
-      <c r="GZ15" s="31"/>
-      <c r="HA15" s="31"/>
-      <c r="HB15" s="31"/>
-      <c r="HC15" s="31"/>
-      <c r="HD15" s="31"/>
-      <c r="HE15" s="31"/>
-      <c r="HF15" s="31"/>
-      <c r="HG15" s="31"/>
-      <c r="HH15" s="31"/>
-      <c r="HI15" s="31"/>
-      <c r="HJ15" s="31"/>
-      <c r="HK15" s="31"/>
-      <c r="HL15" s="31"/>
-      <c r="HM15" s="31"/>
-      <c r="HN15" s="31"/>
-      <c r="HO15" s="31"/>
-      <c r="HP15" s="31"/>
-      <c r="HQ15" s="31"/>
-      <c r="HR15" s="31"/>
-      <c r="HS15" s="31"/>
-      <c r="HT15" s="31"/>
-      <c r="HU15" s="31"/>
+      <c r="H15" s="28"/>
+      <c r="BQ15" s="29"/>
+      <c r="BS15" s="29"/>
+      <c r="BU15" s="29"/>
+      <c r="BW15" s="29"/>
+      <c r="BY15" s="29"/>
+      <c r="CA15" s="29"/>
+      <c r="CC15" s="29"/>
+      <c r="CE15" s="29"/>
+      <c r="CG15" s="29"/>
+      <c r="CI15" s="29"/>
+      <c r="CK15" s="29"/>
+      <c r="CL15" s="29"/>
+      <c r="CM15" s="29"/>
+      <c r="CN15" s="29"/>
+      <c r="CO15" s="29"/>
+      <c r="CP15" s="29"/>
+      <c r="CQ15" s="29"/>
+      <c r="CR15" s="29"/>
+      <c r="CS15" s="29"/>
+      <c r="CT15" s="29"/>
+      <c r="CU15" s="29"/>
+      <c r="CV15" s="29"/>
+      <c r="CW15" s="29"/>
+      <c r="CX15" s="29"/>
+      <c r="CY15" s="29"/>
+      <c r="CZ15" s="29"/>
+      <c r="DA15" s="29"/>
+      <c r="DB15" s="29"/>
+      <c r="DC15" s="29"/>
+      <c r="DD15" s="29"/>
+      <c r="DE15" s="29"/>
+      <c r="DF15" s="29"/>
+      <c r="DG15" s="29"/>
+      <c r="DH15" s="29"/>
+      <c r="DI15" s="29"/>
+      <c r="DJ15" s="29"/>
+      <c r="DK15" s="29"/>
+      <c r="DL15" s="29"/>
+      <c r="DM15" s="29"/>
+      <c r="DN15" s="29"/>
+      <c r="DO15" s="29"/>
+      <c r="DP15" s="29"/>
+      <c r="DQ15" s="29"/>
+      <c r="DR15" s="29"/>
+      <c r="DS15" s="29"/>
+      <c r="DT15" s="29"/>
+      <c r="DU15" s="29"/>
+      <c r="DV15" s="29"/>
+      <c r="DW15" s="29"/>
+      <c r="DX15" s="29"/>
+      <c r="DY15" s="29"/>
+      <c r="DZ15" s="29"/>
+      <c r="EA15" s="29"/>
+      <c r="EB15" s="29"/>
+      <c r="EC15" s="29"/>
+      <c r="ED15" s="29"/>
+      <c r="EE15" s="29"/>
+      <c r="EF15" s="29"/>
+      <c r="EG15" s="29"/>
+      <c r="EH15" s="29"/>
+      <c r="EI15" s="29"/>
+      <c r="EJ15" s="29"/>
+      <c r="EK15" s="29"/>
+      <c r="EL15" s="29"/>
+      <c r="EM15" s="29"/>
+      <c r="EN15" s="29"/>
+      <c r="EO15" s="29"/>
+      <c r="EP15" s="29"/>
+      <c r="EQ15" s="29"/>
+      <c r="ER15" s="29"/>
+      <c r="ES15" s="29"/>
+      <c r="ET15" s="29"/>
+      <c r="EU15" s="29"/>
+      <c r="EV15" s="29"/>
+      <c r="EW15" s="29"/>
+      <c r="EX15" s="29"/>
+      <c r="EY15" s="29"/>
+      <c r="EZ15" s="29"/>
+      <c r="FA15" s="29"/>
+      <c r="FB15" s="29"/>
+      <c r="FC15" s="29"/>
+      <c r="FD15" s="29"/>
+      <c r="FE15" s="29"/>
+      <c r="FF15" s="29"/>
+      <c r="FG15" s="29"/>
+      <c r="FH15" s="29"/>
+      <c r="FI15" s="29"/>
+      <c r="FJ15" s="29"/>
+      <c r="FK15" s="29"/>
+      <c r="FL15" s="29"/>
+      <c r="FM15" s="29"/>
+      <c r="FN15" s="29"/>
+      <c r="FO15" s="29"/>
+      <c r="FP15" s="29"/>
+      <c r="FQ15" s="29"/>
+      <c r="FR15" s="29"/>
+      <c r="FS15" s="29"/>
+      <c r="FT15" s="29"/>
+      <c r="FU15" s="29"/>
+      <c r="FV15" s="29"/>
+      <c r="FW15" s="29"/>
+      <c r="FX15" s="29"/>
+      <c r="FY15" s="29"/>
+      <c r="FZ15" s="29"/>
+      <c r="GA15" s="29"/>
+      <c r="GB15" s="29"/>
+      <c r="GC15" s="29"/>
+      <c r="GD15" s="29"/>
+      <c r="GE15" s="29"/>
+      <c r="GF15" s="29"/>
+      <c r="GG15" s="29"/>
+      <c r="GH15" s="29"/>
+      <c r="GI15" s="29"/>
+      <c r="GJ15" s="29"/>
+      <c r="GK15" s="29"/>
+      <c r="GL15" s="29"/>
+      <c r="GM15" s="29"/>
+      <c r="GN15" s="29"/>
+      <c r="GO15" s="29"/>
+      <c r="GP15" s="29"/>
+      <c r="GQ15" s="29"/>
+      <c r="GR15" s="29"/>
+      <c r="GS15" s="29"/>
+      <c r="GT15" s="29"/>
+      <c r="GU15" s="29"/>
+      <c r="GV15" s="29"/>
+      <c r="GW15" s="29"/>
+      <c r="GX15" s="29"/>
+      <c r="GY15" s="29"/>
+      <c r="GZ15" s="29"/>
+      <c r="HA15" s="29"/>
+      <c r="HB15" s="29"/>
+      <c r="HC15" s="29"/>
+      <c r="HD15" s="29"/>
+      <c r="HE15" s="29"/>
+      <c r="HF15" s="29"/>
+      <c r="HG15" s="29"/>
+      <c r="HH15" s="29"/>
+      <c r="HI15" s="29"/>
+      <c r="HJ15" s="29"/>
+      <c r="HK15" s="29"/>
+      <c r="HL15" s="29"/>
+      <c r="HM15" s="29"/>
+      <c r="HN15" s="29"/>
+      <c r="HO15" s="29"/>
+      <c r="HP15" s="29"/>
+      <c r="HQ15" s="29"/>
+      <c r="HR15" s="29"/>
+      <c r="HS15" s="29"/>
+      <c r="HT15" s="29"/>
+      <c r="HU15" s="29"/>
     </row>
-    <row r="16" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>3</v>
       </c>
@@ -5626,160 +5761,160 @@
       <c r="G16" s="7">
         <v>0</v>
       </c>
-      <c r="H16" s="30"/>
-      <c r="BQ16" s="31"/>
-      <c r="BS16" s="31"/>
-      <c r="BU16" s="31"/>
-      <c r="BW16" s="31"/>
-      <c r="BY16" s="31"/>
-      <c r="CA16" s="31"/>
-      <c r="CC16" s="31"/>
-      <c r="CE16" s="31"/>
-      <c r="CG16" s="31"/>
-      <c r="CI16" s="31"/>
-      <c r="CK16" s="31"/>
-      <c r="CL16" s="31"/>
-      <c r="CM16" s="31"/>
-      <c r="CN16" s="31"/>
-      <c r="CO16" s="31"/>
-      <c r="CP16" s="31"/>
-      <c r="CQ16" s="31"/>
-      <c r="CR16" s="31"/>
-      <c r="CS16" s="31"/>
-      <c r="CT16" s="31"/>
-      <c r="CU16" s="31"/>
-      <c r="CV16" s="31"/>
-      <c r="CW16" s="31"/>
-      <c r="CX16" s="31"/>
-      <c r="CY16" s="31"/>
-      <c r="CZ16" s="31"/>
-      <c r="DA16" s="31"/>
-      <c r="DB16" s="31"/>
-      <c r="DC16" s="31"/>
-      <c r="DD16" s="31"/>
-      <c r="DE16" s="31"/>
-      <c r="DF16" s="31"/>
-      <c r="DG16" s="31"/>
-      <c r="DH16" s="31"/>
-      <c r="DI16" s="31"/>
-      <c r="DJ16" s="31"/>
-      <c r="DK16" s="31"/>
-      <c r="DL16" s="31"/>
-      <c r="DM16" s="31"/>
-      <c r="DN16" s="31"/>
-      <c r="DO16" s="31"/>
-      <c r="DP16" s="31"/>
-      <c r="DQ16" s="31"/>
-      <c r="DR16" s="31"/>
-      <c r="DS16" s="31"/>
-      <c r="DT16" s="31"/>
-      <c r="DU16" s="31"/>
-      <c r="DV16" s="31"/>
-      <c r="DW16" s="31"/>
-      <c r="DX16" s="31"/>
-      <c r="DY16" s="31"/>
-      <c r="DZ16" s="31"/>
-      <c r="EA16" s="31"/>
-      <c r="EB16" s="31"/>
-      <c r="EC16" s="31"/>
-      <c r="ED16" s="31"/>
-      <c r="EE16" s="31"/>
-      <c r="EF16" s="31"/>
-      <c r="EG16" s="31"/>
-      <c r="EH16" s="31"/>
-      <c r="EI16" s="31"/>
-      <c r="EJ16" s="31"/>
-      <c r="EK16" s="31"/>
-      <c r="EL16" s="31"/>
-      <c r="EM16" s="31"/>
-      <c r="EN16" s="31"/>
-      <c r="EO16" s="31"/>
-      <c r="EP16" s="31"/>
-      <c r="EQ16" s="31"/>
-      <c r="ER16" s="31"/>
-      <c r="ES16" s="31"/>
-      <c r="ET16" s="31"/>
-      <c r="EU16" s="31"/>
-      <c r="EV16" s="31"/>
-      <c r="EW16" s="31"/>
-      <c r="EX16" s="31"/>
-      <c r="EY16" s="31"/>
-      <c r="EZ16" s="31"/>
-      <c r="FA16" s="31"/>
-      <c r="FB16" s="31"/>
-      <c r="FC16" s="31"/>
-      <c r="FD16" s="31"/>
-      <c r="FE16" s="31"/>
-      <c r="FF16" s="31"/>
-      <c r="FG16" s="31"/>
-      <c r="FH16" s="31"/>
-      <c r="FI16" s="31"/>
-      <c r="FJ16" s="31"/>
-      <c r="FK16" s="31"/>
-      <c r="FL16" s="31"/>
-      <c r="FM16" s="31"/>
-      <c r="FN16" s="31"/>
-      <c r="FO16" s="31"/>
-      <c r="FP16" s="31"/>
-      <c r="FQ16" s="31"/>
-      <c r="FR16" s="31"/>
-      <c r="FS16" s="31"/>
-      <c r="FT16" s="31"/>
-      <c r="FU16" s="31"/>
-      <c r="FV16" s="31"/>
-      <c r="FW16" s="31"/>
-      <c r="FX16" s="31"/>
-      <c r="FY16" s="31"/>
-      <c r="FZ16" s="31"/>
-      <c r="GA16" s="31"/>
-      <c r="GB16" s="31"/>
-      <c r="GC16" s="31"/>
-      <c r="GD16" s="31"/>
-      <c r="GE16" s="31"/>
-      <c r="GF16" s="31"/>
-      <c r="GG16" s="31"/>
-      <c r="GH16" s="31"/>
-      <c r="GI16" s="31"/>
-      <c r="GJ16" s="31"/>
-      <c r="GK16" s="31"/>
-      <c r="GL16" s="31"/>
-      <c r="GM16" s="31"/>
-      <c r="GN16" s="31"/>
-      <c r="GO16" s="31"/>
-      <c r="GP16" s="31"/>
-      <c r="GQ16" s="31"/>
-      <c r="GR16" s="31"/>
-      <c r="GS16" s="31"/>
-      <c r="GT16" s="31"/>
-      <c r="GU16" s="31"/>
-      <c r="GV16" s="31"/>
-      <c r="GW16" s="31"/>
-      <c r="GX16" s="31"/>
-      <c r="GY16" s="31"/>
-      <c r="GZ16" s="31"/>
-      <c r="HA16" s="31"/>
-      <c r="HB16" s="31"/>
-      <c r="HC16" s="31"/>
-      <c r="HD16" s="31"/>
-      <c r="HE16" s="31"/>
-      <c r="HF16" s="31"/>
-      <c r="HG16" s="31"/>
-      <c r="HH16" s="31"/>
-      <c r="HI16" s="31"/>
-      <c r="HJ16" s="31"/>
-      <c r="HK16" s="31"/>
-      <c r="HL16" s="31"/>
-      <c r="HM16" s="31"/>
-      <c r="HN16" s="31"/>
-      <c r="HO16" s="31"/>
-      <c r="HP16" s="31"/>
-      <c r="HQ16" s="31"/>
-      <c r="HR16" s="31"/>
-      <c r="HS16" s="31"/>
-      <c r="HT16" s="31"/>
-      <c r="HU16" s="31"/>
+      <c r="H16" s="28"/>
+      <c r="BQ16" s="29"/>
+      <c r="BS16" s="29"/>
+      <c r="BU16" s="29"/>
+      <c r="BW16" s="29"/>
+      <c r="BY16" s="29"/>
+      <c r="CA16" s="29"/>
+      <c r="CC16" s="29"/>
+      <c r="CE16" s="29"/>
+      <c r="CG16" s="29"/>
+      <c r="CI16" s="29"/>
+      <c r="CK16" s="29"/>
+      <c r="CL16" s="29"/>
+      <c r="CM16" s="29"/>
+      <c r="CN16" s="29"/>
+      <c r="CO16" s="29"/>
+      <c r="CP16" s="29"/>
+      <c r="CQ16" s="29"/>
+      <c r="CR16" s="29"/>
+      <c r="CS16" s="29"/>
+      <c r="CT16" s="29"/>
+      <c r="CU16" s="29"/>
+      <c r="CV16" s="29"/>
+      <c r="CW16" s="29"/>
+      <c r="CX16" s="29"/>
+      <c r="CY16" s="29"/>
+      <c r="CZ16" s="29"/>
+      <c r="DA16" s="29"/>
+      <c r="DB16" s="29"/>
+      <c r="DC16" s="29"/>
+      <c r="DD16" s="29"/>
+      <c r="DE16" s="29"/>
+      <c r="DF16" s="29"/>
+      <c r="DG16" s="29"/>
+      <c r="DH16" s="29"/>
+      <c r="DI16" s="29"/>
+      <c r="DJ16" s="29"/>
+      <c r="DK16" s="29"/>
+      <c r="DL16" s="29"/>
+      <c r="DM16" s="29"/>
+      <c r="DN16" s="29"/>
+      <c r="DO16" s="29"/>
+      <c r="DP16" s="29"/>
+      <c r="DQ16" s="29"/>
+      <c r="DR16" s="29"/>
+      <c r="DS16" s="29"/>
+      <c r="DT16" s="29"/>
+      <c r="DU16" s="29"/>
+      <c r="DV16" s="29"/>
+      <c r="DW16" s="29"/>
+      <c r="DX16" s="29"/>
+      <c r="DY16" s="29"/>
+      <c r="DZ16" s="29"/>
+      <c r="EA16" s="29"/>
+      <c r="EB16" s="29"/>
+      <c r="EC16" s="29"/>
+      <c r="ED16" s="29"/>
+      <c r="EE16" s="29"/>
+      <c r="EF16" s="29"/>
+      <c r="EG16" s="29"/>
+      <c r="EH16" s="29"/>
+      <c r="EI16" s="29"/>
+      <c r="EJ16" s="29"/>
+      <c r="EK16" s="29"/>
+      <c r="EL16" s="29"/>
+      <c r="EM16" s="29"/>
+      <c r="EN16" s="29"/>
+      <c r="EO16" s="29"/>
+      <c r="EP16" s="29"/>
+      <c r="EQ16" s="29"/>
+      <c r="ER16" s="29"/>
+      <c r="ES16" s="29"/>
+      <c r="ET16" s="29"/>
+      <c r="EU16" s="29"/>
+      <c r="EV16" s="29"/>
+      <c r="EW16" s="29"/>
+      <c r="EX16" s="29"/>
+      <c r="EY16" s="29"/>
+      <c r="EZ16" s="29"/>
+      <c r="FA16" s="29"/>
+      <c r="FB16" s="29"/>
+      <c r="FC16" s="29"/>
+      <c r="FD16" s="29"/>
+      <c r="FE16" s="29"/>
+      <c r="FF16" s="29"/>
+      <c r="FG16" s="29"/>
+      <c r="FH16" s="29"/>
+      <c r="FI16" s="29"/>
+      <c r="FJ16" s="29"/>
+      <c r="FK16" s="29"/>
+      <c r="FL16" s="29"/>
+      <c r="FM16" s="29"/>
+      <c r="FN16" s="29"/>
+      <c r="FO16" s="29"/>
+      <c r="FP16" s="29"/>
+      <c r="FQ16" s="29"/>
+      <c r="FR16" s="29"/>
+      <c r="FS16" s="29"/>
+      <c r="FT16" s="29"/>
+      <c r="FU16" s="29"/>
+      <c r="FV16" s="29"/>
+      <c r="FW16" s="29"/>
+      <c r="FX16" s="29"/>
+      <c r="FY16" s="29"/>
+      <c r="FZ16" s="29"/>
+      <c r="GA16" s="29"/>
+      <c r="GB16" s="29"/>
+      <c r="GC16" s="29"/>
+      <c r="GD16" s="29"/>
+      <c r="GE16" s="29"/>
+      <c r="GF16" s="29"/>
+      <c r="GG16" s="29"/>
+      <c r="GH16" s="29"/>
+      <c r="GI16" s="29"/>
+      <c r="GJ16" s="29"/>
+      <c r="GK16" s="29"/>
+      <c r="GL16" s="29"/>
+      <c r="GM16" s="29"/>
+      <c r="GN16" s="29"/>
+      <c r="GO16" s="29"/>
+      <c r="GP16" s="29"/>
+      <c r="GQ16" s="29"/>
+      <c r="GR16" s="29"/>
+      <c r="GS16" s="29"/>
+      <c r="GT16" s="29"/>
+      <c r="GU16" s="29"/>
+      <c r="GV16" s="29"/>
+      <c r="GW16" s="29"/>
+      <c r="GX16" s="29"/>
+      <c r="GY16" s="29"/>
+      <c r="GZ16" s="29"/>
+      <c r="HA16" s="29"/>
+      <c r="HB16" s="29"/>
+      <c r="HC16" s="29"/>
+      <c r="HD16" s="29"/>
+      <c r="HE16" s="29"/>
+      <c r="HF16" s="29"/>
+      <c r="HG16" s="29"/>
+      <c r="HH16" s="29"/>
+      <c r="HI16" s="29"/>
+      <c r="HJ16" s="29"/>
+      <c r="HK16" s="29"/>
+      <c r="HL16" s="29"/>
+      <c r="HM16" s="29"/>
+      <c r="HN16" s="29"/>
+      <c r="HO16" s="29"/>
+      <c r="HP16" s="29"/>
+      <c r="HQ16" s="29"/>
+      <c r="HR16" s="29"/>
+      <c r="HS16" s="29"/>
+      <c r="HT16" s="29"/>
+      <c r="HU16" s="29"/>
     </row>
-    <row r="17" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -5798,160 +5933,160 @@
       <c r="G17" s="7">
         <v>0</v>
       </c>
-      <c r="H17" s="30"/>
-      <c r="BQ17" s="31"/>
-      <c r="BS17" s="31"/>
-      <c r="BU17" s="31"/>
-      <c r="BW17" s="31"/>
-      <c r="BY17" s="31"/>
-      <c r="CA17" s="31"/>
-      <c r="CC17" s="31"/>
-      <c r="CE17" s="31"/>
-      <c r="CG17" s="31"/>
-      <c r="CI17" s="31"/>
-      <c r="CK17" s="31"/>
-      <c r="CL17" s="31"/>
-      <c r="CM17" s="31"/>
-      <c r="CN17" s="31"/>
-      <c r="CO17" s="31"/>
-      <c r="CP17" s="31"/>
-      <c r="CQ17" s="31"/>
-      <c r="CR17" s="31"/>
-      <c r="CS17" s="31"/>
-      <c r="CT17" s="31"/>
-      <c r="CU17" s="31"/>
-      <c r="CV17" s="31"/>
-      <c r="CW17" s="31"/>
-      <c r="CX17" s="31"/>
-      <c r="CY17" s="31"/>
-      <c r="CZ17" s="31"/>
-      <c r="DA17" s="31"/>
-      <c r="DB17" s="31"/>
-      <c r="DC17" s="31"/>
-      <c r="DD17" s="31"/>
-      <c r="DE17" s="31"/>
-      <c r="DF17" s="31"/>
-      <c r="DG17" s="31"/>
-      <c r="DH17" s="31"/>
-      <c r="DI17" s="31"/>
-      <c r="DJ17" s="31"/>
-      <c r="DK17" s="31"/>
-      <c r="DL17" s="31"/>
-      <c r="DM17" s="31"/>
-      <c r="DN17" s="31"/>
-      <c r="DO17" s="31"/>
-      <c r="DP17" s="31"/>
-      <c r="DQ17" s="31"/>
-      <c r="DR17" s="31"/>
-      <c r="DS17" s="31"/>
-      <c r="DT17" s="31"/>
-      <c r="DU17" s="31"/>
-      <c r="DV17" s="31"/>
-      <c r="DW17" s="31"/>
-      <c r="DX17" s="31"/>
-      <c r="DY17" s="31"/>
-      <c r="DZ17" s="31"/>
-      <c r="EA17" s="31"/>
-      <c r="EB17" s="31"/>
-      <c r="EC17" s="31"/>
-      <c r="ED17" s="31"/>
-      <c r="EE17" s="31"/>
-      <c r="EF17" s="31"/>
-      <c r="EG17" s="31"/>
-      <c r="EH17" s="31"/>
-      <c r="EI17" s="31"/>
-      <c r="EJ17" s="31"/>
-      <c r="EK17" s="31"/>
-      <c r="EL17" s="31"/>
-      <c r="EM17" s="31"/>
-      <c r="EN17" s="31"/>
-      <c r="EO17" s="31"/>
-      <c r="EP17" s="31"/>
-      <c r="EQ17" s="31"/>
-      <c r="ER17" s="31"/>
-      <c r="ES17" s="31"/>
-      <c r="ET17" s="31"/>
-      <c r="EU17" s="31"/>
-      <c r="EV17" s="31"/>
-      <c r="EW17" s="31"/>
-      <c r="EX17" s="31"/>
-      <c r="EY17" s="31"/>
-      <c r="EZ17" s="31"/>
-      <c r="FA17" s="31"/>
-      <c r="FB17" s="31"/>
-      <c r="FC17" s="31"/>
-      <c r="FD17" s="31"/>
-      <c r="FE17" s="31"/>
-      <c r="FF17" s="31"/>
-      <c r="FG17" s="31"/>
-      <c r="FH17" s="31"/>
-      <c r="FI17" s="31"/>
-      <c r="FJ17" s="31"/>
-      <c r="FK17" s="31"/>
-      <c r="FL17" s="31"/>
-      <c r="FM17" s="31"/>
-      <c r="FN17" s="31"/>
-      <c r="FO17" s="31"/>
-      <c r="FP17" s="31"/>
-      <c r="FQ17" s="31"/>
-      <c r="FR17" s="31"/>
-      <c r="FS17" s="31"/>
-      <c r="FT17" s="31"/>
-      <c r="FU17" s="31"/>
-      <c r="FV17" s="31"/>
-      <c r="FW17" s="31"/>
-      <c r="FX17" s="31"/>
-      <c r="FY17" s="31"/>
-      <c r="FZ17" s="31"/>
-      <c r="GA17" s="31"/>
-      <c r="GB17" s="31"/>
-      <c r="GC17" s="31"/>
-      <c r="GD17" s="31"/>
-      <c r="GE17" s="31"/>
-      <c r="GF17" s="31"/>
-      <c r="GG17" s="31"/>
-      <c r="GH17" s="31"/>
-      <c r="GI17" s="31"/>
-      <c r="GJ17" s="31"/>
-      <c r="GK17" s="31"/>
-      <c r="GL17" s="31"/>
-      <c r="GM17" s="31"/>
-      <c r="GN17" s="31"/>
-      <c r="GO17" s="31"/>
-      <c r="GP17" s="31"/>
-      <c r="GQ17" s="31"/>
-      <c r="GR17" s="31"/>
-      <c r="GS17" s="31"/>
-      <c r="GT17" s="31"/>
-      <c r="GU17" s="31"/>
-      <c r="GV17" s="31"/>
-      <c r="GW17" s="31"/>
-      <c r="GX17" s="31"/>
-      <c r="GY17" s="31"/>
-      <c r="GZ17" s="31"/>
-      <c r="HA17" s="31"/>
-      <c r="HB17" s="31"/>
-      <c r="HC17" s="31"/>
-      <c r="HD17" s="31"/>
-      <c r="HE17" s="31"/>
-      <c r="HF17" s="31"/>
-      <c r="HG17" s="31"/>
-      <c r="HH17" s="31"/>
-      <c r="HI17" s="31"/>
-      <c r="HJ17" s="31"/>
-      <c r="HK17" s="31"/>
-      <c r="HL17" s="31"/>
-      <c r="HM17" s="31"/>
-      <c r="HN17" s="31"/>
-      <c r="HO17" s="31"/>
-      <c r="HP17" s="31"/>
-      <c r="HQ17" s="31"/>
-      <c r="HR17" s="31"/>
-      <c r="HS17" s="31"/>
-      <c r="HT17" s="31"/>
-      <c r="HU17" s="31"/>
+      <c r="H17" s="28"/>
+      <c r="BQ17" s="29"/>
+      <c r="BS17" s="29"/>
+      <c r="BU17" s="29"/>
+      <c r="BW17" s="29"/>
+      <c r="BY17" s="29"/>
+      <c r="CA17" s="29"/>
+      <c r="CC17" s="29"/>
+      <c r="CE17" s="29"/>
+      <c r="CG17" s="29"/>
+      <c r="CI17" s="29"/>
+      <c r="CK17" s="29"/>
+      <c r="CL17" s="29"/>
+      <c r="CM17" s="29"/>
+      <c r="CN17" s="29"/>
+      <c r="CO17" s="29"/>
+      <c r="CP17" s="29"/>
+      <c r="CQ17" s="29"/>
+      <c r="CR17" s="29"/>
+      <c r="CS17" s="29"/>
+      <c r="CT17" s="29"/>
+      <c r="CU17" s="29"/>
+      <c r="CV17" s="29"/>
+      <c r="CW17" s="29"/>
+      <c r="CX17" s="29"/>
+      <c r="CY17" s="29"/>
+      <c r="CZ17" s="29"/>
+      <c r="DA17" s="29"/>
+      <c r="DB17" s="29"/>
+      <c r="DC17" s="29"/>
+      <c r="DD17" s="29"/>
+      <c r="DE17" s="29"/>
+      <c r="DF17" s="29"/>
+      <c r="DG17" s="29"/>
+      <c r="DH17" s="29"/>
+      <c r="DI17" s="29"/>
+      <c r="DJ17" s="29"/>
+      <c r="DK17" s="29"/>
+      <c r="DL17" s="29"/>
+      <c r="DM17" s="29"/>
+      <c r="DN17" s="29"/>
+      <c r="DO17" s="29"/>
+      <c r="DP17" s="29"/>
+      <c r="DQ17" s="29"/>
+      <c r="DR17" s="29"/>
+      <c r="DS17" s="29"/>
+      <c r="DT17" s="29"/>
+      <c r="DU17" s="29"/>
+      <c r="DV17" s="29"/>
+      <c r="DW17" s="29"/>
+      <c r="DX17" s="29"/>
+      <c r="DY17" s="29"/>
+      <c r="DZ17" s="29"/>
+      <c r="EA17" s="29"/>
+      <c r="EB17" s="29"/>
+      <c r="EC17" s="29"/>
+      <c r="ED17" s="29"/>
+      <c r="EE17" s="29"/>
+      <c r="EF17" s="29"/>
+      <c r="EG17" s="29"/>
+      <c r="EH17" s="29"/>
+      <c r="EI17" s="29"/>
+      <c r="EJ17" s="29"/>
+      <c r="EK17" s="29"/>
+      <c r="EL17" s="29"/>
+      <c r="EM17" s="29"/>
+      <c r="EN17" s="29"/>
+      <c r="EO17" s="29"/>
+      <c r="EP17" s="29"/>
+      <c r="EQ17" s="29"/>
+      <c r="ER17" s="29"/>
+      <c r="ES17" s="29"/>
+      <c r="ET17" s="29"/>
+      <c r="EU17" s="29"/>
+      <c r="EV17" s="29"/>
+      <c r="EW17" s="29"/>
+      <c r="EX17" s="29"/>
+      <c r="EY17" s="29"/>
+      <c r="EZ17" s="29"/>
+      <c r="FA17" s="29"/>
+      <c r="FB17" s="29"/>
+      <c r="FC17" s="29"/>
+      <c r="FD17" s="29"/>
+      <c r="FE17" s="29"/>
+      <c r="FF17" s="29"/>
+      <c r="FG17" s="29"/>
+      <c r="FH17" s="29"/>
+      <c r="FI17" s="29"/>
+      <c r="FJ17" s="29"/>
+      <c r="FK17" s="29"/>
+      <c r="FL17" s="29"/>
+      <c r="FM17" s="29"/>
+      <c r="FN17" s="29"/>
+      <c r="FO17" s="29"/>
+      <c r="FP17" s="29"/>
+      <c r="FQ17" s="29"/>
+      <c r="FR17" s="29"/>
+      <c r="FS17" s="29"/>
+      <c r="FT17" s="29"/>
+      <c r="FU17" s="29"/>
+      <c r="FV17" s="29"/>
+      <c r="FW17" s="29"/>
+      <c r="FX17" s="29"/>
+      <c r="FY17" s="29"/>
+      <c r="FZ17" s="29"/>
+      <c r="GA17" s="29"/>
+      <c r="GB17" s="29"/>
+      <c r="GC17" s="29"/>
+      <c r="GD17" s="29"/>
+      <c r="GE17" s="29"/>
+      <c r="GF17" s="29"/>
+      <c r="GG17" s="29"/>
+      <c r="GH17" s="29"/>
+      <c r="GI17" s="29"/>
+      <c r="GJ17" s="29"/>
+      <c r="GK17" s="29"/>
+      <c r="GL17" s="29"/>
+      <c r="GM17" s="29"/>
+      <c r="GN17" s="29"/>
+      <c r="GO17" s="29"/>
+      <c r="GP17" s="29"/>
+      <c r="GQ17" s="29"/>
+      <c r="GR17" s="29"/>
+      <c r="GS17" s="29"/>
+      <c r="GT17" s="29"/>
+      <c r="GU17" s="29"/>
+      <c r="GV17" s="29"/>
+      <c r="GW17" s="29"/>
+      <c r="GX17" s="29"/>
+      <c r="GY17" s="29"/>
+      <c r="GZ17" s="29"/>
+      <c r="HA17" s="29"/>
+      <c r="HB17" s="29"/>
+      <c r="HC17" s="29"/>
+      <c r="HD17" s="29"/>
+      <c r="HE17" s="29"/>
+      <c r="HF17" s="29"/>
+      <c r="HG17" s="29"/>
+      <c r="HH17" s="29"/>
+      <c r="HI17" s="29"/>
+      <c r="HJ17" s="29"/>
+      <c r="HK17" s="29"/>
+      <c r="HL17" s="29"/>
+      <c r="HM17" s="29"/>
+      <c r="HN17" s="29"/>
+      <c r="HO17" s="29"/>
+      <c r="HP17" s="29"/>
+      <c r="HQ17" s="29"/>
+      <c r="HR17" s="29"/>
+      <c r="HS17" s="29"/>
+      <c r="HT17" s="29"/>
+      <c r="HU17" s="29"/>
     </row>
-    <row r="18" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>5</v>
       </c>
@@ -5970,160 +6105,160 @@
       <c r="G18" s="7">
         <v>0</v>
       </c>
-      <c r="H18" s="30"/>
-      <c r="BQ18" s="31"/>
-      <c r="BS18" s="31"/>
-      <c r="BU18" s="31"/>
-      <c r="BW18" s="31"/>
-      <c r="BY18" s="31"/>
-      <c r="CA18" s="31"/>
-      <c r="CC18" s="31"/>
-      <c r="CE18" s="31"/>
-      <c r="CG18" s="31"/>
-      <c r="CI18" s="31"/>
-      <c r="CK18" s="31"/>
-      <c r="CL18" s="31"/>
-      <c r="CM18" s="31"/>
-      <c r="CN18" s="31"/>
-      <c r="CO18" s="31"/>
-      <c r="CP18" s="31"/>
-      <c r="CQ18" s="31"/>
-      <c r="CR18" s="31"/>
-      <c r="CS18" s="31"/>
-      <c r="CT18" s="31"/>
-      <c r="CU18" s="31"/>
-      <c r="CV18" s="31"/>
-      <c r="CW18" s="31"/>
-      <c r="CX18" s="31"/>
-      <c r="CY18" s="31"/>
-      <c r="CZ18" s="31"/>
-      <c r="DA18" s="31"/>
-      <c r="DB18" s="31"/>
-      <c r="DC18" s="31"/>
-      <c r="DD18" s="31"/>
-      <c r="DE18" s="31"/>
-      <c r="DF18" s="31"/>
-      <c r="DG18" s="31"/>
-      <c r="DH18" s="31"/>
-      <c r="DI18" s="31"/>
-      <c r="DJ18" s="31"/>
-      <c r="DK18" s="31"/>
-      <c r="DL18" s="31"/>
-      <c r="DM18" s="31"/>
-      <c r="DN18" s="31"/>
-      <c r="DO18" s="31"/>
-      <c r="DP18" s="31"/>
-      <c r="DQ18" s="31"/>
-      <c r="DR18" s="31"/>
-      <c r="DS18" s="31"/>
-      <c r="DT18" s="31"/>
-      <c r="DU18" s="31"/>
-      <c r="DV18" s="31"/>
-      <c r="DW18" s="31"/>
-      <c r="DX18" s="31"/>
-      <c r="DY18" s="31"/>
-      <c r="DZ18" s="31"/>
-      <c r="EA18" s="31"/>
-      <c r="EB18" s="31"/>
-      <c r="EC18" s="31"/>
-      <c r="ED18" s="31"/>
-      <c r="EE18" s="31"/>
-      <c r="EF18" s="31"/>
-      <c r="EG18" s="31"/>
-      <c r="EH18" s="31"/>
-      <c r="EI18" s="31"/>
-      <c r="EJ18" s="31"/>
-      <c r="EK18" s="31"/>
-      <c r="EL18" s="31"/>
-      <c r="EM18" s="31"/>
-      <c r="EN18" s="31"/>
-      <c r="EO18" s="31"/>
-      <c r="EP18" s="31"/>
-      <c r="EQ18" s="31"/>
-      <c r="ER18" s="31"/>
-      <c r="ES18" s="31"/>
-      <c r="ET18" s="31"/>
-      <c r="EU18" s="31"/>
-      <c r="EV18" s="31"/>
-      <c r="EW18" s="31"/>
-      <c r="EX18" s="31"/>
-      <c r="EY18" s="31"/>
-      <c r="EZ18" s="31"/>
-      <c r="FA18" s="31"/>
-      <c r="FB18" s="31"/>
-      <c r="FC18" s="31"/>
-      <c r="FD18" s="31"/>
-      <c r="FE18" s="31"/>
-      <c r="FF18" s="31"/>
-      <c r="FG18" s="31"/>
-      <c r="FH18" s="31"/>
-      <c r="FI18" s="31"/>
-      <c r="FJ18" s="31"/>
-      <c r="FK18" s="31"/>
-      <c r="FL18" s="31"/>
-      <c r="FM18" s="31"/>
-      <c r="FN18" s="31"/>
-      <c r="FO18" s="31"/>
-      <c r="FP18" s="31"/>
-      <c r="FQ18" s="31"/>
-      <c r="FR18" s="31"/>
-      <c r="FS18" s="31"/>
-      <c r="FT18" s="31"/>
-      <c r="FU18" s="31"/>
-      <c r="FV18" s="31"/>
-      <c r="FW18" s="31"/>
-      <c r="FX18" s="31"/>
-      <c r="FY18" s="31"/>
-      <c r="FZ18" s="31"/>
-      <c r="GA18" s="31"/>
-      <c r="GB18" s="31"/>
-      <c r="GC18" s="31"/>
-      <c r="GD18" s="31"/>
-      <c r="GE18" s="31"/>
-      <c r="GF18" s="31"/>
-      <c r="GG18" s="31"/>
-      <c r="GH18" s="31"/>
-      <c r="GI18" s="31"/>
-      <c r="GJ18" s="31"/>
-      <c r="GK18" s="31"/>
-      <c r="GL18" s="31"/>
-      <c r="GM18" s="31"/>
-      <c r="GN18" s="31"/>
-      <c r="GO18" s="31"/>
-      <c r="GP18" s="31"/>
-      <c r="GQ18" s="31"/>
-      <c r="GR18" s="31"/>
-      <c r="GS18" s="31"/>
-      <c r="GT18" s="31"/>
-      <c r="GU18" s="31"/>
-      <c r="GV18" s="31"/>
-      <c r="GW18" s="31"/>
-      <c r="GX18" s="31"/>
-      <c r="GY18" s="31"/>
-      <c r="GZ18" s="31"/>
-      <c r="HA18" s="31"/>
-      <c r="HB18" s="31"/>
-      <c r="HC18" s="31"/>
-      <c r="HD18" s="31"/>
-      <c r="HE18" s="31"/>
-      <c r="HF18" s="31"/>
-      <c r="HG18" s="31"/>
-      <c r="HH18" s="31"/>
-      <c r="HI18" s="31"/>
-      <c r="HJ18" s="31"/>
-      <c r="HK18" s="31"/>
-      <c r="HL18" s="31"/>
-      <c r="HM18" s="31"/>
-      <c r="HN18" s="31"/>
-      <c r="HO18" s="31"/>
-      <c r="HP18" s="31"/>
-      <c r="HQ18" s="31"/>
-      <c r="HR18" s="31"/>
-      <c r="HS18" s="31"/>
-      <c r="HT18" s="31"/>
-      <c r="HU18" s="31"/>
+      <c r="H18" s="28"/>
+      <c r="BQ18" s="29"/>
+      <c r="BS18" s="29"/>
+      <c r="BU18" s="29"/>
+      <c r="BW18" s="29"/>
+      <c r="BY18" s="29"/>
+      <c r="CA18" s="29"/>
+      <c r="CC18" s="29"/>
+      <c r="CE18" s="29"/>
+      <c r="CG18" s="29"/>
+      <c r="CI18" s="29"/>
+      <c r="CK18" s="29"/>
+      <c r="CL18" s="29"/>
+      <c r="CM18" s="29"/>
+      <c r="CN18" s="29"/>
+      <c r="CO18" s="29"/>
+      <c r="CP18" s="29"/>
+      <c r="CQ18" s="29"/>
+      <c r="CR18" s="29"/>
+      <c r="CS18" s="29"/>
+      <c r="CT18" s="29"/>
+      <c r="CU18" s="29"/>
+      <c r="CV18" s="29"/>
+      <c r="CW18" s="29"/>
+      <c r="CX18" s="29"/>
+      <c r="CY18" s="29"/>
+      <c r="CZ18" s="29"/>
+      <c r="DA18" s="29"/>
+      <c r="DB18" s="29"/>
+      <c r="DC18" s="29"/>
+      <c r="DD18" s="29"/>
+      <c r="DE18" s="29"/>
+      <c r="DF18" s="29"/>
+      <c r="DG18" s="29"/>
+      <c r="DH18" s="29"/>
+      <c r="DI18" s="29"/>
+      <c r="DJ18" s="29"/>
+      <c r="DK18" s="29"/>
+      <c r="DL18" s="29"/>
+      <c r="DM18" s="29"/>
+      <c r="DN18" s="29"/>
+      <c r="DO18" s="29"/>
+      <c r="DP18" s="29"/>
+      <c r="DQ18" s="29"/>
+      <c r="DR18" s="29"/>
+      <c r="DS18" s="29"/>
+      <c r="DT18" s="29"/>
+      <c r="DU18" s="29"/>
+      <c r="DV18" s="29"/>
+      <c r="DW18" s="29"/>
+      <c r="DX18" s="29"/>
+      <c r="DY18" s="29"/>
+      <c r="DZ18" s="29"/>
+      <c r="EA18" s="29"/>
+      <c r="EB18" s="29"/>
+      <c r="EC18" s="29"/>
+      <c r="ED18" s="29"/>
+      <c r="EE18" s="29"/>
+      <c r="EF18" s="29"/>
+      <c r="EG18" s="29"/>
+      <c r="EH18" s="29"/>
+      <c r="EI18" s="29"/>
+      <c r="EJ18" s="29"/>
+      <c r="EK18" s="29"/>
+      <c r="EL18" s="29"/>
+      <c r="EM18" s="29"/>
+      <c r="EN18" s="29"/>
+      <c r="EO18" s="29"/>
+      <c r="EP18" s="29"/>
+      <c r="EQ18" s="29"/>
+      <c r="ER18" s="29"/>
+      <c r="ES18" s="29"/>
+      <c r="ET18" s="29"/>
+      <c r="EU18" s="29"/>
+      <c r="EV18" s="29"/>
+      <c r="EW18" s="29"/>
+      <c r="EX18" s="29"/>
+      <c r="EY18" s="29"/>
+      <c r="EZ18" s="29"/>
+      <c r="FA18" s="29"/>
+      <c r="FB18" s="29"/>
+      <c r="FC18" s="29"/>
+      <c r="FD18" s="29"/>
+      <c r="FE18" s="29"/>
+      <c r="FF18" s="29"/>
+      <c r="FG18" s="29"/>
+      <c r="FH18" s="29"/>
+      <c r="FI18" s="29"/>
+      <c r="FJ18" s="29"/>
+      <c r="FK18" s="29"/>
+      <c r="FL18" s="29"/>
+      <c r="FM18" s="29"/>
+      <c r="FN18" s="29"/>
+      <c r="FO18" s="29"/>
+      <c r="FP18" s="29"/>
+      <c r="FQ18" s="29"/>
+      <c r="FR18" s="29"/>
+      <c r="FS18" s="29"/>
+      <c r="FT18" s="29"/>
+      <c r="FU18" s="29"/>
+      <c r="FV18" s="29"/>
+      <c r="FW18" s="29"/>
+      <c r="FX18" s="29"/>
+      <c r="FY18" s="29"/>
+      <c r="FZ18" s="29"/>
+      <c r="GA18" s="29"/>
+      <c r="GB18" s="29"/>
+      <c r="GC18" s="29"/>
+      <c r="GD18" s="29"/>
+      <c r="GE18" s="29"/>
+      <c r="GF18" s="29"/>
+      <c r="GG18" s="29"/>
+      <c r="GH18" s="29"/>
+      <c r="GI18" s="29"/>
+      <c r="GJ18" s="29"/>
+      <c r="GK18" s="29"/>
+      <c r="GL18" s="29"/>
+      <c r="GM18" s="29"/>
+      <c r="GN18" s="29"/>
+      <c r="GO18" s="29"/>
+      <c r="GP18" s="29"/>
+      <c r="GQ18" s="29"/>
+      <c r="GR18" s="29"/>
+      <c r="GS18" s="29"/>
+      <c r="GT18" s="29"/>
+      <c r="GU18" s="29"/>
+      <c r="GV18" s="29"/>
+      <c r="GW18" s="29"/>
+      <c r="GX18" s="29"/>
+      <c r="GY18" s="29"/>
+      <c r="GZ18" s="29"/>
+      <c r="HA18" s="29"/>
+      <c r="HB18" s="29"/>
+      <c r="HC18" s="29"/>
+      <c r="HD18" s="29"/>
+      <c r="HE18" s="29"/>
+      <c r="HF18" s="29"/>
+      <c r="HG18" s="29"/>
+      <c r="HH18" s="29"/>
+      <c r="HI18" s="29"/>
+      <c r="HJ18" s="29"/>
+      <c r="HK18" s="29"/>
+      <c r="HL18" s="29"/>
+      <c r="HM18" s="29"/>
+      <c r="HN18" s="29"/>
+      <c r="HO18" s="29"/>
+      <c r="HP18" s="29"/>
+      <c r="HQ18" s="29"/>
+      <c r="HR18" s="29"/>
+      <c r="HS18" s="29"/>
+      <c r="HT18" s="29"/>
+      <c r="HU18" s="29"/>
     </row>
-    <row r="19" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
@@ -6142,160 +6277,160 @@
       <c r="G19" s="7">
         <v>0</v>
       </c>
-      <c r="H19" s="30"/>
-      <c r="BQ19" s="31"/>
-      <c r="BS19" s="31"/>
-      <c r="BU19" s="31"/>
-      <c r="BW19" s="31"/>
-      <c r="BY19" s="31"/>
-      <c r="CA19" s="31"/>
-      <c r="CC19" s="31"/>
-      <c r="CE19" s="31"/>
-      <c r="CG19" s="31"/>
-      <c r="CI19" s="31"/>
-      <c r="CK19" s="31"/>
-      <c r="CL19" s="31"/>
-      <c r="CM19" s="31"/>
-      <c r="CN19" s="31"/>
-      <c r="CO19" s="31"/>
-      <c r="CP19" s="31"/>
-      <c r="CQ19" s="31"/>
-      <c r="CR19" s="31"/>
-      <c r="CS19" s="31"/>
-      <c r="CT19" s="31"/>
-      <c r="CU19" s="31"/>
-      <c r="CV19" s="31"/>
-      <c r="CW19" s="31"/>
-      <c r="CX19" s="31"/>
-      <c r="CY19" s="31"/>
-      <c r="CZ19" s="31"/>
-      <c r="DA19" s="31"/>
-      <c r="DB19" s="31"/>
-      <c r="DC19" s="31"/>
-      <c r="DD19" s="31"/>
-      <c r="DE19" s="31"/>
-      <c r="DF19" s="31"/>
-      <c r="DG19" s="31"/>
-      <c r="DH19" s="31"/>
-      <c r="DI19" s="31"/>
-      <c r="DJ19" s="31"/>
-      <c r="DK19" s="31"/>
-      <c r="DL19" s="31"/>
-      <c r="DM19" s="31"/>
-      <c r="DN19" s="31"/>
-      <c r="DO19" s="31"/>
-      <c r="DP19" s="31"/>
-      <c r="DQ19" s="31"/>
-      <c r="DR19" s="31"/>
-      <c r="DS19" s="31"/>
-      <c r="DT19" s="31"/>
-      <c r="DU19" s="31"/>
-      <c r="DV19" s="31"/>
-      <c r="DW19" s="31"/>
-      <c r="DX19" s="31"/>
-      <c r="DY19" s="31"/>
-      <c r="DZ19" s="31"/>
-      <c r="EA19" s="31"/>
-      <c r="EB19" s="31"/>
-      <c r="EC19" s="31"/>
-      <c r="ED19" s="31"/>
-      <c r="EE19" s="31"/>
-      <c r="EF19" s="31"/>
-      <c r="EG19" s="31"/>
-      <c r="EH19" s="31"/>
-      <c r="EI19" s="31"/>
-      <c r="EJ19" s="31"/>
-      <c r="EK19" s="31"/>
-      <c r="EL19" s="31"/>
-      <c r="EM19" s="31"/>
-      <c r="EN19" s="31"/>
-      <c r="EO19" s="31"/>
-      <c r="EP19" s="31"/>
-      <c r="EQ19" s="31"/>
-      <c r="ER19" s="31"/>
-      <c r="ES19" s="31"/>
-      <c r="ET19" s="31"/>
-      <c r="EU19" s="31"/>
-      <c r="EV19" s="31"/>
-      <c r="EW19" s="31"/>
-      <c r="EX19" s="31"/>
-      <c r="EY19" s="31"/>
-      <c r="EZ19" s="31"/>
-      <c r="FA19" s="31"/>
-      <c r="FB19" s="31"/>
-      <c r="FC19" s="31"/>
-      <c r="FD19" s="31"/>
-      <c r="FE19" s="31"/>
-      <c r="FF19" s="31"/>
-      <c r="FG19" s="31"/>
-      <c r="FH19" s="31"/>
-      <c r="FI19" s="31"/>
-      <c r="FJ19" s="31"/>
-      <c r="FK19" s="31"/>
-      <c r="FL19" s="31"/>
-      <c r="FM19" s="31"/>
-      <c r="FN19" s="31"/>
-      <c r="FO19" s="31"/>
-      <c r="FP19" s="31"/>
-      <c r="FQ19" s="31"/>
-      <c r="FR19" s="31"/>
-      <c r="FS19" s="31"/>
-      <c r="FT19" s="31"/>
-      <c r="FU19" s="31"/>
-      <c r="FV19" s="31"/>
-      <c r="FW19" s="31"/>
-      <c r="FX19" s="31"/>
-      <c r="FY19" s="31"/>
-      <c r="FZ19" s="31"/>
-      <c r="GA19" s="31"/>
-      <c r="GB19" s="31"/>
-      <c r="GC19" s="31"/>
-      <c r="GD19" s="31"/>
-      <c r="GE19" s="31"/>
-      <c r="GF19" s="31"/>
-      <c r="GG19" s="31"/>
-      <c r="GH19" s="31"/>
-      <c r="GI19" s="31"/>
-      <c r="GJ19" s="31"/>
-      <c r="GK19" s="31"/>
-      <c r="GL19" s="31"/>
-      <c r="GM19" s="31"/>
-      <c r="GN19" s="31"/>
-      <c r="GO19" s="31"/>
-      <c r="GP19" s="31"/>
-      <c r="GQ19" s="31"/>
-      <c r="GR19" s="31"/>
-      <c r="GS19" s="31"/>
-      <c r="GT19" s="31"/>
-      <c r="GU19" s="31"/>
-      <c r="GV19" s="31"/>
-      <c r="GW19" s="31"/>
-      <c r="GX19" s="31"/>
-      <c r="GY19" s="31"/>
-      <c r="GZ19" s="31"/>
-      <c r="HA19" s="31"/>
-      <c r="HB19" s="31"/>
-      <c r="HC19" s="31"/>
-      <c r="HD19" s="31"/>
-      <c r="HE19" s="31"/>
-      <c r="HF19" s="31"/>
-      <c r="HG19" s="31"/>
-      <c r="HH19" s="31"/>
-      <c r="HI19" s="31"/>
-      <c r="HJ19" s="31"/>
-      <c r="HK19" s="31"/>
-      <c r="HL19" s="31"/>
-      <c r="HM19" s="31"/>
-      <c r="HN19" s="31"/>
-      <c r="HO19" s="31"/>
-      <c r="HP19" s="31"/>
-      <c r="HQ19" s="31"/>
-      <c r="HR19" s="31"/>
-      <c r="HS19" s="31"/>
-      <c r="HT19" s="31"/>
-      <c r="HU19" s="31"/>
+      <c r="H19" s="28"/>
+      <c r="BQ19" s="29"/>
+      <c r="BS19" s="29"/>
+      <c r="BU19" s="29"/>
+      <c r="BW19" s="29"/>
+      <c r="BY19" s="29"/>
+      <c r="CA19" s="29"/>
+      <c r="CC19" s="29"/>
+      <c r="CE19" s="29"/>
+      <c r="CG19" s="29"/>
+      <c r="CI19" s="29"/>
+      <c r="CK19" s="29"/>
+      <c r="CL19" s="29"/>
+      <c r="CM19" s="29"/>
+      <c r="CN19" s="29"/>
+      <c r="CO19" s="29"/>
+      <c r="CP19" s="29"/>
+      <c r="CQ19" s="29"/>
+      <c r="CR19" s="29"/>
+      <c r="CS19" s="29"/>
+      <c r="CT19" s="29"/>
+      <c r="CU19" s="29"/>
+      <c r="CV19" s="29"/>
+      <c r="CW19" s="29"/>
+      <c r="CX19" s="29"/>
+      <c r="CY19" s="29"/>
+      <c r="CZ19" s="29"/>
+      <c r="DA19" s="29"/>
+      <c r="DB19" s="29"/>
+      <c r="DC19" s="29"/>
+      <c r="DD19" s="29"/>
+      <c r="DE19" s="29"/>
+      <c r="DF19" s="29"/>
+      <c r="DG19" s="29"/>
+      <c r="DH19" s="29"/>
+      <c r="DI19" s="29"/>
+      <c r="DJ19" s="29"/>
+      <c r="DK19" s="29"/>
+      <c r="DL19" s="29"/>
+      <c r="DM19" s="29"/>
+      <c r="DN19" s="29"/>
+      <c r="DO19" s="29"/>
+      <c r="DP19" s="29"/>
+      <c r="DQ19" s="29"/>
+      <c r="DR19" s="29"/>
+      <c r="DS19" s="29"/>
+      <c r="DT19" s="29"/>
+      <c r="DU19" s="29"/>
+      <c r="DV19" s="29"/>
+      <c r="DW19" s="29"/>
+      <c r="DX19" s="29"/>
+      <c r="DY19" s="29"/>
+      <c r="DZ19" s="29"/>
+      <c r="EA19" s="29"/>
+      <c r="EB19" s="29"/>
+      <c r="EC19" s="29"/>
+      <c r="ED19" s="29"/>
+      <c r="EE19" s="29"/>
+      <c r="EF19" s="29"/>
+      <c r="EG19" s="29"/>
+      <c r="EH19" s="29"/>
+      <c r="EI19" s="29"/>
+      <c r="EJ19" s="29"/>
+      <c r="EK19" s="29"/>
+      <c r="EL19" s="29"/>
+      <c r="EM19" s="29"/>
+      <c r="EN19" s="29"/>
+      <c r="EO19" s="29"/>
+      <c r="EP19" s="29"/>
+      <c r="EQ19" s="29"/>
+      <c r="ER19" s="29"/>
+      <c r="ES19" s="29"/>
+      <c r="ET19" s="29"/>
+      <c r="EU19" s="29"/>
+      <c r="EV19" s="29"/>
+      <c r="EW19" s="29"/>
+      <c r="EX19" s="29"/>
+      <c r="EY19" s="29"/>
+      <c r="EZ19" s="29"/>
+      <c r="FA19" s="29"/>
+      <c r="FB19" s="29"/>
+      <c r="FC19" s="29"/>
+      <c r="FD19" s="29"/>
+      <c r="FE19" s="29"/>
+      <c r="FF19" s="29"/>
+      <c r="FG19" s="29"/>
+      <c r="FH19" s="29"/>
+      <c r="FI19" s="29"/>
+      <c r="FJ19" s="29"/>
+      <c r="FK19" s="29"/>
+      <c r="FL19" s="29"/>
+      <c r="FM19" s="29"/>
+      <c r="FN19" s="29"/>
+      <c r="FO19" s="29"/>
+      <c r="FP19" s="29"/>
+      <c r="FQ19" s="29"/>
+      <c r="FR19" s="29"/>
+      <c r="FS19" s="29"/>
+      <c r="FT19" s="29"/>
+      <c r="FU19" s="29"/>
+      <c r="FV19" s="29"/>
+      <c r="FW19" s="29"/>
+      <c r="FX19" s="29"/>
+      <c r="FY19" s="29"/>
+      <c r="FZ19" s="29"/>
+      <c r="GA19" s="29"/>
+      <c r="GB19" s="29"/>
+      <c r="GC19" s="29"/>
+      <c r="GD19" s="29"/>
+      <c r="GE19" s="29"/>
+      <c r="GF19" s="29"/>
+      <c r="GG19" s="29"/>
+      <c r="GH19" s="29"/>
+      <c r="GI19" s="29"/>
+      <c r="GJ19" s="29"/>
+      <c r="GK19" s="29"/>
+      <c r="GL19" s="29"/>
+      <c r="GM19" s="29"/>
+      <c r="GN19" s="29"/>
+      <c r="GO19" s="29"/>
+      <c r="GP19" s="29"/>
+      <c r="GQ19" s="29"/>
+      <c r="GR19" s="29"/>
+      <c r="GS19" s="29"/>
+      <c r="GT19" s="29"/>
+      <c r="GU19" s="29"/>
+      <c r="GV19" s="29"/>
+      <c r="GW19" s="29"/>
+      <c r="GX19" s="29"/>
+      <c r="GY19" s="29"/>
+      <c r="GZ19" s="29"/>
+      <c r="HA19" s="29"/>
+      <c r="HB19" s="29"/>
+      <c r="HC19" s="29"/>
+      <c r="HD19" s="29"/>
+      <c r="HE19" s="29"/>
+      <c r="HF19" s="29"/>
+      <c r="HG19" s="29"/>
+      <c r="HH19" s="29"/>
+      <c r="HI19" s="29"/>
+      <c r="HJ19" s="29"/>
+      <c r="HK19" s="29"/>
+      <c r="HL19" s="29"/>
+      <c r="HM19" s="29"/>
+      <c r="HN19" s="29"/>
+      <c r="HO19" s="29"/>
+      <c r="HP19" s="29"/>
+      <c r="HQ19" s="29"/>
+      <c r="HR19" s="29"/>
+      <c r="HS19" s="29"/>
+      <c r="HT19" s="29"/>
+      <c r="HU19" s="29"/>
     </row>
-    <row r="20" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
@@ -6314,160 +6449,160 @@
       <c r="G20" s="7">
         <v>0</v>
       </c>
-      <c r="H20" s="30"/>
-      <c r="BQ20" s="31"/>
-      <c r="BS20" s="31"/>
-      <c r="BU20" s="31"/>
-      <c r="BW20" s="31"/>
-      <c r="BY20" s="31"/>
-      <c r="CA20" s="31"/>
-      <c r="CC20" s="31"/>
-      <c r="CE20" s="31"/>
-      <c r="CG20" s="31"/>
-      <c r="CI20" s="31"/>
-      <c r="CK20" s="31"/>
-      <c r="CL20" s="31"/>
-      <c r="CM20" s="31"/>
-      <c r="CN20" s="31"/>
-      <c r="CO20" s="31"/>
-      <c r="CP20" s="31"/>
-      <c r="CQ20" s="31"/>
-      <c r="CR20" s="31"/>
-      <c r="CS20" s="31"/>
-      <c r="CT20" s="31"/>
-      <c r="CU20" s="31"/>
-      <c r="CV20" s="31"/>
-      <c r="CW20" s="31"/>
-      <c r="CX20" s="31"/>
-      <c r="CY20" s="31"/>
-      <c r="CZ20" s="31"/>
-      <c r="DA20" s="31"/>
-      <c r="DB20" s="31"/>
-      <c r="DC20" s="31"/>
-      <c r="DD20" s="31"/>
-      <c r="DE20" s="31"/>
-      <c r="DF20" s="31"/>
-      <c r="DG20" s="31"/>
-      <c r="DH20" s="31"/>
-      <c r="DI20" s="31"/>
-      <c r="DJ20" s="31"/>
-      <c r="DK20" s="31"/>
-      <c r="DL20" s="31"/>
-      <c r="DM20" s="31"/>
-      <c r="DN20" s="31"/>
-      <c r="DO20" s="31"/>
-      <c r="DP20" s="31"/>
-      <c r="DQ20" s="31"/>
-      <c r="DR20" s="31"/>
-      <c r="DS20" s="31"/>
-      <c r="DT20" s="31"/>
-      <c r="DU20" s="31"/>
-      <c r="DV20" s="31"/>
-      <c r="DW20" s="31"/>
-      <c r="DX20" s="31"/>
-      <c r="DY20" s="31"/>
-      <c r="DZ20" s="31"/>
-      <c r="EA20" s="31"/>
-      <c r="EB20" s="31"/>
-      <c r="EC20" s="31"/>
-      <c r="ED20" s="31"/>
-      <c r="EE20" s="31"/>
-      <c r="EF20" s="31"/>
-      <c r="EG20" s="31"/>
-      <c r="EH20" s="31"/>
-      <c r="EI20" s="31"/>
-      <c r="EJ20" s="31"/>
-      <c r="EK20" s="31"/>
-      <c r="EL20" s="31"/>
-      <c r="EM20" s="31"/>
-      <c r="EN20" s="31"/>
-      <c r="EO20" s="31"/>
-      <c r="EP20" s="31"/>
-      <c r="EQ20" s="31"/>
-      <c r="ER20" s="31"/>
-      <c r="ES20" s="31"/>
-      <c r="ET20" s="31"/>
-      <c r="EU20" s="31"/>
-      <c r="EV20" s="31"/>
-      <c r="EW20" s="31"/>
-      <c r="EX20" s="31"/>
-      <c r="EY20" s="31"/>
-      <c r="EZ20" s="31"/>
-      <c r="FA20" s="31"/>
-      <c r="FB20" s="31"/>
-      <c r="FC20" s="31"/>
-      <c r="FD20" s="31"/>
-      <c r="FE20" s="31"/>
-      <c r="FF20" s="31"/>
-      <c r="FG20" s="31"/>
-      <c r="FH20" s="31"/>
-      <c r="FI20" s="31"/>
-      <c r="FJ20" s="31"/>
-      <c r="FK20" s="31"/>
-      <c r="FL20" s="31"/>
-      <c r="FM20" s="31"/>
-      <c r="FN20" s="31"/>
-      <c r="FO20" s="31"/>
-      <c r="FP20" s="31"/>
-      <c r="FQ20" s="31"/>
-      <c r="FR20" s="31"/>
-      <c r="FS20" s="31"/>
-      <c r="FT20" s="31"/>
-      <c r="FU20" s="31"/>
-      <c r="FV20" s="31"/>
-      <c r="FW20" s="31"/>
-      <c r="FX20" s="31"/>
-      <c r="FY20" s="31"/>
-      <c r="FZ20" s="31"/>
-      <c r="GA20" s="31"/>
-      <c r="GB20" s="31"/>
-      <c r="GC20" s="31"/>
-      <c r="GD20" s="31"/>
-      <c r="GE20" s="31"/>
-      <c r="GF20" s="31"/>
-      <c r="GG20" s="31"/>
-      <c r="GH20" s="31"/>
-      <c r="GI20" s="31"/>
-      <c r="GJ20" s="31"/>
-      <c r="GK20" s="31"/>
-      <c r="GL20" s="31"/>
-      <c r="GM20" s="31"/>
-      <c r="GN20" s="31"/>
-      <c r="GO20" s="31"/>
-      <c r="GP20" s="31"/>
-      <c r="GQ20" s="31"/>
-      <c r="GR20" s="31"/>
-      <c r="GS20" s="31"/>
-      <c r="GT20" s="31"/>
-      <c r="GU20" s="31"/>
-      <c r="GV20" s="31"/>
-      <c r="GW20" s="31"/>
-      <c r="GX20" s="31"/>
-      <c r="GY20" s="31"/>
-      <c r="GZ20" s="31"/>
-      <c r="HA20" s="31"/>
-      <c r="HB20" s="31"/>
-      <c r="HC20" s="31"/>
-      <c r="HD20" s="31"/>
-      <c r="HE20" s="31"/>
-      <c r="HF20" s="31"/>
-      <c r="HG20" s="31"/>
-      <c r="HH20" s="31"/>
-      <c r="HI20" s="31"/>
-      <c r="HJ20" s="31"/>
-      <c r="HK20" s="31"/>
-      <c r="HL20" s="31"/>
-      <c r="HM20" s="31"/>
-      <c r="HN20" s="31"/>
-      <c r="HO20" s="31"/>
-      <c r="HP20" s="31"/>
-      <c r="HQ20" s="31"/>
-      <c r="HR20" s="31"/>
-      <c r="HS20" s="31"/>
-      <c r="HT20" s="31"/>
-      <c r="HU20" s="31"/>
+      <c r="H20" s="28"/>
+      <c r="BQ20" s="29"/>
+      <c r="BS20" s="29"/>
+      <c r="BU20" s="29"/>
+      <c r="BW20" s="29"/>
+      <c r="BY20" s="29"/>
+      <c r="CA20" s="29"/>
+      <c r="CC20" s="29"/>
+      <c r="CE20" s="29"/>
+      <c r="CG20" s="29"/>
+      <c r="CI20" s="29"/>
+      <c r="CK20" s="29"/>
+      <c r="CL20" s="29"/>
+      <c r="CM20" s="29"/>
+      <c r="CN20" s="29"/>
+      <c r="CO20" s="29"/>
+      <c r="CP20" s="29"/>
+      <c r="CQ20" s="29"/>
+      <c r="CR20" s="29"/>
+      <c r="CS20" s="29"/>
+      <c r="CT20" s="29"/>
+      <c r="CU20" s="29"/>
+      <c r="CV20" s="29"/>
+      <c r="CW20" s="29"/>
+      <c r="CX20" s="29"/>
+      <c r="CY20" s="29"/>
+      <c r="CZ20" s="29"/>
+      <c r="DA20" s="29"/>
+      <c r="DB20" s="29"/>
+      <c r="DC20" s="29"/>
+      <c r="DD20" s="29"/>
+      <c r="DE20" s="29"/>
+      <c r="DF20" s="29"/>
+      <c r="DG20" s="29"/>
+      <c r="DH20" s="29"/>
+      <c r="DI20" s="29"/>
+      <c r="DJ20" s="29"/>
+      <c r="DK20" s="29"/>
+      <c r="DL20" s="29"/>
+      <c r="DM20" s="29"/>
+      <c r="DN20" s="29"/>
+      <c r="DO20" s="29"/>
+      <c r="DP20" s="29"/>
+      <c r="DQ20" s="29"/>
+      <c r="DR20" s="29"/>
+      <c r="DS20" s="29"/>
+      <c r="DT20" s="29"/>
+      <c r="DU20" s="29"/>
+      <c r="DV20" s="29"/>
+      <c r="DW20" s="29"/>
+      <c r="DX20" s="29"/>
+      <c r="DY20" s="29"/>
+      <c r="DZ20" s="29"/>
+      <c r="EA20" s="29"/>
+      <c r="EB20" s="29"/>
+      <c r="EC20" s="29"/>
+      <c r="ED20" s="29"/>
+      <c r="EE20" s="29"/>
+      <c r="EF20" s="29"/>
+      <c r="EG20" s="29"/>
+      <c r="EH20" s="29"/>
+      <c r="EI20" s="29"/>
+      <c r="EJ20" s="29"/>
+      <c r="EK20" s="29"/>
+      <c r="EL20" s="29"/>
+      <c r="EM20" s="29"/>
+      <c r="EN20" s="29"/>
+      <c r="EO20" s="29"/>
+      <c r="EP20" s="29"/>
+      <c r="EQ20" s="29"/>
+      <c r="ER20" s="29"/>
+      <c r="ES20" s="29"/>
+      <c r="ET20" s="29"/>
+      <c r="EU20" s="29"/>
+      <c r="EV20" s="29"/>
+      <c r="EW20" s="29"/>
+      <c r="EX20" s="29"/>
+      <c r="EY20" s="29"/>
+      <c r="EZ20" s="29"/>
+      <c r="FA20" s="29"/>
+      <c r="FB20" s="29"/>
+      <c r="FC20" s="29"/>
+      <c r="FD20" s="29"/>
+      <c r="FE20" s="29"/>
+      <c r="FF20" s="29"/>
+      <c r="FG20" s="29"/>
+      <c r="FH20" s="29"/>
+      <c r="FI20" s="29"/>
+      <c r="FJ20" s="29"/>
+      <c r="FK20" s="29"/>
+      <c r="FL20" s="29"/>
+      <c r="FM20" s="29"/>
+      <c r="FN20" s="29"/>
+      <c r="FO20" s="29"/>
+      <c r="FP20" s="29"/>
+      <c r="FQ20" s="29"/>
+      <c r="FR20" s="29"/>
+      <c r="FS20" s="29"/>
+      <c r="FT20" s="29"/>
+      <c r="FU20" s="29"/>
+      <c r="FV20" s="29"/>
+      <c r="FW20" s="29"/>
+      <c r="FX20" s="29"/>
+      <c r="FY20" s="29"/>
+      <c r="FZ20" s="29"/>
+      <c r="GA20" s="29"/>
+      <c r="GB20" s="29"/>
+      <c r="GC20" s="29"/>
+      <c r="GD20" s="29"/>
+      <c r="GE20" s="29"/>
+      <c r="GF20" s="29"/>
+      <c r="GG20" s="29"/>
+      <c r="GH20" s="29"/>
+      <c r="GI20" s="29"/>
+      <c r="GJ20" s="29"/>
+      <c r="GK20" s="29"/>
+      <c r="GL20" s="29"/>
+      <c r="GM20" s="29"/>
+      <c r="GN20" s="29"/>
+      <c r="GO20" s="29"/>
+      <c r="GP20" s="29"/>
+      <c r="GQ20" s="29"/>
+      <c r="GR20" s="29"/>
+      <c r="GS20" s="29"/>
+      <c r="GT20" s="29"/>
+      <c r="GU20" s="29"/>
+      <c r="GV20" s="29"/>
+      <c r="GW20" s="29"/>
+      <c r="GX20" s="29"/>
+      <c r="GY20" s="29"/>
+      <c r="GZ20" s="29"/>
+      <c r="HA20" s="29"/>
+      <c r="HB20" s="29"/>
+      <c r="HC20" s="29"/>
+      <c r="HD20" s="29"/>
+      <c r="HE20" s="29"/>
+      <c r="HF20" s="29"/>
+      <c r="HG20" s="29"/>
+      <c r="HH20" s="29"/>
+      <c r="HI20" s="29"/>
+      <c r="HJ20" s="29"/>
+      <c r="HK20" s="29"/>
+      <c r="HL20" s="29"/>
+      <c r="HM20" s="29"/>
+      <c r="HN20" s="29"/>
+      <c r="HO20" s="29"/>
+      <c r="HP20" s="29"/>
+      <c r="HQ20" s="29"/>
+      <c r="HR20" s="29"/>
+      <c r="HS20" s="29"/>
+      <c r="HT20" s="29"/>
+      <c r="HU20" s="29"/>
     </row>
-    <row r="21" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -6486,160 +6621,160 @@
       <c r="G21" s="7">
         <v>0</v>
       </c>
-      <c r="H21" s="30"/>
-      <c r="BQ21" s="31"/>
-      <c r="BS21" s="31"/>
-      <c r="BU21" s="31"/>
-      <c r="BW21" s="31"/>
-      <c r="BY21" s="31"/>
-      <c r="CA21" s="31"/>
-      <c r="CC21" s="31"/>
-      <c r="CE21" s="31"/>
-      <c r="CG21" s="31"/>
-      <c r="CI21" s="31"/>
-      <c r="CK21" s="31"/>
-      <c r="CL21" s="31"/>
-      <c r="CM21" s="31"/>
-      <c r="CN21" s="31"/>
-      <c r="CO21" s="31"/>
-      <c r="CP21" s="31"/>
-      <c r="CQ21" s="31"/>
-      <c r="CR21" s="31"/>
-      <c r="CS21" s="31"/>
-      <c r="CT21" s="31"/>
-      <c r="CU21" s="31"/>
-      <c r="CV21" s="31"/>
-      <c r="CW21" s="31"/>
-      <c r="CX21" s="31"/>
-      <c r="CY21" s="31"/>
-      <c r="CZ21" s="31"/>
-      <c r="DA21" s="31"/>
-      <c r="DB21" s="31"/>
-      <c r="DC21" s="31"/>
-      <c r="DD21" s="31"/>
-      <c r="DE21" s="31"/>
-      <c r="DF21" s="31"/>
-      <c r="DG21" s="31"/>
-      <c r="DH21" s="31"/>
-      <c r="DI21" s="31"/>
-      <c r="DJ21" s="31"/>
-      <c r="DK21" s="31"/>
-      <c r="DL21" s="31"/>
-      <c r="DM21" s="31"/>
-      <c r="DN21" s="31"/>
-      <c r="DO21" s="31"/>
-      <c r="DP21" s="31"/>
-      <c r="DQ21" s="31"/>
-      <c r="DR21" s="31"/>
-      <c r="DS21" s="31"/>
-      <c r="DT21" s="31"/>
-      <c r="DU21" s="31"/>
-      <c r="DV21" s="31"/>
-      <c r="DW21" s="31"/>
-      <c r="DX21" s="31"/>
-      <c r="DY21" s="31"/>
-      <c r="DZ21" s="31"/>
-      <c r="EA21" s="31"/>
-      <c r="EB21" s="31"/>
-      <c r="EC21" s="31"/>
-      <c r="ED21" s="31"/>
-      <c r="EE21" s="31"/>
-      <c r="EF21" s="31"/>
-      <c r="EG21" s="31"/>
-      <c r="EH21" s="31"/>
-      <c r="EI21" s="31"/>
-      <c r="EJ21" s="31"/>
-      <c r="EK21" s="31"/>
-      <c r="EL21" s="31"/>
-      <c r="EM21" s="31"/>
-      <c r="EN21" s="31"/>
-      <c r="EO21" s="31"/>
-      <c r="EP21" s="31"/>
-      <c r="EQ21" s="31"/>
-      <c r="ER21" s="31"/>
-      <c r="ES21" s="31"/>
-      <c r="ET21" s="31"/>
-      <c r="EU21" s="31"/>
-      <c r="EV21" s="31"/>
-      <c r="EW21" s="31"/>
-      <c r="EX21" s="31"/>
-      <c r="EY21" s="31"/>
-      <c r="EZ21" s="31"/>
-      <c r="FA21" s="31"/>
-      <c r="FB21" s="31"/>
-      <c r="FC21" s="31"/>
-      <c r="FD21" s="31"/>
-      <c r="FE21" s="31"/>
-      <c r="FF21" s="31"/>
-      <c r="FG21" s="31"/>
-      <c r="FH21" s="31"/>
-      <c r="FI21" s="31"/>
-      <c r="FJ21" s="31"/>
-      <c r="FK21" s="31"/>
-      <c r="FL21" s="31"/>
-      <c r="FM21" s="31"/>
-      <c r="FN21" s="31"/>
-      <c r="FO21" s="31"/>
-      <c r="FP21" s="31"/>
-      <c r="FQ21" s="31"/>
-      <c r="FR21" s="31"/>
-      <c r="FS21" s="31"/>
-      <c r="FT21" s="31"/>
-      <c r="FU21" s="31"/>
-      <c r="FV21" s="31"/>
-      <c r="FW21" s="31"/>
-      <c r="FX21" s="31"/>
-      <c r="FY21" s="31"/>
-      <c r="FZ21" s="31"/>
-      <c r="GA21" s="31"/>
-      <c r="GB21" s="31"/>
-      <c r="GC21" s="31"/>
-      <c r="GD21" s="31"/>
-      <c r="GE21" s="31"/>
-      <c r="GF21" s="31"/>
-      <c r="GG21" s="31"/>
-      <c r="GH21" s="31"/>
-      <c r="GI21" s="31"/>
-      <c r="GJ21" s="31"/>
-      <c r="GK21" s="31"/>
-      <c r="GL21" s="31"/>
-      <c r="GM21" s="31"/>
-      <c r="GN21" s="31"/>
-      <c r="GO21" s="31"/>
-      <c r="GP21" s="31"/>
-      <c r="GQ21" s="31"/>
-      <c r="GR21" s="31"/>
-      <c r="GS21" s="31"/>
-      <c r="GT21" s="31"/>
-      <c r="GU21" s="31"/>
-      <c r="GV21" s="31"/>
-      <c r="GW21" s="31"/>
-      <c r="GX21" s="31"/>
-      <c r="GY21" s="31"/>
-      <c r="GZ21" s="31"/>
-      <c r="HA21" s="31"/>
-      <c r="HB21" s="31"/>
-      <c r="HC21" s="31"/>
-      <c r="HD21" s="31"/>
-      <c r="HE21" s="31"/>
-      <c r="HF21" s="31"/>
-      <c r="HG21" s="31"/>
-      <c r="HH21" s="31"/>
-      <c r="HI21" s="31"/>
-      <c r="HJ21" s="31"/>
-      <c r="HK21" s="31"/>
-      <c r="HL21" s="31"/>
-      <c r="HM21" s="31"/>
-      <c r="HN21" s="31"/>
-      <c r="HO21" s="31"/>
-      <c r="HP21" s="31"/>
-      <c r="HQ21" s="31"/>
-      <c r="HR21" s="31"/>
-      <c r="HS21" s="31"/>
-      <c r="HT21" s="31"/>
-      <c r="HU21" s="31"/>
+      <c r="H21" s="28"/>
+      <c r="BQ21" s="29"/>
+      <c r="BS21" s="29"/>
+      <c r="BU21" s="29"/>
+      <c r="BW21" s="29"/>
+      <c r="BY21" s="29"/>
+      <c r="CA21" s="29"/>
+      <c r="CC21" s="29"/>
+      <c r="CE21" s="29"/>
+      <c r="CG21" s="29"/>
+      <c r="CI21" s="29"/>
+      <c r="CK21" s="29"/>
+      <c r="CL21" s="29"/>
+      <c r="CM21" s="29"/>
+      <c r="CN21" s="29"/>
+      <c r="CO21" s="29"/>
+      <c r="CP21" s="29"/>
+      <c r="CQ21" s="29"/>
+      <c r="CR21" s="29"/>
+      <c r="CS21" s="29"/>
+      <c r="CT21" s="29"/>
+      <c r="CU21" s="29"/>
+      <c r="CV21" s="29"/>
+      <c r="CW21" s="29"/>
+      <c r="CX21" s="29"/>
+      <c r="CY21" s="29"/>
+      <c r="CZ21" s="29"/>
+      <c r="DA21" s="29"/>
+      <c r="DB21" s="29"/>
+      <c r="DC21" s="29"/>
+      <c r="DD21" s="29"/>
+      <c r="DE21" s="29"/>
+      <c r="DF21" s="29"/>
+      <c r="DG21" s="29"/>
+      <c r="DH21" s="29"/>
+      <c r="DI21" s="29"/>
+      <c r="DJ21" s="29"/>
+      <c r="DK21" s="29"/>
+      <c r="DL21" s="29"/>
+      <c r="DM21" s="29"/>
+      <c r="DN21" s="29"/>
+      <c r="DO21" s="29"/>
+      <c r="DP21" s="29"/>
+      <c r="DQ21" s="29"/>
+      <c r="DR21" s="29"/>
+      <c r="DS21" s="29"/>
+      <c r="DT21" s="29"/>
+      <c r="DU21" s="29"/>
+      <c r="DV21" s="29"/>
+      <c r="DW21" s="29"/>
+      <c r="DX21" s="29"/>
+      <c r="DY21" s="29"/>
+      <c r="DZ21" s="29"/>
+      <c r="EA21" s="29"/>
+      <c r="EB21" s="29"/>
+      <c r="EC21" s="29"/>
+      <c r="ED21" s="29"/>
+      <c r="EE21" s="29"/>
+      <c r="EF21" s="29"/>
+      <c r="EG21" s="29"/>
+      <c r="EH21" s="29"/>
+      <c r="EI21" s="29"/>
+      <c r="EJ21" s="29"/>
+      <c r="EK21" s="29"/>
+      <c r="EL21" s="29"/>
+      <c r="EM21" s="29"/>
+      <c r="EN21" s="29"/>
+      <c r="EO21" s="29"/>
+      <c r="EP21" s="29"/>
+      <c r="EQ21" s="29"/>
+      <c r="ER21" s="29"/>
+      <c r="ES21" s="29"/>
+      <c r="ET21" s="29"/>
+      <c r="EU21" s="29"/>
+      <c r="EV21" s="29"/>
+      <c r="EW21" s="29"/>
+      <c r="EX21" s="29"/>
+      <c r="EY21" s="29"/>
+      <c r="EZ21" s="29"/>
+      <c r="FA21" s="29"/>
+      <c r="FB21" s="29"/>
+      <c r="FC21" s="29"/>
+      <c r="FD21" s="29"/>
+      <c r="FE21" s="29"/>
+      <c r="FF21" s="29"/>
+      <c r="FG21" s="29"/>
+      <c r="FH21" s="29"/>
+      <c r="FI21" s="29"/>
+      <c r="FJ21" s="29"/>
+      <c r="FK21" s="29"/>
+      <c r="FL21" s="29"/>
+      <c r="FM21" s="29"/>
+      <c r="FN21" s="29"/>
+      <c r="FO21" s="29"/>
+      <c r="FP21" s="29"/>
+      <c r="FQ21" s="29"/>
+      <c r="FR21" s="29"/>
+      <c r="FS21" s="29"/>
+      <c r="FT21" s="29"/>
+      <c r="FU21" s="29"/>
+      <c r="FV21" s="29"/>
+      <c r="FW21" s="29"/>
+      <c r="FX21" s="29"/>
+      <c r="FY21" s="29"/>
+      <c r="FZ21" s="29"/>
+      <c r="GA21" s="29"/>
+      <c r="GB21" s="29"/>
+      <c r="GC21" s="29"/>
+      <c r="GD21" s="29"/>
+      <c r="GE21" s="29"/>
+      <c r="GF21" s="29"/>
+      <c r="GG21" s="29"/>
+      <c r="GH21" s="29"/>
+      <c r="GI21" s="29"/>
+      <c r="GJ21" s="29"/>
+      <c r="GK21" s="29"/>
+      <c r="GL21" s="29"/>
+      <c r="GM21" s="29"/>
+      <c r="GN21" s="29"/>
+      <c r="GO21" s="29"/>
+      <c r="GP21" s="29"/>
+      <c r="GQ21" s="29"/>
+      <c r="GR21" s="29"/>
+      <c r="GS21" s="29"/>
+      <c r="GT21" s="29"/>
+      <c r="GU21" s="29"/>
+      <c r="GV21" s="29"/>
+      <c r="GW21" s="29"/>
+      <c r="GX21" s="29"/>
+      <c r="GY21" s="29"/>
+      <c r="GZ21" s="29"/>
+      <c r="HA21" s="29"/>
+      <c r="HB21" s="29"/>
+      <c r="HC21" s="29"/>
+      <c r="HD21" s="29"/>
+      <c r="HE21" s="29"/>
+      <c r="HF21" s="29"/>
+      <c r="HG21" s="29"/>
+      <c r="HH21" s="29"/>
+      <c r="HI21" s="29"/>
+      <c r="HJ21" s="29"/>
+      <c r="HK21" s="29"/>
+      <c r="HL21" s="29"/>
+      <c r="HM21" s="29"/>
+      <c r="HN21" s="29"/>
+      <c r="HO21" s="29"/>
+      <c r="HP21" s="29"/>
+      <c r="HQ21" s="29"/>
+      <c r="HR21" s="29"/>
+      <c r="HS21" s="29"/>
+      <c r="HT21" s="29"/>
+      <c r="HU21" s="29"/>
     </row>
-    <row r="22" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
@@ -6658,160 +6793,160 @@
       <c r="G22" s="7">
         <v>0</v>
       </c>
-      <c r="H22" s="30"/>
-      <c r="BQ22" s="31"/>
-      <c r="BS22" s="31"/>
-      <c r="BU22" s="31"/>
-      <c r="BW22" s="31"/>
-      <c r="BY22" s="31"/>
-      <c r="CA22" s="31"/>
-      <c r="CC22" s="31"/>
-      <c r="CE22" s="31"/>
-      <c r="CG22" s="31"/>
-      <c r="CI22" s="31"/>
-      <c r="CK22" s="31"/>
-      <c r="CL22" s="31"/>
-      <c r="CM22" s="31"/>
-      <c r="CN22" s="31"/>
-      <c r="CO22" s="31"/>
-      <c r="CP22" s="31"/>
-      <c r="CQ22" s="31"/>
-      <c r="CR22" s="31"/>
-      <c r="CS22" s="31"/>
-      <c r="CT22" s="31"/>
-      <c r="CU22" s="31"/>
-      <c r="CV22" s="31"/>
-      <c r="CW22" s="31"/>
-      <c r="CX22" s="31"/>
-      <c r="CY22" s="31"/>
-      <c r="CZ22" s="31"/>
-      <c r="DA22" s="31"/>
-      <c r="DB22" s="31"/>
-      <c r="DC22" s="31"/>
-      <c r="DD22" s="31"/>
-      <c r="DE22" s="31"/>
-      <c r="DF22" s="31"/>
-      <c r="DG22" s="31"/>
-      <c r="DH22" s="31"/>
-      <c r="DI22" s="31"/>
-      <c r="DJ22" s="31"/>
-      <c r="DK22" s="31"/>
-      <c r="DL22" s="31"/>
-      <c r="DM22" s="31"/>
-      <c r="DN22" s="31"/>
-      <c r="DO22" s="31"/>
-      <c r="DP22" s="31"/>
-      <c r="DQ22" s="31"/>
-      <c r="DR22" s="31"/>
-      <c r="DS22" s="31"/>
-      <c r="DT22" s="31"/>
-      <c r="DU22" s="31"/>
-      <c r="DV22" s="31"/>
-      <c r="DW22" s="31"/>
-      <c r="DX22" s="31"/>
-      <c r="DY22" s="31"/>
-      <c r="DZ22" s="31"/>
-      <c r="EA22" s="31"/>
-      <c r="EB22" s="31"/>
-      <c r="EC22" s="31"/>
-      <c r="ED22" s="31"/>
-      <c r="EE22" s="31"/>
-      <c r="EF22" s="31"/>
-      <c r="EG22" s="31"/>
-      <c r="EH22" s="31"/>
-      <c r="EI22" s="31"/>
-      <c r="EJ22" s="31"/>
-      <c r="EK22" s="31"/>
-      <c r="EL22" s="31"/>
-      <c r="EM22" s="31"/>
-      <c r="EN22" s="31"/>
-      <c r="EO22" s="31"/>
-      <c r="EP22" s="31"/>
-      <c r="EQ22" s="31"/>
-      <c r="ER22" s="31"/>
-      <c r="ES22" s="31"/>
-      <c r="ET22" s="31"/>
-      <c r="EU22" s="31"/>
-      <c r="EV22" s="31"/>
-      <c r="EW22" s="31"/>
-      <c r="EX22" s="31"/>
-      <c r="EY22" s="31"/>
-      <c r="EZ22" s="31"/>
-      <c r="FA22" s="31"/>
-      <c r="FB22" s="31"/>
-      <c r="FC22" s="31"/>
-      <c r="FD22" s="31"/>
-      <c r="FE22" s="31"/>
-      <c r="FF22" s="31"/>
-      <c r="FG22" s="31"/>
-      <c r="FH22" s="31"/>
-      <c r="FI22" s="31"/>
-      <c r="FJ22" s="31"/>
-      <c r="FK22" s="31"/>
-      <c r="FL22" s="31"/>
-      <c r="FM22" s="31"/>
-      <c r="FN22" s="31"/>
-      <c r="FO22" s="31"/>
-      <c r="FP22" s="31"/>
-      <c r="FQ22" s="31"/>
-      <c r="FR22" s="31"/>
-      <c r="FS22" s="31"/>
-      <c r="FT22" s="31"/>
-      <c r="FU22" s="31"/>
-      <c r="FV22" s="31"/>
-      <c r="FW22" s="31"/>
-      <c r="FX22" s="31"/>
-      <c r="FY22" s="31"/>
-      <c r="FZ22" s="31"/>
-      <c r="GA22" s="31"/>
-      <c r="GB22" s="31"/>
-      <c r="GC22" s="31"/>
-      <c r="GD22" s="31"/>
-      <c r="GE22" s="31"/>
-      <c r="GF22" s="31"/>
-      <c r="GG22" s="31"/>
-      <c r="GH22" s="31"/>
-      <c r="GI22" s="31"/>
-      <c r="GJ22" s="31"/>
-      <c r="GK22" s="31"/>
-      <c r="GL22" s="31"/>
-      <c r="GM22" s="31"/>
-      <c r="GN22" s="31"/>
-      <c r="GO22" s="31"/>
-      <c r="GP22" s="31"/>
-      <c r="GQ22" s="31"/>
-      <c r="GR22" s="31"/>
-      <c r="GS22" s="31"/>
-      <c r="GT22" s="31"/>
-      <c r="GU22" s="31"/>
-      <c r="GV22" s="31"/>
-      <c r="GW22" s="31"/>
-      <c r="GX22" s="31"/>
-      <c r="GY22" s="31"/>
-      <c r="GZ22" s="31"/>
-      <c r="HA22" s="31"/>
-      <c r="HB22" s="31"/>
-      <c r="HC22" s="31"/>
-      <c r="HD22" s="31"/>
-      <c r="HE22" s="31"/>
-      <c r="HF22" s="31"/>
-      <c r="HG22" s="31"/>
-      <c r="HH22" s="31"/>
-      <c r="HI22" s="31"/>
-      <c r="HJ22" s="31"/>
-      <c r="HK22" s="31"/>
-      <c r="HL22" s="31"/>
-      <c r="HM22" s="31"/>
-      <c r="HN22" s="31"/>
-      <c r="HO22" s="31"/>
-      <c r="HP22" s="31"/>
-      <c r="HQ22" s="31"/>
-      <c r="HR22" s="31"/>
-      <c r="HS22" s="31"/>
-      <c r="HT22" s="31"/>
-      <c r="HU22" s="31"/>
+      <c r="H22" s="28"/>
+      <c r="BQ22" s="29"/>
+      <c r="BS22" s="29"/>
+      <c r="BU22" s="29"/>
+      <c r="BW22" s="29"/>
+      <c r="BY22" s="29"/>
+      <c r="CA22" s="29"/>
+      <c r="CC22" s="29"/>
+      <c r="CE22" s="29"/>
+      <c r="CG22" s="29"/>
+      <c r="CI22" s="29"/>
+      <c r="CK22" s="29"/>
+      <c r="CL22" s="29"/>
+      <c r="CM22" s="29"/>
+      <c r="CN22" s="29"/>
+      <c r="CO22" s="29"/>
+      <c r="CP22" s="29"/>
+      <c r="CQ22" s="29"/>
+      <c r="CR22" s="29"/>
+      <c r="CS22" s="29"/>
+      <c r="CT22" s="29"/>
+      <c r="CU22" s="29"/>
+      <c r="CV22" s="29"/>
+      <c r="CW22" s="29"/>
+      <c r="CX22" s="29"/>
+      <c r="CY22" s="29"/>
+      <c r="CZ22" s="29"/>
+      <c r="DA22" s="29"/>
+      <c r="DB22" s="29"/>
+      <c r="DC22" s="29"/>
+      <c r="DD22" s="29"/>
+      <c r="DE22" s="29"/>
+      <c r="DF22" s="29"/>
+      <c r="DG22" s="29"/>
+      <c r="DH22" s="29"/>
+      <c r="DI22" s="29"/>
+      <c r="DJ22" s="29"/>
+      <c r="DK22" s="29"/>
+      <c r="DL22" s="29"/>
+      <c r="DM22" s="29"/>
+      <c r="DN22" s="29"/>
+      <c r="DO22" s="29"/>
+      <c r="DP22" s="29"/>
+      <c r="DQ22" s="29"/>
+      <c r="DR22" s="29"/>
+      <c r="DS22" s="29"/>
+      <c r="DT22" s="29"/>
+      <c r="DU22" s="29"/>
+      <c r="DV22" s="29"/>
+      <c r="DW22" s="29"/>
+      <c r="DX22" s="29"/>
+      <c r="DY22" s="29"/>
+      <c r="DZ22" s="29"/>
+      <c r="EA22" s="29"/>
+      <c r="EB22" s="29"/>
+      <c r="EC22" s="29"/>
+      <c r="ED22" s="29"/>
+      <c r="EE22" s="29"/>
+      <c r="EF22" s="29"/>
+      <c r="EG22" s="29"/>
+      <c r="EH22" s="29"/>
+      <c r="EI22" s="29"/>
+      <c r="EJ22" s="29"/>
+      <c r="EK22" s="29"/>
+      <c r="EL22" s="29"/>
+      <c r="EM22" s="29"/>
+      <c r="EN22" s="29"/>
+      <c r="EO22" s="29"/>
+      <c r="EP22" s="29"/>
+      <c r="EQ22" s="29"/>
+      <c r="ER22" s="29"/>
+      <c r="ES22" s="29"/>
+      <c r="ET22" s="29"/>
+      <c r="EU22" s="29"/>
+      <c r="EV22" s="29"/>
+      <c r="EW22" s="29"/>
+      <c r="EX22" s="29"/>
+      <c r="EY22" s="29"/>
+      <c r="EZ22" s="29"/>
+      <c r="FA22" s="29"/>
+      <c r="FB22" s="29"/>
+      <c r="FC22" s="29"/>
+      <c r="FD22" s="29"/>
+      <c r="FE22" s="29"/>
+      <c r="FF22" s="29"/>
+      <c r="FG22" s="29"/>
+      <c r="FH22" s="29"/>
+      <c r="FI22" s="29"/>
+      <c r="FJ22" s="29"/>
+      <c r="FK22" s="29"/>
+      <c r="FL22" s="29"/>
+      <c r="FM22" s="29"/>
+      <c r="FN22" s="29"/>
+      <c r="FO22" s="29"/>
+      <c r="FP22" s="29"/>
+      <c r="FQ22" s="29"/>
+      <c r="FR22" s="29"/>
+      <c r="FS22" s="29"/>
+      <c r="FT22" s="29"/>
+      <c r="FU22" s="29"/>
+      <c r="FV22" s="29"/>
+      <c r="FW22" s="29"/>
+      <c r="FX22" s="29"/>
+      <c r="FY22" s="29"/>
+      <c r="FZ22" s="29"/>
+      <c r="GA22" s="29"/>
+      <c r="GB22" s="29"/>
+      <c r="GC22" s="29"/>
+      <c r="GD22" s="29"/>
+      <c r="GE22" s="29"/>
+      <c r="GF22" s="29"/>
+      <c r="GG22" s="29"/>
+      <c r="GH22" s="29"/>
+      <c r="GI22" s="29"/>
+      <c r="GJ22" s="29"/>
+      <c r="GK22" s="29"/>
+      <c r="GL22" s="29"/>
+      <c r="GM22" s="29"/>
+      <c r="GN22" s="29"/>
+      <c r="GO22" s="29"/>
+      <c r="GP22" s="29"/>
+      <c r="GQ22" s="29"/>
+      <c r="GR22" s="29"/>
+      <c r="GS22" s="29"/>
+      <c r="GT22" s="29"/>
+      <c r="GU22" s="29"/>
+      <c r="GV22" s="29"/>
+      <c r="GW22" s="29"/>
+      <c r="GX22" s="29"/>
+      <c r="GY22" s="29"/>
+      <c r="GZ22" s="29"/>
+      <c r="HA22" s="29"/>
+      <c r="HB22" s="29"/>
+      <c r="HC22" s="29"/>
+      <c r="HD22" s="29"/>
+      <c r="HE22" s="29"/>
+      <c r="HF22" s="29"/>
+      <c r="HG22" s="29"/>
+      <c r="HH22" s="29"/>
+      <c r="HI22" s="29"/>
+      <c r="HJ22" s="29"/>
+      <c r="HK22" s="29"/>
+      <c r="HL22" s="29"/>
+      <c r="HM22" s="29"/>
+      <c r="HN22" s="29"/>
+      <c r="HO22" s="29"/>
+      <c r="HP22" s="29"/>
+      <c r="HQ22" s="29"/>
+      <c r="HR22" s="29"/>
+      <c r="HS22" s="29"/>
+      <c r="HT22" s="29"/>
+      <c r="HU22" s="29"/>
     </row>
-    <row r="23" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
@@ -6830,160 +6965,160 @@
       <c r="G23" s="7">
         <v>0</v>
       </c>
-      <c r="H23" s="30"/>
-      <c r="BQ23" s="31"/>
-      <c r="BS23" s="31"/>
-      <c r="BU23" s="31"/>
-      <c r="BW23" s="31"/>
-      <c r="BY23" s="31"/>
-      <c r="CA23" s="31"/>
-      <c r="CC23" s="31"/>
-      <c r="CE23" s="31"/>
-      <c r="CG23" s="31"/>
-      <c r="CI23" s="31"/>
-      <c r="CK23" s="31"/>
-      <c r="CL23" s="31"/>
-      <c r="CM23" s="31"/>
-      <c r="CN23" s="31"/>
-      <c r="CO23" s="31"/>
-      <c r="CP23" s="31"/>
-      <c r="CQ23" s="31"/>
-      <c r="CR23" s="31"/>
-      <c r="CS23" s="31"/>
-      <c r="CT23" s="31"/>
-      <c r="CU23" s="31"/>
-      <c r="CV23" s="31"/>
-      <c r="CW23" s="31"/>
-      <c r="CX23" s="31"/>
-      <c r="CY23" s="31"/>
-      <c r="CZ23" s="31"/>
-      <c r="DA23" s="31"/>
-      <c r="DB23" s="31"/>
-      <c r="DC23" s="31"/>
-      <c r="DD23" s="31"/>
-      <c r="DE23" s="31"/>
-      <c r="DF23" s="31"/>
-      <c r="DG23" s="31"/>
-      <c r="DH23" s="31"/>
-      <c r="DI23" s="31"/>
-      <c r="DJ23" s="31"/>
-      <c r="DK23" s="31"/>
-      <c r="DL23" s="31"/>
-      <c r="DM23" s="31"/>
-      <c r="DN23" s="31"/>
-      <c r="DO23" s="31"/>
-      <c r="DP23" s="31"/>
-      <c r="DQ23" s="31"/>
-      <c r="DR23" s="31"/>
-      <c r="DS23" s="31"/>
-      <c r="DT23" s="31"/>
-      <c r="DU23" s="31"/>
-      <c r="DV23" s="31"/>
-      <c r="DW23" s="31"/>
-      <c r="DX23" s="31"/>
-      <c r="DY23" s="31"/>
-      <c r="DZ23" s="31"/>
-      <c r="EA23" s="31"/>
-      <c r="EB23" s="31"/>
-      <c r="EC23" s="31"/>
-      <c r="ED23" s="31"/>
-      <c r="EE23" s="31"/>
-      <c r="EF23" s="31"/>
-      <c r="EG23" s="31"/>
-      <c r="EH23" s="31"/>
-      <c r="EI23" s="31"/>
-      <c r="EJ23" s="31"/>
-      <c r="EK23" s="31"/>
-      <c r="EL23" s="31"/>
-      <c r="EM23" s="31"/>
-      <c r="EN23" s="31"/>
-      <c r="EO23" s="31"/>
-      <c r="EP23" s="31"/>
-      <c r="EQ23" s="31"/>
-      <c r="ER23" s="31"/>
-      <c r="ES23" s="31"/>
-      <c r="ET23" s="31"/>
-      <c r="EU23" s="31"/>
-      <c r="EV23" s="31"/>
-      <c r="EW23" s="31"/>
-      <c r="EX23" s="31"/>
-      <c r="EY23" s="31"/>
-      <c r="EZ23" s="31"/>
-      <c r="FA23" s="31"/>
-      <c r="FB23" s="31"/>
-      <c r="FC23" s="31"/>
-      <c r="FD23" s="31"/>
-      <c r="FE23" s="31"/>
-      <c r="FF23" s="31"/>
-      <c r="FG23" s="31"/>
-      <c r="FH23" s="31"/>
-      <c r="FI23" s="31"/>
-      <c r="FJ23" s="31"/>
-      <c r="FK23" s="31"/>
-      <c r="FL23" s="31"/>
-      <c r="FM23" s="31"/>
-      <c r="FN23" s="31"/>
-      <c r="FO23" s="31"/>
-      <c r="FP23" s="31"/>
-      <c r="FQ23" s="31"/>
-      <c r="FR23" s="31"/>
-      <c r="FS23" s="31"/>
-      <c r="FT23" s="31"/>
-      <c r="FU23" s="31"/>
-      <c r="FV23" s="31"/>
-      <c r="FW23" s="31"/>
-      <c r="FX23" s="31"/>
-      <c r="FY23" s="31"/>
-      <c r="FZ23" s="31"/>
-      <c r="GA23" s="31"/>
-      <c r="GB23" s="31"/>
-      <c r="GC23" s="31"/>
-      <c r="GD23" s="31"/>
-      <c r="GE23" s="31"/>
-      <c r="GF23" s="31"/>
-      <c r="GG23" s="31"/>
-      <c r="GH23" s="31"/>
-      <c r="GI23" s="31"/>
-      <c r="GJ23" s="31"/>
-      <c r="GK23" s="31"/>
-      <c r="GL23" s="31"/>
-      <c r="GM23" s="31"/>
-      <c r="GN23" s="31"/>
-      <c r="GO23" s="31"/>
-      <c r="GP23" s="31"/>
-      <c r="GQ23" s="31"/>
-      <c r="GR23" s="31"/>
-      <c r="GS23" s="31"/>
-      <c r="GT23" s="31"/>
-      <c r="GU23" s="31"/>
-      <c r="GV23" s="31"/>
-      <c r="GW23" s="31"/>
-      <c r="GX23" s="31"/>
-      <c r="GY23" s="31"/>
-      <c r="GZ23" s="31"/>
-      <c r="HA23" s="31"/>
-      <c r="HB23" s="31"/>
-      <c r="HC23" s="31"/>
-      <c r="HD23" s="31"/>
-      <c r="HE23" s="31"/>
-      <c r="HF23" s="31"/>
-      <c r="HG23" s="31"/>
-      <c r="HH23" s="31"/>
-      <c r="HI23" s="31"/>
-      <c r="HJ23" s="31"/>
-      <c r="HK23" s="31"/>
-      <c r="HL23" s="31"/>
-      <c r="HM23" s="31"/>
-      <c r="HN23" s="31"/>
-      <c r="HO23" s="31"/>
-      <c r="HP23" s="31"/>
-      <c r="HQ23" s="31"/>
-      <c r="HR23" s="31"/>
-      <c r="HS23" s="31"/>
-      <c r="HT23" s="31"/>
-      <c r="HU23" s="31"/>
+      <c r="H23" s="28"/>
+      <c r="BQ23" s="29"/>
+      <c r="BS23" s="29"/>
+      <c r="BU23" s="29"/>
+      <c r="BW23" s="29"/>
+      <c r="BY23" s="29"/>
+      <c r="CA23" s="29"/>
+      <c r="CC23" s="29"/>
+      <c r="CE23" s="29"/>
+      <c r="CG23" s="29"/>
+      <c r="CI23" s="29"/>
+      <c r="CK23" s="29"/>
+      <c r="CL23" s="29"/>
+      <c r="CM23" s="29"/>
+      <c r="CN23" s="29"/>
+      <c r="CO23" s="29"/>
+      <c r="CP23" s="29"/>
+      <c r="CQ23" s="29"/>
+      <c r="CR23" s="29"/>
+      <c r="CS23" s="29"/>
+      <c r="CT23" s="29"/>
+      <c r="CU23" s="29"/>
+      <c r="CV23" s="29"/>
+      <c r="CW23" s="29"/>
+      <c r="CX23" s="29"/>
+      <c r="CY23" s="29"/>
+      <c r="CZ23" s="29"/>
+      <c r="DA23" s="29"/>
+      <c r="DB23" s="29"/>
+      <c r="DC23" s="29"/>
+      <c r="DD23" s="29"/>
+      <c r="DE23" s="29"/>
+      <c r="DF23" s="29"/>
+      <c r="DG23" s="29"/>
+      <c r="DH23" s="29"/>
+      <c r="DI23" s="29"/>
+      <c r="DJ23" s="29"/>
+      <c r="DK23" s="29"/>
+      <c r="DL23" s="29"/>
+      <c r="DM23" s="29"/>
+      <c r="DN23" s="29"/>
+      <c r="DO23" s="29"/>
+      <c r="DP23" s="29"/>
+      <c r="DQ23" s="29"/>
+      <c r="DR23" s="29"/>
+      <c r="DS23" s="29"/>
+      <c r="DT23" s="29"/>
+      <c r="DU23" s="29"/>
+      <c r="DV23" s="29"/>
+      <c r="DW23" s="29"/>
+      <c r="DX23" s="29"/>
+      <c r="DY23" s="29"/>
+      <c r="DZ23" s="29"/>
+      <c r="EA23" s="29"/>
+      <c r="EB23" s="29"/>
+      <c r="EC23" s="29"/>
+      <c r="ED23" s="29"/>
+      <c r="EE23" s="29"/>
+      <c r="EF23" s="29"/>
+      <c r="EG23" s="29"/>
+      <c r="EH23" s="29"/>
+      <c r="EI23" s="29"/>
+      <c r="EJ23" s="29"/>
+      <c r="EK23" s="29"/>
+      <c r="EL23" s="29"/>
+      <c r="EM23" s="29"/>
+      <c r="EN23" s="29"/>
+      <c r="EO23" s="29"/>
+      <c r="EP23" s="29"/>
+      <c r="EQ23" s="29"/>
+      <c r="ER23" s="29"/>
+      <c r="ES23" s="29"/>
+      <c r="ET23" s="29"/>
+      <c r="EU23" s="29"/>
+      <c r="EV23" s="29"/>
+      <c r="EW23" s="29"/>
+      <c r="EX23" s="29"/>
+      <c r="EY23" s="29"/>
+      <c r="EZ23" s="29"/>
+      <c r="FA23" s="29"/>
+      <c r="FB23" s="29"/>
+      <c r="FC23" s="29"/>
+      <c r="FD23" s="29"/>
+      <c r="FE23" s="29"/>
+      <c r="FF23" s="29"/>
+      <c r="FG23" s="29"/>
+      <c r="FH23" s="29"/>
+      <c r="FI23" s="29"/>
+      <c r="FJ23" s="29"/>
+      <c r="FK23" s="29"/>
+      <c r="FL23" s="29"/>
+      <c r="FM23" s="29"/>
+      <c r="FN23" s="29"/>
+      <c r="FO23" s="29"/>
+      <c r="FP23" s="29"/>
+      <c r="FQ23" s="29"/>
+      <c r="FR23" s="29"/>
+      <c r="FS23" s="29"/>
+      <c r="FT23" s="29"/>
+      <c r="FU23" s="29"/>
+      <c r="FV23" s="29"/>
+      <c r="FW23" s="29"/>
+      <c r="FX23" s="29"/>
+      <c r="FY23" s="29"/>
+      <c r="FZ23" s="29"/>
+      <c r="GA23" s="29"/>
+      <c r="GB23" s="29"/>
+      <c r="GC23" s="29"/>
+      <c r="GD23" s="29"/>
+      <c r="GE23" s="29"/>
+      <c r="GF23" s="29"/>
+      <c r="GG23" s="29"/>
+      <c r="GH23" s="29"/>
+      <c r="GI23" s="29"/>
+      <c r="GJ23" s="29"/>
+      <c r="GK23" s="29"/>
+      <c r="GL23" s="29"/>
+      <c r="GM23" s="29"/>
+      <c r="GN23" s="29"/>
+      <c r="GO23" s="29"/>
+      <c r="GP23" s="29"/>
+      <c r="GQ23" s="29"/>
+      <c r="GR23" s="29"/>
+      <c r="GS23" s="29"/>
+      <c r="GT23" s="29"/>
+      <c r="GU23" s="29"/>
+      <c r="GV23" s="29"/>
+      <c r="GW23" s="29"/>
+      <c r="GX23" s="29"/>
+      <c r="GY23" s="29"/>
+      <c r="GZ23" s="29"/>
+      <c r="HA23" s="29"/>
+      <c r="HB23" s="29"/>
+      <c r="HC23" s="29"/>
+      <c r="HD23" s="29"/>
+      <c r="HE23" s="29"/>
+      <c r="HF23" s="29"/>
+      <c r="HG23" s="29"/>
+      <c r="HH23" s="29"/>
+      <c r="HI23" s="29"/>
+      <c r="HJ23" s="29"/>
+      <c r="HK23" s="29"/>
+      <c r="HL23" s="29"/>
+      <c r="HM23" s="29"/>
+      <c r="HN23" s="29"/>
+      <c r="HO23" s="29"/>
+      <c r="HP23" s="29"/>
+      <c r="HQ23" s="29"/>
+      <c r="HR23" s="29"/>
+      <c r="HS23" s="29"/>
+      <c r="HT23" s="29"/>
+      <c r="HU23" s="29"/>
     </row>
-    <row r="24" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
@@ -7002,160 +7137,160 @@
       <c r="G24" s="7">
         <v>0</v>
       </c>
-      <c r="H24" s="30"/>
-      <c r="BQ24" s="31"/>
-      <c r="BS24" s="31"/>
-      <c r="BU24" s="31"/>
-      <c r="BW24" s="31"/>
-      <c r="BY24" s="31"/>
-      <c r="CA24" s="31"/>
-      <c r="CC24" s="31"/>
-      <c r="CE24" s="31"/>
-      <c r="CG24" s="31"/>
-      <c r="CI24" s="31"/>
-      <c r="CK24" s="31"/>
-      <c r="CL24" s="31"/>
-      <c r="CM24" s="31"/>
-      <c r="CN24" s="31"/>
-      <c r="CO24" s="31"/>
-      <c r="CP24" s="31"/>
-      <c r="CQ24" s="31"/>
-      <c r="CR24" s="31"/>
-      <c r="CS24" s="31"/>
-      <c r="CT24" s="31"/>
-      <c r="CU24" s="31"/>
-      <c r="CV24" s="31"/>
-      <c r="CW24" s="31"/>
-      <c r="CX24" s="31"/>
-      <c r="CY24" s="31"/>
-      <c r="CZ24" s="31"/>
-      <c r="DA24" s="31"/>
-      <c r="DB24" s="31"/>
-      <c r="DC24" s="31"/>
-      <c r="DD24" s="31"/>
-      <c r="DE24" s="31"/>
-      <c r="DF24" s="31"/>
-      <c r="DG24" s="31"/>
-      <c r="DH24" s="31"/>
-      <c r="DI24" s="31"/>
-      <c r="DJ24" s="31"/>
-      <c r="DK24" s="31"/>
-      <c r="DL24" s="31"/>
-      <c r="DM24" s="31"/>
-      <c r="DN24" s="31"/>
-      <c r="DO24" s="31"/>
-      <c r="DP24" s="31"/>
-      <c r="DQ24" s="31"/>
-      <c r="DR24" s="31"/>
-      <c r="DS24" s="31"/>
-      <c r="DT24" s="31"/>
-      <c r="DU24" s="31"/>
-      <c r="DV24" s="31"/>
-      <c r="DW24" s="31"/>
-      <c r="DX24" s="31"/>
-      <c r="DY24" s="31"/>
-      <c r="DZ24" s="31"/>
-      <c r="EA24" s="31"/>
-      <c r="EB24" s="31"/>
-      <c r="EC24" s="31"/>
-      <c r="ED24" s="31"/>
-      <c r="EE24" s="31"/>
-      <c r="EF24" s="31"/>
-      <c r="EG24" s="31"/>
-      <c r="EH24" s="31"/>
-      <c r="EI24" s="31"/>
-      <c r="EJ24" s="31"/>
-      <c r="EK24" s="31"/>
-      <c r="EL24" s="31"/>
-      <c r="EM24" s="31"/>
-      <c r="EN24" s="31"/>
-      <c r="EO24" s="31"/>
-      <c r="EP24" s="31"/>
-      <c r="EQ24" s="31"/>
-      <c r="ER24" s="31"/>
-      <c r="ES24" s="31"/>
-      <c r="ET24" s="31"/>
-      <c r="EU24" s="31"/>
-      <c r="EV24" s="31"/>
-      <c r="EW24" s="31"/>
-      <c r="EX24" s="31"/>
-      <c r="EY24" s="31"/>
-      <c r="EZ24" s="31"/>
-      <c r="FA24" s="31"/>
-      <c r="FB24" s="31"/>
-      <c r="FC24" s="31"/>
-      <c r="FD24" s="31"/>
-      <c r="FE24" s="31"/>
-      <c r="FF24" s="31"/>
-      <c r="FG24" s="31"/>
-      <c r="FH24" s="31"/>
-      <c r="FI24" s="31"/>
-      <c r="FJ24" s="31"/>
-      <c r="FK24" s="31"/>
-      <c r="FL24" s="31"/>
-      <c r="FM24" s="31"/>
-      <c r="FN24" s="31"/>
-      <c r="FO24" s="31"/>
-      <c r="FP24" s="31"/>
-      <c r="FQ24" s="31"/>
-      <c r="FR24" s="31"/>
-      <c r="FS24" s="31"/>
-      <c r="FT24" s="31"/>
-      <c r="FU24" s="31"/>
-      <c r="FV24" s="31"/>
-      <c r="FW24" s="31"/>
-      <c r="FX24" s="31"/>
-      <c r="FY24" s="31"/>
-      <c r="FZ24" s="31"/>
-      <c r="GA24" s="31"/>
-      <c r="GB24" s="31"/>
-      <c r="GC24" s="31"/>
-      <c r="GD24" s="31"/>
-      <c r="GE24" s="31"/>
-      <c r="GF24" s="31"/>
-      <c r="GG24" s="31"/>
-      <c r="GH24" s="31"/>
-      <c r="GI24" s="31"/>
-      <c r="GJ24" s="31"/>
-      <c r="GK24" s="31"/>
-      <c r="GL24" s="31"/>
-      <c r="GM24" s="31"/>
-      <c r="GN24" s="31"/>
-      <c r="GO24" s="31"/>
-      <c r="GP24" s="31"/>
-      <c r="GQ24" s="31"/>
-      <c r="GR24" s="31"/>
-      <c r="GS24" s="31"/>
-      <c r="GT24" s="31"/>
-      <c r="GU24" s="31"/>
-      <c r="GV24" s="31"/>
-      <c r="GW24" s="31"/>
-      <c r="GX24" s="31"/>
-      <c r="GY24" s="31"/>
-      <c r="GZ24" s="31"/>
-      <c r="HA24" s="31"/>
-      <c r="HB24" s="31"/>
-      <c r="HC24" s="31"/>
-      <c r="HD24" s="31"/>
-      <c r="HE24" s="31"/>
-      <c r="HF24" s="31"/>
-      <c r="HG24" s="31"/>
-      <c r="HH24" s="31"/>
-      <c r="HI24" s="31"/>
-      <c r="HJ24" s="31"/>
-      <c r="HK24" s="31"/>
-      <c r="HL24" s="31"/>
-      <c r="HM24" s="31"/>
-      <c r="HN24" s="31"/>
-      <c r="HO24" s="31"/>
-      <c r="HP24" s="31"/>
-      <c r="HQ24" s="31"/>
-      <c r="HR24" s="31"/>
-      <c r="HS24" s="31"/>
-      <c r="HT24" s="31"/>
-      <c r="HU24" s="31"/>
+      <c r="H24" s="28"/>
+      <c r="BQ24" s="29"/>
+      <c r="BS24" s="29"/>
+      <c r="BU24" s="29"/>
+      <c r="BW24" s="29"/>
+      <c r="BY24" s="29"/>
+      <c r="CA24" s="29"/>
+      <c r="CC24" s="29"/>
+      <c r="CE24" s="29"/>
+      <c r="CG24" s="29"/>
+      <c r="CI24" s="29"/>
+      <c r="CK24" s="29"/>
+      <c r="CL24" s="29"/>
+      <c r="CM24" s="29"/>
+      <c r="CN24" s="29"/>
+      <c r="CO24" s="29"/>
+      <c r="CP24" s="29"/>
+      <c r="CQ24" s="29"/>
+      <c r="CR24" s="29"/>
+      <c r="CS24" s="29"/>
+      <c r="CT24" s="29"/>
+      <c r="CU24" s="29"/>
+      <c r="CV24" s="29"/>
+      <c r="CW24" s="29"/>
+      <c r="CX24" s="29"/>
+      <c r="CY24" s="29"/>
+      <c r="CZ24" s="29"/>
+      <c r="DA24" s="29"/>
+      <c r="DB24" s="29"/>
+      <c r="DC24" s="29"/>
+      <c r="DD24" s="29"/>
+      <c r="DE24" s="29"/>
+      <c r="DF24" s="29"/>
+      <c r="DG24" s="29"/>
+      <c r="DH24" s="29"/>
+      <c r="DI24" s="29"/>
+      <c r="DJ24" s="29"/>
+      <c r="DK24" s="29"/>
+      <c r="DL24" s="29"/>
+      <c r="DM24" s="29"/>
+      <c r="DN24" s="29"/>
+      <c r="DO24" s="29"/>
+      <c r="DP24" s="29"/>
+      <c r="DQ24" s="29"/>
+      <c r="DR24" s="29"/>
+      <c r="DS24" s="29"/>
+      <c r="DT24" s="29"/>
+      <c r="DU24" s="29"/>
+      <c r="DV24" s="29"/>
+      <c r="DW24" s="29"/>
+      <c r="DX24" s="29"/>
+      <c r="DY24" s="29"/>
+      <c r="DZ24" s="29"/>
+      <c r="EA24" s="29"/>
+      <c r="EB24" s="29"/>
+      <c r="EC24" s="29"/>
+      <c r="ED24" s="29"/>
+      <c r="EE24" s="29"/>
+      <c r="EF24" s="29"/>
+      <c r="EG24" s="29"/>
+      <c r="EH24" s="29"/>
+      <c r="EI24" s="29"/>
+      <c r="EJ24" s="29"/>
+      <c r="EK24" s="29"/>
+      <c r="EL24" s="29"/>
+      <c r="EM24" s="29"/>
+      <c r="EN24" s="29"/>
+      <c r="EO24" s="29"/>
+      <c r="EP24" s="29"/>
+      <c r="EQ24" s="29"/>
+      <c r="ER24" s="29"/>
+      <c r="ES24" s="29"/>
+      <c r="ET24" s="29"/>
+      <c r="EU24" s="29"/>
+      <c r="EV24" s="29"/>
+      <c r="EW24" s="29"/>
+      <c r="EX24" s="29"/>
+      <c r="EY24" s="29"/>
+      <c r="EZ24" s="29"/>
+      <c r="FA24" s="29"/>
+      <c r="FB24" s="29"/>
+      <c r="FC24" s="29"/>
+      <c r="FD24" s="29"/>
+      <c r="FE24" s="29"/>
+      <c r="FF24" s="29"/>
+      <c r="FG24" s="29"/>
+      <c r="FH24" s="29"/>
+      <c r="FI24" s="29"/>
+      <c r="FJ24" s="29"/>
+      <c r="FK24" s="29"/>
+      <c r="FL24" s="29"/>
+      <c r="FM24" s="29"/>
+      <c r="FN24" s="29"/>
+      <c r="FO24" s="29"/>
+      <c r="FP24" s="29"/>
+      <c r="FQ24" s="29"/>
+      <c r="FR24" s="29"/>
+      <c r="FS24" s="29"/>
+      <c r="FT24" s="29"/>
+      <c r="FU24" s="29"/>
+      <c r="FV24" s="29"/>
+      <c r="FW24" s="29"/>
+      <c r="FX24" s="29"/>
+      <c r="FY24" s="29"/>
+      <c r="FZ24" s="29"/>
+      <c r="GA24" s="29"/>
+      <c r="GB24" s="29"/>
+      <c r="GC24" s="29"/>
+      <c r="GD24" s="29"/>
+      <c r="GE24" s="29"/>
+      <c r="GF24" s="29"/>
+      <c r="GG24" s="29"/>
+      <c r="GH24" s="29"/>
+      <c r="GI24" s="29"/>
+      <c r="GJ24" s="29"/>
+      <c r="GK24" s="29"/>
+      <c r="GL24" s="29"/>
+      <c r="GM24" s="29"/>
+      <c r="GN24" s="29"/>
+      <c r="GO24" s="29"/>
+      <c r="GP24" s="29"/>
+      <c r="GQ24" s="29"/>
+      <c r="GR24" s="29"/>
+      <c r="GS24" s="29"/>
+      <c r="GT24" s="29"/>
+      <c r="GU24" s="29"/>
+      <c r="GV24" s="29"/>
+      <c r="GW24" s="29"/>
+      <c r="GX24" s="29"/>
+      <c r="GY24" s="29"/>
+      <c r="GZ24" s="29"/>
+      <c r="HA24" s="29"/>
+      <c r="HB24" s="29"/>
+      <c r="HC24" s="29"/>
+      <c r="HD24" s="29"/>
+      <c r="HE24" s="29"/>
+      <c r="HF24" s="29"/>
+      <c r="HG24" s="29"/>
+      <c r="HH24" s="29"/>
+      <c r="HI24" s="29"/>
+      <c r="HJ24" s="29"/>
+      <c r="HK24" s="29"/>
+      <c r="HL24" s="29"/>
+      <c r="HM24" s="29"/>
+      <c r="HN24" s="29"/>
+      <c r="HO24" s="29"/>
+      <c r="HP24" s="29"/>
+      <c r="HQ24" s="29"/>
+      <c r="HR24" s="29"/>
+      <c r="HS24" s="29"/>
+      <c r="HT24" s="29"/>
+      <c r="HU24" s="29"/>
     </row>
-    <row r="25" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
@@ -7174,172 +7309,172 @@
       <c r="G25" s="7">
         <v>0</v>
       </c>
-      <c r="H25" s="30"/>
-      <c r="BO25" s="31"/>
-      <c r="BP25" s="31"/>
-      <c r="BQ25" s="31"/>
-      <c r="BR25" s="31"/>
-      <c r="BS25" s="31"/>
-      <c r="BT25" s="31"/>
-      <c r="BU25" s="31"/>
-      <c r="BV25" s="31"/>
-      <c r="BW25" s="31"/>
-      <c r="BX25" s="31"/>
-      <c r="BY25" s="31"/>
-      <c r="BZ25" s="31"/>
-      <c r="CA25" s="31"/>
-      <c r="CB25" s="31"/>
-      <c r="CC25" s="31"/>
-      <c r="CD25" s="31"/>
-      <c r="CE25" s="31"/>
-      <c r="CF25" s="31"/>
-      <c r="CG25" s="31"/>
-      <c r="CH25" s="31"/>
-      <c r="CI25" s="31"/>
-      <c r="CJ25" s="31"/>
-      <c r="CK25" s="31"/>
-      <c r="CL25" s="31"/>
-      <c r="CM25" s="31"/>
-      <c r="CN25" s="31"/>
-      <c r="CO25" s="31"/>
-      <c r="CP25" s="31"/>
-      <c r="CQ25" s="31"/>
-      <c r="CR25" s="31"/>
-      <c r="CS25" s="31"/>
-      <c r="CT25" s="31"/>
-      <c r="CU25" s="31"/>
-      <c r="CV25" s="31"/>
-      <c r="CW25" s="31"/>
-      <c r="CX25" s="31"/>
-      <c r="CY25" s="31"/>
-      <c r="CZ25" s="31"/>
-      <c r="DA25" s="31"/>
-      <c r="DB25" s="31"/>
-      <c r="DC25" s="31"/>
-      <c r="DD25" s="31"/>
-      <c r="DE25" s="31"/>
-      <c r="DF25" s="31"/>
-      <c r="DG25" s="31"/>
-      <c r="DH25" s="31"/>
-      <c r="DI25" s="31"/>
-      <c r="DJ25" s="31"/>
-      <c r="DK25" s="31"/>
-      <c r="DL25" s="31"/>
-      <c r="DM25" s="31"/>
-      <c r="DN25" s="31"/>
-      <c r="DO25" s="31"/>
-      <c r="DP25" s="31"/>
-      <c r="DQ25" s="31"/>
-      <c r="DR25" s="31"/>
-      <c r="DS25" s="31"/>
-      <c r="DT25" s="31"/>
-      <c r="DU25" s="31"/>
-      <c r="DV25" s="31"/>
-      <c r="DW25" s="31"/>
-      <c r="DX25" s="31"/>
-      <c r="DY25" s="31"/>
-      <c r="DZ25" s="31"/>
-      <c r="EA25" s="31"/>
-      <c r="EB25" s="31"/>
-      <c r="EC25" s="31"/>
-      <c r="ED25" s="31"/>
-      <c r="EE25" s="31"/>
-      <c r="EF25" s="31"/>
-      <c r="EG25" s="31"/>
-      <c r="EH25" s="31"/>
-      <c r="EI25" s="31"/>
-      <c r="EJ25" s="31"/>
-      <c r="EK25" s="31"/>
-      <c r="EL25" s="31"/>
-      <c r="EM25" s="31"/>
-      <c r="EN25" s="31"/>
-      <c r="EO25" s="31"/>
-      <c r="EP25" s="31"/>
-      <c r="EQ25" s="31"/>
-      <c r="ER25" s="31"/>
-      <c r="ES25" s="31"/>
-      <c r="ET25" s="31"/>
-      <c r="EU25" s="31"/>
-      <c r="EV25" s="31"/>
-      <c r="EW25" s="31"/>
-      <c r="EX25" s="31"/>
-      <c r="EY25" s="31"/>
-      <c r="EZ25" s="31"/>
-      <c r="FA25" s="31"/>
-      <c r="FB25" s="31"/>
-      <c r="FC25" s="31"/>
-      <c r="FD25" s="31"/>
-      <c r="FE25" s="31"/>
-      <c r="FF25" s="31"/>
-      <c r="FG25" s="31"/>
-      <c r="FH25" s="31"/>
-      <c r="FI25" s="31"/>
-      <c r="FJ25" s="31"/>
-      <c r="FK25" s="31"/>
-      <c r="FL25" s="31"/>
-      <c r="FM25" s="31"/>
-      <c r="FN25" s="31"/>
-      <c r="FO25" s="31"/>
-      <c r="FP25" s="31"/>
-      <c r="FQ25" s="31"/>
-      <c r="FR25" s="31"/>
-      <c r="FS25" s="31"/>
-      <c r="FT25" s="31"/>
-      <c r="FU25" s="31"/>
-      <c r="FV25" s="31"/>
-      <c r="FW25" s="31"/>
-      <c r="FX25" s="31"/>
-      <c r="FY25" s="31"/>
-      <c r="FZ25" s="31"/>
-      <c r="GA25" s="31"/>
-      <c r="GB25" s="31"/>
-      <c r="GC25" s="31"/>
-      <c r="GD25" s="31"/>
-      <c r="GE25" s="31"/>
-      <c r="GF25" s="31"/>
-      <c r="GG25" s="31"/>
-      <c r="GH25" s="31"/>
-      <c r="GI25" s="31"/>
-      <c r="GJ25" s="31"/>
-      <c r="GK25" s="31"/>
-      <c r="GL25" s="31"/>
-      <c r="GM25" s="31"/>
-      <c r="GN25" s="31"/>
-      <c r="GO25" s="31"/>
-      <c r="GP25" s="31"/>
-      <c r="GQ25" s="31"/>
-      <c r="GR25" s="31"/>
-      <c r="GS25" s="31"/>
-      <c r="GT25" s="31"/>
-      <c r="GU25" s="31"/>
-      <c r="GV25" s="31"/>
-      <c r="GW25" s="31"/>
-      <c r="GX25" s="31"/>
-      <c r="GY25" s="31"/>
-      <c r="GZ25" s="31"/>
-      <c r="HA25" s="31"/>
-      <c r="HB25" s="31"/>
-      <c r="HC25" s="31"/>
-      <c r="HD25" s="31"/>
-      <c r="HE25" s="31"/>
-      <c r="HF25" s="31"/>
-      <c r="HG25" s="31"/>
-      <c r="HH25" s="31"/>
-      <c r="HI25" s="31"/>
-      <c r="HJ25" s="31"/>
-      <c r="HK25" s="31"/>
-      <c r="HL25" s="31"/>
-      <c r="HM25" s="31"/>
-      <c r="HN25" s="31"/>
-      <c r="HO25" s="31"/>
-      <c r="HP25" s="31"/>
-      <c r="HQ25" s="31"/>
-      <c r="HR25" s="31"/>
-      <c r="HS25" s="31"/>
-      <c r="HT25" s="31"/>
-      <c r="HU25" s="31"/>
+      <c r="H25" s="28"/>
+      <c r="BO25" s="29"/>
+      <c r="BP25" s="29"/>
+      <c r="BQ25" s="29"/>
+      <c r="BR25" s="29"/>
+      <c r="BS25" s="29"/>
+      <c r="BT25" s="29"/>
+      <c r="BU25" s="29"/>
+      <c r="BV25" s="29"/>
+      <c r="BW25" s="29"/>
+      <c r="BX25" s="29"/>
+      <c r="BY25" s="29"/>
+      <c r="BZ25" s="29"/>
+      <c r="CA25" s="29"/>
+      <c r="CB25" s="29"/>
+      <c r="CC25" s="29"/>
+      <c r="CD25" s="29"/>
+      <c r="CE25" s="29"/>
+      <c r="CF25" s="29"/>
+      <c r="CG25" s="29"/>
+      <c r="CH25" s="29"/>
+      <c r="CI25" s="29"/>
+      <c r="CJ25" s="29"/>
+      <c r="CK25" s="29"/>
+      <c r="CL25" s="29"/>
+      <c r="CM25" s="29"/>
+      <c r="CN25" s="29"/>
+      <c r="CO25" s="29"/>
+      <c r="CP25" s="29"/>
+      <c r="CQ25" s="29"/>
+      <c r="CR25" s="29"/>
+      <c r="CS25" s="29"/>
+      <c r="CT25" s="29"/>
+      <c r="CU25" s="29"/>
+      <c r="CV25" s="29"/>
+      <c r="CW25" s="29"/>
+      <c r="CX25" s="29"/>
+      <c r="CY25" s="29"/>
+      <c r="CZ25" s="29"/>
+      <c r="DA25" s="29"/>
+      <c r="DB25" s="29"/>
+      <c r="DC25" s="29"/>
+      <c r="DD25" s="29"/>
+      <c r="DE25" s="29"/>
+      <c r="DF25" s="29"/>
+      <c r="DG25" s="29"/>
+      <c r="DH25" s="29"/>
+      <c r="DI25" s="29"/>
+      <c r="DJ25" s="29"/>
+      <c r="DK25" s="29"/>
+      <c r="DL25" s="29"/>
+      <c r="DM25" s="29"/>
+      <c r="DN25" s="29"/>
+      <c r="DO25" s="29"/>
+      <c r="DP25" s="29"/>
+      <c r="DQ25" s="29"/>
+      <c r="DR25" s="29"/>
+      <c r="DS25" s="29"/>
+      <c r="DT25" s="29"/>
+      <c r="DU25" s="29"/>
+      <c r="DV25" s="29"/>
+      <c r="DW25" s="29"/>
+      <c r="DX25" s="29"/>
+      <c r="DY25" s="29"/>
+      <c r="DZ25" s="29"/>
+      <c r="EA25" s="29"/>
+      <c r="EB25" s="29"/>
+      <c r="EC25" s="29"/>
+      <c r="ED25" s="29"/>
+      <c r="EE25" s="29"/>
+      <c r="EF25" s="29"/>
+      <c r="EG25" s="29"/>
+      <c r="EH25" s="29"/>
+      <c r="EI25" s="29"/>
+      <c r="EJ25" s="29"/>
+      <c r="EK25" s="29"/>
+      <c r="EL25" s="29"/>
+      <c r="EM25" s="29"/>
+      <c r="EN25" s="29"/>
+      <c r="EO25" s="29"/>
+      <c r="EP25" s="29"/>
+      <c r="EQ25" s="29"/>
+      <c r="ER25" s="29"/>
+      <c r="ES25" s="29"/>
+      <c r="ET25" s="29"/>
+      <c r="EU25" s="29"/>
+      <c r="EV25" s="29"/>
+      <c r="EW25" s="29"/>
+      <c r="EX25" s="29"/>
+      <c r="EY25" s="29"/>
+      <c r="EZ25" s="29"/>
+      <c r="FA25" s="29"/>
+      <c r="FB25" s="29"/>
+      <c r="FC25" s="29"/>
+      <c r="FD25" s="29"/>
+      <c r="FE25" s="29"/>
+      <c r="FF25" s="29"/>
+      <c r="FG25" s="29"/>
+      <c r="FH25" s="29"/>
+      <c r="FI25" s="29"/>
+      <c r="FJ25" s="29"/>
+      <c r="FK25" s="29"/>
+      <c r="FL25" s="29"/>
+      <c r="FM25" s="29"/>
+      <c r="FN25" s="29"/>
+      <c r="FO25" s="29"/>
+      <c r="FP25" s="29"/>
+      <c r="FQ25" s="29"/>
+      <c r="FR25" s="29"/>
+      <c r="FS25" s="29"/>
+      <c r="FT25" s="29"/>
+      <c r="FU25" s="29"/>
+      <c r="FV25" s="29"/>
+      <c r="FW25" s="29"/>
+      <c r="FX25" s="29"/>
+      <c r="FY25" s="29"/>
+      <c r="FZ25" s="29"/>
+      <c r="GA25" s="29"/>
+      <c r="GB25" s="29"/>
+      <c r="GC25" s="29"/>
+      <c r="GD25" s="29"/>
+      <c r="GE25" s="29"/>
+      <c r="GF25" s="29"/>
+      <c r="GG25" s="29"/>
+      <c r="GH25" s="29"/>
+      <c r="GI25" s="29"/>
+      <c r="GJ25" s="29"/>
+      <c r="GK25" s="29"/>
+      <c r="GL25" s="29"/>
+      <c r="GM25" s="29"/>
+      <c r="GN25" s="29"/>
+      <c r="GO25" s="29"/>
+      <c r="GP25" s="29"/>
+      <c r="GQ25" s="29"/>
+      <c r="GR25" s="29"/>
+      <c r="GS25" s="29"/>
+      <c r="GT25" s="29"/>
+      <c r="GU25" s="29"/>
+      <c r="GV25" s="29"/>
+      <c r="GW25" s="29"/>
+      <c r="GX25" s="29"/>
+      <c r="GY25" s="29"/>
+      <c r="GZ25" s="29"/>
+      <c r="HA25" s="29"/>
+      <c r="HB25" s="29"/>
+      <c r="HC25" s="29"/>
+      <c r="HD25" s="29"/>
+      <c r="HE25" s="29"/>
+      <c r="HF25" s="29"/>
+      <c r="HG25" s="29"/>
+      <c r="HH25" s="29"/>
+      <c r="HI25" s="29"/>
+      <c r="HJ25" s="29"/>
+      <c r="HK25" s="29"/>
+      <c r="HL25" s="29"/>
+      <c r="HM25" s="29"/>
+      <c r="HN25" s="29"/>
+      <c r="HO25" s="29"/>
+      <c r="HP25" s="29"/>
+      <c r="HQ25" s="29"/>
+      <c r="HR25" s="29"/>
+      <c r="HS25" s="29"/>
+      <c r="HT25" s="29"/>
+      <c r="HU25" s="29"/>
     </row>
-    <row r="26" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
         <v>13</v>
       </c>
@@ -7358,9 +7493,9 @@
       <c r="G26" s="7">
         <v>0</v>
       </c>
-      <c r="H26" s="30"/>
+      <c r="H26" s="28"/>
     </row>
-    <row r="27" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="5" t="s">
         <v>14</v>
       </c>
@@ -7379,171 +7514,171 @@
       <c r="G27" s="7">
         <v>0</v>
       </c>
-      <c r="H27" s="30"/>
-      <c r="BP27" s="31"/>
-      <c r="BQ27" s="31"/>
-      <c r="BR27" s="31"/>
-      <c r="BS27" s="31"/>
-      <c r="BT27" s="31"/>
-      <c r="BU27" s="31"/>
-      <c r="BV27" s="31"/>
-      <c r="BW27" s="31"/>
-      <c r="BX27" s="31"/>
-      <c r="BY27" s="31"/>
-      <c r="BZ27" s="31"/>
-      <c r="CA27" s="31"/>
-      <c r="CB27" s="31"/>
-      <c r="CC27" s="31"/>
-      <c r="CD27" s="31"/>
-      <c r="CE27" s="31"/>
-      <c r="CF27" s="31"/>
-      <c r="CG27" s="31"/>
-      <c r="CH27" s="31"/>
-      <c r="CI27" s="31"/>
-      <c r="CJ27" s="31"/>
-      <c r="CK27" s="31"/>
-      <c r="CL27" s="31"/>
-      <c r="CM27" s="31"/>
-      <c r="CN27" s="31"/>
-      <c r="CO27" s="31"/>
-      <c r="CP27" s="31"/>
-      <c r="CQ27" s="31"/>
-      <c r="CR27" s="31"/>
-      <c r="CS27" s="31"/>
-      <c r="CT27" s="31"/>
-      <c r="CU27" s="31"/>
-      <c r="CV27" s="31"/>
-      <c r="CW27" s="31"/>
-      <c r="CX27" s="31"/>
-      <c r="CY27" s="31"/>
-      <c r="CZ27" s="31"/>
-      <c r="DA27" s="31"/>
-      <c r="DB27" s="31"/>
-      <c r="DC27" s="31"/>
-      <c r="DD27" s="31"/>
-      <c r="DE27" s="31"/>
-      <c r="DF27" s="31"/>
-      <c r="DG27" s="31"/>
-      <c r="DH27" s="31"/>
-      <c r="DI27" s="31"/>
-      <c r="DJ27" s="31"/>
-      <c r="DK27" s="31"/>
-      <c r="DL27" s="31"/>
-      <c r="DM27" s="31"/>
-      <c r="DN27" s="31"/>
-      <c r="DO27" s="31"/>
-      <c r="DP27" s="31"/>
-      <c r="DQ27" s="31"/>
-      <c r="DR27" s="31"/>
-      <c r="DS27" s="31"/>
-      <c r="DT27" s="31"/>
-      <c r="DU27" s="31"/>
-      <c r="DV27" s="31"/>
-      <c r="DW27" s="31"/>
-      <c r="DX27" s="31"/>
-      <c r="DY27" s="31"/>
-      <c r="DZ27" s="31"/>
-      <c r="EA27" s="31"/>
-      <c r="EB27" s="31"/>
-      <c r="EC27" s="31"/>
-      <c r="ED27" s="31"/>
-      <c r="EE27" s="31"/>
-      <c r="EF27" s="31"/>
-      <c r="EG27" s="31"/>
-      <c r="EH27" s="31"/>
-      <c r="EI27" s="31"/>
-      <c r="EJ27" s="31"/>
-      <c r="EK27" s="31"/>
-      <c r="EL27" s="31"/>
-      <c r="EM27" s="31"/>
-      <c r="EN27" s="31"/>
-      <c r="EO27" s="31"/>
-      <c r="EP27" s="31"/>
-      <c r="EQ27" s="31"/>
-      <c r="ER27" s="31"/>
-      <c r="ES27" s="31"/>
-      <c r="ET27" s="31"/>
-      <c r="EU27" s="31"/>
-      <c r="EV27" s="31"/>
-      <c r="EW27" s="31"/>
-      <c r="EX27" s="31"/>
-      <c r="EY27" s="31"/>
-      <c r="EZ27" s="31"/>
-      <c r="FA27" s="31"/>
-      <c r="FB27" s="31"/>
-      <c r="FC27" s="31"/>
-      <c r="FD27" s="31"/>
-      <c r="FE27" s="31"/>
-      <c r="FF27" s="31"/>
-      <c r="FG27" s="31"/>
-      <c r="FH27" s="31"/>
-      <c r="FI27" s="31"/>
-      <c r="FJ27" s="31"/>
-      <c r="FK27" s="31"/>
-      <c r="FL27" s="31"/>
-      <c r="FM27" s="31"/>
-      <c r="FN27" s="31"/>
-      <c r="FO27" s="31"/>
-      <c r="FP27" s="31"/>
-      <c r="FQ27" s="31"/>
-      <c r="FR27" s="31"/>
-      <c r="FS27" s="31"/>
-      <c r="FT27" s="31"/>
-      <c r="FU27" s="31"/>
-      <c r="FV27" s="31"/>
-      <c r="FW27" s="31"/>
-      <c r="FX27" s="31"/>
-      <c r="FY27" s="31"/>
-      <c r="FZ27" s="31"/>
-      <c r="GA27" s="31"/>
-      <c r="GB27" s="31"/>
-      <c r="GC27" s="31"/>
-      <c r="GD27" s="31"/>
-      <c r="GE27" s="31"/>
-      <c r="GF27" s="31"/>
-      <c r="GG27" s="31"/>
-      <c r="GH27" s="31"/>
-      <c r="GI27" s="31"/>
-      <c r="GJ27" s="31"/>
-      <c r="GK27" s="31"/>
-      <c r="GL27" s="31"/>
-      <c r="GM27" s="31"/>
-      <c r="GN27" s="31"/>
-      <c r="GO27" s="31"/>
-      <c r="GP27" s="31"/>
-      <c r="GQ27" s="31"/>
-      <c r="GR27" s="31"/>
-      <c r="GS27" s="31"/>
-      <c r="GT27" s="31"/>
-      <c r="GU27" s="31"/>
-      <c r="GV27" s="31"/>
-      <c r="GW27" s="31"/>
-      <c r="GX27" s="31"/>
-      <c r="GY27" s="31"/>
-      <c r="GZ27" s="31"/>
-      <c r="HA27" s="31"/>
-      <c r="HB27" s="31"/>
-      <c r="HC27" s="31"/>
-      <c r="HD27" s="31"/>
-      <c r="HE27" s="31"/>
-      <c r="HF27" s="31"/>
-      <c r="HG27" s="31"/>
-      <c r="HH27" s="31"/>
-      <c r="HI27" s="31"/>
-      <c r="HJ27" s="31"/>
-      <c r="HK27" s="31"/>
-      <c r="HL27" s="31"/>
-      <c r="HM27" s="31"/>
-      <c r="HN27" s="31"/>
-      <c r="HO27" s="31"/>
-      <c r="HP27" s="31"/>
-      <c r="HQ27" s="31"/>
-      <c r="HR27" s="31"/>
-      <c r="HS27" s="31"/>
-      <c r="HT27" s="31"/>
-      <c r="HU27" s="31"/>
+      <c r="H27" s="28"/>
+      <c r="BP27" s="29"/>
+      <c r="BQ27" s="29"/>
+      <c r="BR27" s="29"/>
+      <c r="BS27" s="29"/>
+      <c r="BT27" s="29"/>
+      <c r="BU27" s="29"/>
+      <c r="BV27" s="29"/>
+      <c r="BW27" s="29"/>
+      <c r="BX27" s="29"/>
+      <c r="BY27" s="29"/>
+      <c r="BZ27" s="29"/>
+      <c r="CA27" s="29"/>
+      <c r="CB27" s="29"/>
+      <c r="CC27" s="29"/>
+      <c r="CD27" s="29"/>
+      <c r="CE27" s="29"/>
+      <c r="CF27" s="29"/>
+      <c r="CG27" s="29"/>
+      <c r="CH27" s="29"/>
+      <c r="CI27" s="29"/>
+      <c r="CJ27" s="29"/>
+      <c r="CK27" s="29"/>
+      <c r="CL27" s="29"/>
+      <c r="CM27" s="29"/>
+      <c r="CN27" s="29"/>
+      <c r="CO27" s="29"/>
+      <c r="CP27" s="29"/>
+      <c r="CQ27" s="29"/>
+      <c r="CR27" s="29"/>
+      <c r="CS27" s="29"/>
+      <c r="CT27" s="29"/>
+      <c r="CU27" s="29"/>
+      <c r="CV27" s="29"/>
+      <c r="CW27" s="29"/>
+      <c r="CX27" s="29"/>
+      <c r="CY27" s="29"/>
+      <c r="CZ27" s="29"/>
+      <c r="DA27" s="29"/>
+      <c r="DB27" s="29"/>
+      <c r="DC27" s="29"/>
+      <c r="DD27" s="29"/>
+      <c r="DE27" s="29"/>
+      <c r="DF27" s="29"/>
+      <c r="DG27" s="29"/>
+      <c r="DH27" s="29"/>
+      <c r="DI27" s="29"/>
+      <c r="DJ27" s="29"/>
+      <c r="DK27" s="29"/>
+      <c r="DL27" s="29"/>
+      <c r="DM27" s="29"/>
+      <c r="DN27" s="29"/>
+      <c r="DO27" s="29"/>
+      <c r="DP27" s="29"/>
+      <c r="DQ27" s="29"/>
+      <c r="DR27" s="29"/>
+      <c r="DS27" s="29"/>
+      <c r="DT27" s="29"/>
+      <c r="DU27" s="29"/>
+      <c r="DV27" s="29"/>
+      <c r="DW27" s="29"/>
+      <c r="DX27" s="29"/>
+      <c r="DY27" s="29"/>
+      <c r="DZ27" s="29"/>
+      <c r="EA27" s="29"/>
+      <c r="EB27" s="29"/>
+      <c r="EC27" s="29"/>
+      <c r="ED27" s="29"/>
+      <c r="EE27" s="29"/>
+      <c r="EF27" s="29"/>
+      <c r="EG27" s="29"/>
+      <c r="EH27" s="29"/>
+      <c r="EI27" s="29"/>
+      <c r="EJ27" s="29"/>
+      <c r="EK27" s="29"/>
+      <c r="EL27" s="29"/>
+      <c r="EM27" s="29"/>
+      <c r="EN27" s="29"/>
+      <c r="EO27" s="29"/>
+      <c r="EP27" s="29"/>
+      <c r="EQ27" s="29"/>
+      <c r="ER27" s="29"/>
+      <c r="ES27" s="29"/>
+      <c r="ET27" s="29"/>
+      <c r="EU27" s="29"/>
+      <c r="EV27" s="29"/>
+      <c r="EW27" s="29"/>
+      <c r="EX27" s="29"/>
+      <c r="EY27" s="29"/>
+      <c r="EZ27" s="29"/>
+      <c r="FA27" s="29"/>
+      <c r="FB27" s="29"/>
+      <c r="FC27" s="29"/>
+      <c r="FD27" s="29"/>
+      <c r="FE27" s="29"/>
+      <c r="FF27" s="29"/>
+      <c r="FG27" s="29"/>
+      <c r="FH27" s="29"/>
+      <c r="FI27" s="29"/>
+      <c r="FJ27" s="29"/>
+      <c r="FK27" s="29"/>
+      <c r="FL27" s="29"/>
+      <c r="FM27" s="29"/>
+      <c r="FN27" s="29"/>
+      <c r="FO27" s="29"/>
+      <c r="FP27" s="29"/>
+      <c r="FQ27" s="29"/>
+      <c r="FR27" s="29"/>
+      <c r="FS27" s="29"/>
+      <c r="FT27" s="29"/>
+      <c r="FU27" s="29"/>
+      <c r="FV27" s="29"/>
+      <c r="FW27" s="29"/>
+      <c r="FX27" s="29"/>
+      <c r="FY27" s="29"/>
+      <c r="FZ27" s="29"/>
+      <c r="GA27" s="29"/>
+      <c r="GB27" s="29"/>
+      <c r="GC27" s="29"/>
+      <c r="GD27" s="29"/>
+      <c r="GE27" s="29"/>
+      <c r="GF27" s="29"/>
+      <c r="GG27" s="29"/>
+      <c r="GH27" s="29"/>
+      <c r="GI27" s="29"/>
+      <c r="GJ27" s="29"/>
+      <c r="GK27" s="29"/>
+      <c r="GL27" s="29"/>
+      <c r="GM27" s="29"/>
+      <c r="GN27" s="29"/>
+      <c r="GO27" s="29"/>
+      <c r="GP27" s="29"/>
+      <c r="GQ27" s="29"/>
+      <c r="GR27" s="29"/>
+      <c r="GS27" s="29"/>
+      <c r="GT27" s="29"/>
+      <c r="GU27" s="29"/>
+      <c r="GV27" s="29"/>
+      <c r="GW27" s="29"/>
+      <c r="GX27" s="29"/>
+      <c r="GY27" s="29"/>
+      <c r="GZ27" s="29"/>
+      <c r="HA27" s="29"/>
+      <c r="HB27" s="29"/>
+      <c r="HC27" s="29"/>
+      <c r="HD27" s="29"/>
+      <c r="HE27" s="29"/>
+      <c r="HF27" s="29"/>
+      <c r="HG27" s="29"/>
+      <c r="HH27" s="29"/>
+      <c r="HI27" s="29"/>
+      <c r="HJ27" s="29"/>
+      <c r="HK27" s="29"/>
+      <c r="HL27" s="29"/>
+      <c r="HM27" s="29"/>
+      <c r="HN27" s="29"/>
+      <c r="HO27" s="29"/>
+      <c r="HP27" s="29"/>
+      <c r="HQ27" s="29"/>
+      <c r="HR27" s="29"/>
+      <c r="HS27" s="29"/>
+      <c r="HT27" s="29"/>
+      <c r="HU27" s="29"/>
     </row>
-    <row r="28" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
@@ -7562,9 +7697,9 @@
       <c r="G28" s="7">
         <v>0</v>
       </c>
-      <c r="H28" s="30"/>
+      <c r="H28" s="28"/>
     </row>
-    <row r="29" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="5" t="s">
         <v>16</v>
       </c>
@@ -7583,9 +7718,9 @@
       <c r="G29" s="7">
         <v>0</v>
       </c>
-      <c r="H29" s="30"/>
+      <c r="H29" s="28"/>
     </row>
-    <row r="30" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
         <v>17</v>
       </c>
@@ -7604,7 +7739,7 @@
       <c r="G30" s="7">
         <v>0</v>
       </c>
-      <c r="H30" s="30"/>
+      <c r="H30" s="28"/>
       <c r="J30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
@@ -7809,7 +7944,7 @@
       <c r="HT30" s="1"/>
       <c r="HU30" s="1"/>
     </row>
-    <row r="31" spans="2:229" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -8052,216 +8187,216 @@
     <mergeCell ref="AA2:AG2"/>
     <mergeCell ref="W2:X2"/>
   </mergeCells>
-  <conditionalFormatting sqref="BP28:HU29 BP26:HU26 I26:BO29 I25:BN25 I30:HU30 I15:BO24 I5:HU14">
-    <cfRule type="expression" dxfId="105" priority="121">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="104" priority="123">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="103" priority="124">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="125">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="126">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="127">
-      <formula>I$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="131">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="132">
-      <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B31:HU31">
-    <cfRule type="expression" dxfId="97" priority="122">
+    <cfRule type="expression" dxfId="105" priority="122">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:HU4 H5:H30">
-    <cfRule type="expression" dxfId="96" priority="128">
+    <cfRule type="expression" dxfId="104" priority="128">
       <formula>H$4=időszak_kiválasztva</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BP27:HU27 BO25:HU25 CK23:HU23 CK21:HU21 CK19:HU19 CK17:HU17 CK15:HU15">
-    <cfRule type="expression" dxfId="95" priority="113">
+  <conditionalFormatting sqref="I5:HU14 I15:BO24">
+    <cfRule type="expression" dxfId="103" priority="127">
+      <formula>I$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="126">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="125">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="124">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="123">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="121">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="114">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="115">
-      <formula>Tényleges</formula>
+    <cfRule type="expression" dxfId="97" priority="132">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="131">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I25:HU30">
+    <cfRule type="expression" dxfId="95" priority="120">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="119">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="118">
+      <formula>I$4=időszak_kiválasztva</formula>
     </cfRule>
     <cfRule type="expression" dxfId="92" priority="116">
       <formula>TénylegTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="117">
+    <cfRule type="expression" dxfId="91" priority="115">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="90" priority="117">
       <formula>Terv</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="118">
-      <formula>BO$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="119">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="120">
-      <formula>MOD(COLUMN(),2)=0</formula>
+    <cfRule type="expression" dxfId="89" priority="114">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="113">
+      <formula>KészültségiSzint</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ15:BQ24">
-    <cfRule type="expression" dxfId="87" priority="81">
+    <cfRule type="expression" dxfId="87" priority="88">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="87">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="86">
+      <formula>BQ$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="85">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="84">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="83">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="82">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="81">
       <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="82">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="83">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="84">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="85">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="86">
-      <formula>BQ$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="87">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="88">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS15:BS24">
-    <cfRule type="expression" dxfId="79" priority="73">
+    <cfRule type="expression" dxfId="79" priority="78">
+      <formula>BS$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="77">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="76">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="75">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="74">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="73">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="74">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="75">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="76">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="77">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="78">
-      <formula>BS$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="79">
+    <cfRule type="expression" dxfId="73" priority="80">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="79">
       <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="80">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU15:BU24">
-    <cfRule type="expression" dxfId="71" priority="65">
+    <cfRule type="expression" dxfId="71" priority="70">
+      <formula>BU$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="69">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="68">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="72">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="65">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="66">
+    <cfRule type="expression" dxfId="66" priority="67">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="66">
       <formula>KészültségiSzintTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="67">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="68">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="69">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="70">
-      <formula>BU$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="71">
+    <cfRule type="expression" dxfId="64" priority="71">
       <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="72">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BW15:BW24">
-    <cfRule type="expression" dxfId="63" priority="57">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="58">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="59">
-      <formula>Tényleges</formula>
+    <cfRule type="expression" dxfId="63" priority="64">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="63">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="62">
+      <formula>BW$4=időszak_kiválasztva</formula>
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="60">
       <formula>TénylegTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="61">
+    <cfRule type="expression" dxfId="59" priority="59">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="58">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="57">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="61">
       <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="62">
-      <formula>BW$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="63">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="64">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BY15:BY24">
-    <cfRule type="expression" dxfId="55" priority="49">
+    <cfRule type="expression" dxfId="55" priority="51">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="52">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="53">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="54">
+      <formula>BY$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="55">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="56">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="49">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="50">
+    <cfRule type="expression" dxfId="48" priority="50">
       <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="51">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="52">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="53">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="54">
-      <formula>BY$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="55">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="56">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CA15:CA24">
-    <cfRule type="expression" dxfId="47" priority="41">
+    <cfRule type="expression" dxfId="47" priority="46">
+      <formula>CA$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="45">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="44">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="43">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="42">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="41">
       <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="42">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="43">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="44">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="45">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="46">
-      <formula>CA$4=időszak_kiválasztva</formula>
     </cfRule>
     <cfRule type="expression" dxfId="41" priority="47">
       <formula>MOD(COLUMN(),2)</formula>
@@ -8271,133 +8406,133 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CC15:CC24">
-    <cfRule type="expression" dxfId="39" priority="33">
+    <cfRule type="expression" dxfId="39" priority="40">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="39">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="38">
+      <formula>CC$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="37">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="36">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="35">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="34">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="33">
       <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="34">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="35">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="36">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="37">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="38">
-      <formula>CC$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="39">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="40">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CE15:CE24">
-    <cfRule type="expression" dxfId="31" priority="25">
+    <cfRule type="expression" dxfId="31" priority="32">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="31">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="30">
+      <formula>CE$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="29">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="28">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="26">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="25">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="26">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="24" priority="27">
       <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="29">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="30">
-      <formula>CE$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="31">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="32">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG15:CG24">
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="23" priority="22">
+      <formula>CG$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="21">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="20">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="19">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="18">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="21">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="22">
-      <formula>CG$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="23">
+    <cfRule type="expression" dxfId="17" priority="24">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="23">
       <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="24">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CI15:CI24">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="15" priority="13">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="12">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>CI$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="10">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="10">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>Tényleges</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="13">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="14">
-      <formula>CI$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="15">
+    <cfRule type="expression" dxfId="9" priority="16">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="16">
-      <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CK24:HU24 CK22:HU22 CK20:HU20 CK18:HU18 CK16:HU16">
+  <conditionalFormatting sqref="CK15:HU24">
     <cfRule type="expression" dxfId="7" priority="1">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>CK$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>KészültségiSzintTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
-      <formula>CK$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1722" yWindow="207" count="16">

--- a/dokumentumok/Ütemterv.xlsx
+++ b/dokumentumok/Ütemterv.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FC4893-D2E6-411A-B8CC-47A2BD697856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546F0AD3-9AA6-4FA9-A2A8-011ABBE90613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projekttervező" sheetId="1" r:id="rId1"/>
@@ -41,60 +41,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Válassza ki a kiemelendő időszakot a jobb oldalon.  A diagram jelmagyarázata következik.</t>
   </si>
   <si>
     <t>TEVÉKENYSÉG</t>
-  </si>
-  <si>
-    <t>Tevékenység 11</t>
-  </si>
-  <si>
-    <t>Tevékenység 12</t>
-  </si>
-  <si>
-    <t>Tevékenység 13</t>
-  </si>
-  <si>
-    <t>Tevékenység 14</t>
-  </si>
-  <si>
-    <t>Tevékenység 15</t>
-  </si>
-  <si>
-    <t>Tevékenység 16</t>
-  </si>
-  <si>
-    <t>Tevékenység 17</t>
-  </si>
-  <si>
-    <t>Tevékenység 18</t>
-  </si>
-  <si>
-    <t>Tevékenység 19</t>
-  </si>
-  <si>
-    <t>Tevékenység 20</t>
-  </si>
-  <si>
-    <t>Tevékenység 21</t>
-  </si>
-  <si>
-    <t>Tevékenység 22</t>
-  </si>
-  <si>
-    <t>Tevékenység 23</t>
-  </si>
-  <si>
-    <t>Tevékenység 24</t>
-  </si>
-  <si>
-    <t>Tevékenység 25</t>
-  </si>
-  <si>
-    <t>Tevékenység 26</t>
   </si>
   <si>
     <t>TERV KEZDETE</t>
@@ -230,6 +182,15 @@
   </si>
   <si>
     <t>PPT megkezdése &amp; bemutatása</t>
+  </si>
+  <si>
+    <t>Webes felület befejezése</t>
+  </si>
+  <si>
+    <t>Dokumentáció befejezése</t>
+  </si>
+  <si>
+    <t>PPT befejezése</t>
   </si>
 </sst>
 </file>
@@ -543,7 +504,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -559,17 +520,8 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="7">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4">
       <alignment horizontal="center" wrapText="1"/>
@@ -634,6 +586,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -676,23 +640,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -719,54 +686,30 @@
   <dxfs count="106">
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -791,30 +734,54 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -833,7 +800,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <border>
@@ -847,7 +814,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
       <border>
@@ -856,45 +823,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -921,7 +849,7 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -934,41 +862,39 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -986,54 +912,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1060,7 +962,46 @@
       <fill>
         <patternFill patternType="lightUp">
           <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
           <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -1084,41 +1025,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1143,30 +1073,54 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1184,54 +1138,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1256,58 +1186,54 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1325,54 +1251,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1397,6 +1299,45 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor theme="9"/>
@@ -1510,9 +1451,9 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -1536,41 +1477,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1595,44 +1525,41 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1650,19 +1577,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor theme="7"/>
@@ -1690,28 +1604,16 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1736,30 +1638,54 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1777,54 +1703,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1849,6 +1751,58 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <fgColor auto="1"/>
           <bgColor theme="7"/>
@@ -1862,54 +1816,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1934,30 +1864,54 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1975,54 +1929,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2047,58 +1977,54 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2116,54 +2042,30 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor auto="1"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="lightUp">
-          <fgColor theme="7"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2184,6 +2086,71 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor theme="7"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2460,7 +2427,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:HU31"/>
-  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="30.1" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.25" defaultRowHeight="30.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" customWidth="1"/>
@@ -2471,7 +2438,7 @@
     <col min="7" max="7" width="17" style="3" customWidth="1"/>
     <col min="8" max="8" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" style="22" customWidth="1"/>
+    <col min="10" max="10" width="7.375" style="19" customWidth="1"/>
     <col min="11" max="11" width="6.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="1" customWidth="1"/>
     <col min="13" max="13" width="5.125" style="1" customWidth="1"/>
@@ -2567,809 +2534,809 @@
     <col min="130" max="236" width="5.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:229" ht="59.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+    <row r="1" spans="2:229" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
+      <c r="B1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
-    <row r="2" spans="2:229" ht="21.1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+    <row r="2" spans="2:229" ht="21.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
       <c r="G2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="14">
+        <v>5</v>
+      </c>
+      <c r="H2" s="11">
         <v>1</v>
       </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="39"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="40"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
     </row>
-    <row r="3" spans="2:229" s="11" customFormat="1" ht="39.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+    <row r="3" spans="2:229" s="8" customFormat="1" ht="39.950000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
+      <c r="C3" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
     </row>
-    <row r="4" spans="2:229" ht="15.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="33"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="26">
+    <row r="4" spans="2:229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="34"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="23">
         <v>45901</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="22">
         <v>45902</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="22">
         <v>45903</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="22">
         <v>45904</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="22">
         <v>45905</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="22">
         <v>45906</v>
       </c>
-      <c r="N4" s="25">
+      <c r="N4" s="22">
         <v>45907</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="22">
         <v>45908</v>
       </c>
-      <c r="P4" s="25">
+      <c r="P4" s="22">
         <v>45909</v>
       </c>
-      <c r="Q4" s="25">
+      <c r="Q4" s="22">
         <v>45910</v>
       </c>
-      <c r="R4" s="25">
+      <c r="R4" s="22">
         <v>45911</v>
       </c>
-      <c r="S4" s="25">
+      <c r="S4" s="22">
         <v>45912</v>
       </c>
-      <c r="T4" s="25">
+      <c r="T4" s="22">
         <v>45913</v>
       </c>
-      <c r="U4" s="25">
+      <c r="U4" s="22">
         <v>45914</v>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="22">
         <v>45915</v>
       </c>
-      <c r="W4" s="25">
+      <c r="W4" s="22">
         <v>45916</v>
       </c>
-      <c r="X4" s="25">
+      <c r="X4" s="22">
         <v>45917</v>
       </c>
-      <c r="Y4" s="25">
+      <c r="Y4" s="22">
         <v>45918</v>
       </c>
-      <c r="Z4" s="25">
+      <c r="Z4" s="22">
         <v>45919</v>
       </c>
-      <c r="AA4" s="25">
+      <c r="AA4" s="22">
         <v>45920</v>
       </c>
-      <c r="AB4" s="25">
+      <c r="AB4" s="22">
         <v>45921</v>
       </c>
-      <c r="AC4" s="25">
+      <c r="AC4" s="22">
         <v>45922</v>
       </c>
-      <c r="AD4" s="25">
+      <c r="AD4" s="22">
         <v>45923</v>
       </c>
-      <c r="AE4" s="25">
+      <c r="AE4" s="22">
         <v>45924</v>
       </c>
-      <c r="AF4" s="25">
+      <c r="AF4" s="22">
         <v>45925</v>
       </c>
-      <c r="AG4" s="25">
+      <c r="AG4" s="22">
         <v>45926</v>
       </c>
-      <c r="AH4" s="25">
+      <c r="AH4" s="22">
         <v>45927</v>
       </c>
-      <c r="AI4" s="25">
+      <c r="AI4" s="22">
         <v>45928</v>
       </c>
-      <c r="AJ4" s="25">
+      <c r="AJ4" s="22">
         <v>45929</v>
       </c>
-      <c r="AK4" s="25">
+      <c r="AK4" s="22">
         <v>45930</v>
       </c>
-      <c r="AL4" s="25">
+      <c r="AL4" s="22">
         <v>45931</v>
       </c>
-      <c r="AM4" s="25">
+      <c r="AM4" s="22">
         <v>45932</v>
       </c>
-      <c r="AN4" s="25">
+      <c r="AN4" s="22">
         <v>45933</v>
       </c>
-      <c r="AO4" s="25">
+      <c r="AO4" s="22">
         <v>45934</v>
       </c>
-      <c r="AP4" s="25">
+      <c r="AP4" s="22">
         <v>45935</v>
       </c>
-      <c r="AQ4" s="25">
+      <c r="AQ4" s="22">
         <v>45936</v>
       </c>
-      <c r="AR4" s="25">
+      <c r="AR4" s="22">
         <v>45937</v>
       </c>
-      <c r="AS4" s="25">
+      <c r="AS4" s="22">
         <v>45938</v>
       </c>
-      <c r="AT4" s="25">
+      <c r="AT4" s="22">
         <v>45939</v>
       </c>
-      <c r="AU4" s="25">
+      <c r="AU4" s="22">
         <v>45940</v>
       </c>
-      <c r="AV4" s="25">
+      <c r="AV4" s="22">
         <v>45941</v>
       </c>
-      <c r="AW4" s="25">
+      <c r="AW4" s="22">
         <v>45942</v>
       </c>
-      <c r="AX4" s="25">
+      <c r="AX4" s="22">
         <v>45943</v>
       </c>
-      <c r="AY4" s="25">
+      <c r="AY4" s="22">
         <v>45944</v>
       </c>
-      <c r="AZ4" s="25">
+      <c r="AZ4" s="22">
         <v>45945</v>
       </c>
-      <c r="BA4" s="25">
+      <c r="BA4" s="22">
         <v>45946</v>
       </c>
-      <c r="BB4" s="25">
+      <c r="BB4" s="22">
         <v>45947</v>
       </c>
-      <c r="BC4" s="25">
+      <c r="BC4" s="22">
         <v>45948</v>
       </c>
-      <c r="BD4" s="25">
+      <c r="BD4" s="22">
         <v>45949</v>
       </c>
-      <c r="BE4" s="25">
+      <c r="BE4" s="22">
         <v>45950</v>
       </c>
-      <c r="BF4" s="25">
+      <c r="BF4" s="22">
         <v>45951</v>
       </c>
-      <c r="BG4" s="25">
+      <c r="BG4" s="22">
         <v>45952</v>
       </c>
-      <c r="BH4" s="25">
+      <c r="BH4" s="22">
         <v>45953</v>
       </c>
-      <c r="BI4" s="25">
+      <c r="BI4" s="22">
         <v>45954</v>
       </c>
-      <c r="BJ4" s="25">
+      <c r="BJ4" s="22">
         <v>45955</v>
       </c>
-      <c r="BK4" s="25">
+      <c r="BK4" s="22">
         <v>45956</v>
       </c>
-      <c r="BL4" s="25">
+      <c r="BL4" s="22">
         <v>45957</v>
       </c>
-      <c r="BM4" s="25">
+      <c r="BM4" s="22">
         <v>45958</v>
       </c>
-      <c r="BN4" s="25">
+      <c r="BN4" s="22">
         <v>45959</v>
       </c>
-      <c r="BO4" s="25">
+      <c r="BO4" s="22">
         <v>45960</v>
       </c>
-      <c r="BP4" s="25">
+      <c r="BP4" s="22">
         <v>45961</v>
       </c>
-      <c r="BQ4" s="25">
+      <c r="BQ4" s="22">
         <v>45962</v>
       </c>
-      <c r="BR4" s="25">
+      <c r="BR4" s="22">
         <v>45963</v>
       </c>
-      <c r="BS4" s="25">
+      <c r="BS4" s="22">
         <v>45964</v>
       </c>
-      <c r="BT4" s="25">
+      <c r="BT4" s="22">
         <v>45965</v>
       </c>
-      <c r="BU4" s="25">
+      <c r="BU4" s="22">
         <v>45966</v>
       </c>
-      <c r="BV4" s="25">
+      <c r="BV4" s="22">
         <v>45967</v>
       </c>
-      <c r="BW4" s="25">
+      <c r="BW4" s="22">
         <v>45968</v>
       </c>
-      <c r="BX4" s="25">
+      <c r="BX4" s="22">
         <v>45969</v>
       </c>
-      <c r="BY4" s="25">
+      <c r="BY4" s="22">
         <v>45970</v>
       </c>
-      <c r="BZ4" s="25">
+      <c r="BZ4" s="22">
         <v>45971</v>
       </c>
-      <c r="CA4" s="25">
+      <c r="CA4" s="22">
         <v>45972</v>
       </c>
-      <c r="CB4" s="25">
+      <c r="CB4" s="22">
         <v>45973</v>
       </c>
-      <c r="CC4" s="25">
+      <c r="CC4" s="22">
         <v>45974</v>
       </c>
-      <c r="CD4" s="25">
+      <c r="CD4" s="22">
         <v>45975</v>
       </c>
-      <c r="CE4" s="25">
+      <c r="CE4" s="22">
         <v>45976</v>
       </c>
-      <c r="CF4" s="25">
+      <c r="CF4" s="22">
         <v>45977</v>
       </c>
-      <c r="CG4" s="25">
+      <c r="CG4" s="22">
         <v>45978</v>
       </c>
-      <c r="CH4" s="25">
+      <c r="CH4" s="22">
         <v>45979</v>
       </c>
-      <c r="CI4" s="25">
+      <c r="CI4" s="22">
         <v>45980</v>
       </c>
-      <c r="CJ4" s="25">
+      <c r="CJ4" s="22">
         <v>45981</v>
       </c>
-      <c r="CK4" s="25">
+      <c r="CK4" s="22">
         <v>45982</v>
       </c>
-      <c r="CL4" s="25">
+      <c r="CL4" s="22">
         <v>45983</v>
       </c>
-      <c r="CM4" s="25">
+      <c r="CM4" s="22">
         <v>45984</v>
       </c>
-      <c r="CN4" s="25">
+      <c r="CN4" s="22">
         <v>45985</v>
       </c>
-      <c r="CO4" s="25">
+      <c r="CO4" s="22">
         <v>45986</v>
       </c>
-      <c r="CP4" s="25">
+      <c r="CP4" s="22">
         <v>45987</v>
       </c>
-      <c r="CQ4" s="25">
+      <c r="CQ4" s="22">
         <v>45988</v>
       </c>
-      <c r="CR4" s="25">
+      <c r="CR4" s="22">
         <v>45989</v>
       </c>
-      <c r="CS4" s="25">
+      <c r="CS4" s="22">
         <v>45990</v>
       </c>
-      <c r="CT4" s="25">
+      <c r="CT4" s="22">
         <v>45991</v>
       </c>
-      <c r="CU4" s="25">
+      <c r="CU4" s="22">
         <v>45992</v>
       </c>
-      <c r="CV4" s="25">
+      <c r="CV4" s="22">
         <v>45993</v>
       </c>
-      <c r="CW4" s="25">
+      <c r="CW4" s="22">
         <v>45994</v>
       </c>
-      <c r="CX4" s="25">
+      <c r="CX4" s="22">
         <v>45995</v>
       </c>
-      <c r="CY4" s="25">
+      <c r="CY4" s="22">
         <v>45996</v>
       </c>
-      <c r="CZ4" s="25">
+      <c r="CZ4" s="22">
         <v>45997</v>
       </c>
-      <c r="DA4" s="25">
+      <c r="DA4" s="22">
         <v>45998</v>
       </c>
-      <c r="DB4" s="25">
+      <c r="DB4" s="22">
         <v>45999</v>
       </c>
-      <c r="DC4" s="25">
+      <c r="DC4" s="22">
         <v>46000</v>
       </c>
-      <c r="DD4" s="25">
+      <c r="DD4" s="22">
         <v>46001</v>
       </c>
-      <c r="DE4" s="25">
+      <c r="DE4" s="22">
         <v>46002</v>
       </c>
-      <c r="DF4" s="25">
+      <c r="DF4" s="22">
         <v>46003</v>
       </c>
-      <c r="DG4" s="25">
+      <c r="DG4" s="22">
         <v>46004</v>
       </c>
-      <c r="DH4" s="25">
+      <c r="DH4" s="22">
         <v>46005</v>
       </c>
-      <c r="DI4" s="25">
+      <c r="DI4" s="22">
         <v>46006</v>
       </c>
-      <c r="DJ4" s="25">
+      <c r="DJ4" s="22">
         <v>46007</v>
       </c>
-      <c r="DK4" s="25">
+      <c r="DK4" s="22">
         <v>46008</v>
       </c>
-      <c r="DL4" s="25">
+      <c r="DL4" s="22">
         <v>46009</v>
       </c>
-      <c r="DM4" s="25">
+      <c r="DM4" s="22">
         <v>46010</v>
       </c>
-      <c r="DN4" s="25">
+      <c r="DN4" s="22">
         <v>46011</v>
       </c>
-      <c r="DO4" s="25">
+      <c r="DO4" s="22">
         <v>46012</v>
       </c>
-      <c r="DP4" s="25">
+      <c r="DP4" s="22">
         <v>46013</v>
       </c>
-      <c r="DQ4" s="25">
+      <c r="DQ4" s="22">
         <v>46014</v>
       </c>
-      <c r="DR4" s="25">
+      <c r="DR4" s="22">
         <v>46015</v>
       </c>
-      <c r="DS4" s="25">
+      <c r="DS4" s="22">
         <v>46016</v>
       </c>
-      <c r="DT4" s="25">
+      <c r="DT4" s="22">
         <v>46017</v>
       </c>
-      <c r="DU4" s="25">
+      <c r="DU4" s="22">
         <v>46018</v>
       </c>
-      <c r="DV4" s="25">
+      <c r="DV4" s="22">
         <v>46019</v>
       </c>
-      <c r="DW4" s="25">
+      <c r="DW4" s="22">
         <v>46020</v>
       </c>
-      <c r="DX4" s="25">
+      <c r="DX4" s="22">
         <v>46021</v>
       </c>
-      <c r="DY4" s="25">
+      <c r="DY4" s="22">
         <v>46022</v>
       </c>
-      <c r="DZ4" s="25">
+      <c r="DZ4" s="22">
         <v>46023</v>
       </c>
-      <c r="EA4" s="25">
+      <c r="EA4" s="22">
         <v>46024</v>
       </c>
-      <c r="EB4" s="25">
+      <c r="EB4" s="22">
         <v>46025</v>
       </c>
-      <c r="EC4" s="25">
+      <c r="EC4" s="22">
         <v>46026</v>
       </c>
-      <c r="ED4" s="25">
+      <c r="ED4" s="22">
         <v>46027</v>
       </c>
-      <c r="EE4" s="25">
+      <c r="EE4" s="22">
         <v>46028</v>
       </c>
-      <c r="EF4" s="25">
+      <c r="EF4" s="22">
         <v>46029</v>
       </c>
-      <c r="EG4" s="25">
+      <c r="EG4" s="22">
         <v>46030</v>
       </c>
-      <c r="EH4" s="25">
+      <c r="EH4" s="22">
         <v>46031</v>
       </c>
-      <c r="EI4" s="25">
+      <c r="EI4" s="22">
         <v>46032</v>
       </c>
-      <c r="EJ4" s="25">
+      <c r="EJ4" s="22">
         <v>46033</v>
       </c>
-      <c r="EK4" s="25">
+      <c r="EK4" s="22">
         <v>46034</v>
       </c>
-      <c r="EL4" s="25">
+      <c r="EL4" s="22">
         <v>46035</v>
       </c>
-      <c r="EM4" s="25">
+      <c r="EM4" s="22">
         <v>46036</v>
       </c>
-      <c r="EN4" s="25">
+      <c r="EN4" s="22">
         <v>46037</v>
       </c>
-      <c r="EO4" s="25">
+      <c r="EO4" s="22">
         <v>46038</v>
       </c>
-      <c r="EP4" s="25">
+      <c r="EP4" s="22">
         <v>46039</v>
       </c>
-      <c r="EQ4" s="25">
+      <c r="EQ4" s="22">
         <v>46040</v>
       </c>
-      <c r="ER4" s="25">
+      <c r="ER4" s="22">
         <v>46041</v>
       </c>
-      <c r="ES4" s="25">
+      <c r="ES4" s="22">
         <v>46042</v>
       </c>
-      <c r="ET4" s="25">
+      <c r="ET4" s="22">
         <v>46043</v>
       </c>
-      <c r="EU4" s="25">
+      <c r="EU4" s="22">
         <v>46044</v>
       </c>
-      <c r="EV4" s="25">
+      <c r="EV4" s="22">
         <v>46045</v>
       </c>
-      <c r="EW4" s="25">
+      <c r="EW4" s="22">
         <v>46046</v>
       </c>
-      <c r="EX4" s="25">
+      <c r="EX4" s="22">
         <v>46047</v>
       </c>
-      <c r="EY4" s="25">
+      <c r="EY4" s="22">
         <v>46048</v>
       </c>
-      <c r="EZ4" s="25">
+      <c r="EZ4" s="22">
         <v>46049</v>
       </c>
-      <c r="FA4" s="25">
+      <c r="FA4" s="22">
         <v>46050</v>
       </c>
-      <c r="FB4" s="25">
+      <c r="FB4" s="22">
         <v>46051</v>
       </c>
-      <c r="FC4" s="25">
+      <c r="FC4" s="22">
         <v>46052</v>
       </c>
-      <c r="FD4" s="25">
+      <c r="FD4" s="22">
         <v>46053</v>
       </c>
-      <c r="FE4" s="25">
+      <c r="FE4" s="22">
         <v>46054</v>
       </c>
-      <c r="FF4" s="25">
+      <c r="FF4" s="22">
         <v>46055</v>
       </c>
-      <c r="FG4" s="25">
+      <c r="FG4" s="22">
         <v>46056</v>
       </c>
-      <c r="FH4" s="25">
+      <c r="FH4" s="22">
         <v>46057</v>
       </c>
-      <c r="FI4" s="25">
+      <c r="FI4" s="22">
         <v>46058</v>
       </c>
-      <c r="FJ4" s="25">
+      <c r="FJ4" s="22">
         <v>46059</v>
       </c>
-      <c r="FK4" s="25">
+      <c r="FK4" s="22">
         <v>46060</v>
       </c>
-      <c r="FL4" s="25">
+      <c r="FL4" s="22">
         <v>46061</v>
       </c>
-      <c r="FM4" s="25">
+      <c r="FM4" s="22">
         <v>46062</v>
       </c>
-      <c r="FN4" s="25">
+      <c r="FN4" s="22">
         <v>46063</v>
       </c>
-      <c r="FO4" s="25">
+      <c r="FO4" s="22">
         <v>46064</v>
       </c>
-      <c r="FP4" s="25">
+      <c r="FP4" s="22">
         <v>46065</v>
       </c>
-      <c r="FQ4" s="25">
+      <c r="FQ4" s="22">
         <v>46066</v>
       </c>
-      <c r="FR4" s="25">
+      <c r="FR4" s="22">
         <v>46067</v>
       </c>
-      <c r="FS4" s="25">
+      <c r="FS4" s="22">
         <v>46068</v>
       </c>
-      <c r="FT4" s="25">
+      <c r="FT4" s="22">
         <v>46069</v>
       </c>
-      <c r="FU4" s="25">
+      <c r="FU4" s="22">
         <v>46070</v>
       </c>
-      <c r="FV4" s="25">
+      <c r="FV4" s="22">
         <v>46071</v>
       </c>
-      <c r="FW4" s="25">
+      <c r="FW4" s="22">
         <v>46072</v>
       </c>
-      <c r="FX4" s="25">
+      <c r="FX4" s="22">
         <v>46073</v>
       </c>
-      <c r="FY4" s="25">
+      <c r="FY4" s="22">
         <v>46074</v>
       </c>
-      <c r="FZ4" s="25">
+      <c r="FZ4" s="22">
         <v>46075</v>
       </c>
-      <c r="GA4" s="25">
+      <c r="GA4" s="22">
         <v>46076</v>
       </c>
-      <c r="GB4" s="25">
+      <c r="GB4" s="22">
         <v>46077</v>
       </c>
-      <c r="GC4" s="25">
+      <c r="GC4" s="22">
         <v>46078</v>
       </c>
-      <c r="GD4" s="25">
+      <c r="GD4" s="22">
         <v>46079</v>
       </c>
-      <c r="GE4" s="25">
+      <c r="GE4" s="22">
         <v>46080</v>
       </c>
-      <c r="GF4" s="25">
+      <c r="GF4" s="22">
         <v>46081</v>
       </c>
-      <c r="GG4" s="25">
+      <c r="GG4" s="22">
         <v>46082</v>
       </c>
-      <c r="GH4" s="25">
+      <c r="GH4" s="22">
         <v>46083</v>
       </c>
-      <c r="GI4" s="25">
+      <c r="GI4" s="22">
         <v>46084</v>
       </c>
-      <c r="GJ4" s="25">
+      <c r="GJ4" s="22">
         <v>46085</v>
       </c>
-      <c r="GK4" s="25">
+      <c r="GK4" s="22">
         <v>46086</v>
       </c>
-      <c r="GL4" s="25">
+      <c r="GL4" s="22">
         <v>46087</v>
       </c>
-      <c r="GM4" s="25">
+      <c r="GM4" s="22">
         <v>46088</v>
       </c>
-      <c r="GN4" s="25">
+      <c r="GN4" s="22">
         <v>46089</v>
       </c>
-      <c r="GO4" s="25">
+      <c r="GO4" s="22">
         <v>46090</v>
       </c>
-      <c r="GP4" s="25">
+      <c r="GP4" s="22">
         <v>46091</v>
       </c>
-      <c r="GQ4" s="25">
+      <c r="GQ4" s="22">
         <v>46092</v>
       </c>
-      <c r="GR4" s="25">
+      <c r="GR4" s="22">
         <v>46093</v>
       </c>
-      <c r="GS4" s="25">
+      <c r="GS4" s="22">
         <v>46094</v>
       </c>
-      <c r="GT4" s="25">
+      <c r="GT4" s="22">
         <v>46095</v>
       </c>
-      <c r="GU4" s="25">
+      <c r="GU4" s="22">
         <v>46096</v>
       </c>
-      <c r="GV4" s="25">
+      <c r="GV4" s="22">
         <v>46097</v>
       </c>
-      <c r="GW4" s="25">
+      <c r="GW4" s="22">
         <v>46098</v>
       </c>
-      <c r="GX4" s="25">
+      <c r="GX4" s="22">
         <v>46099</v>
       </c>
-      <c r="GY4" s="25">
+      <c r="GY4" s="22">
         <v>46100</v>
       </c>
-      <c r="GZ4" s="25">
+      <c r="GZ4" s="22">
         <v>46101</v>
       </c>
-      <c r="HA4" s="25">
+      <c r="HA4" s="22">
         <v>46102</v>
       </c>
-      <c r="HB4" s="25">
+      <c r="HB4" s="22">
         <v>46103</v>
       </c>
-      <c r="HC4" s="25">
+      <c r="HC4" s="22">
         <v>46104</v>
       </c>
-      <c r="HD4" s="25">
+      <c r="HD4" s="22">
         <v>46105</v>
       </c>
-      <c r="HE4" s="25">
+      <c r="HE4" s="22">
         <v>46106</v>
       </c>
-      <c r="HF4" s="25">
+      <c r="HF4" s="22">
         <v>46107</v>
       </c>
-      <c r="HG4" s="25">
+      <c r="HG4" s="22">
         <v>46108</v>
       </c>
-      <c r="HH4" s="25">
+      <c r="HH4" s="22">
         <v>46109</v>
       </c>
-      <c r="HI4" s="25">
+      <c r="HI4" s="22">
         <v>46110</v>
       </c>
-      <c r="HJ4" s="25">
+      <c r="HJ4" s="22">
         <v>46111</v>
       </c>
-      <c r="HK4" s="25">
+      <c r="HK4" s="22">
         <v>46112</v>
       </c>
-      <c r="HL4" s="25">
+      <c r="HL4" s="22">
         <v>46113</v>
       </c>
-      <c r="HM4" s="25">
+      <c r="HM4" s="22">
         <v>46114</v>
       </c>
-      <c r="HN4" s="25">
+      <c r="HN4" s="22">
         <v>46115</v>
       </c>
-      <c r="HO4" s="25">
+      <c r="HO4" s="22">
         <v>46116</v>
       </c>
-      <c r="HP4" s="25">
+      <c r="HP4" s="22">
         <v>46117</v>
       </c>
-      <c r="HQ4" s="25">
+      <c r="HQ4" s="22">
         <v>46118</v>
       </c>
-      <c r="HR4" s="25">
+      <c r="HR4" s="22">
         <v>46119</v>
       </c>
-      <c r="HS4" s="25">
+      <c r="HS4" s="22">
         <v>46120</v>
       </c>
-      <c r="HT4" s="25">
+      <c r="HT4" s="22">
         <v>46121</v>
       </c>
-      <c r="HU4" s="25">
+      <c r="HU4" s="22">
         <v>46122</v>
       </c>
     </row>
-    <row r="5" spans="2:229" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="47">
+    <row r="5" spans="2:229" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="29">
         <v>45902</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="30">
         <v>35</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="29">
         <v>45903</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="45">
         <v>31</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="5">
         <v>1</v>
       </c>
-      <c r="H5" s="27"/>
+      <c r="H5" s="24"/>
       <c r="J5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -3574,26 +3541,26 @@
       <c r="HT5" s="1"/>
       <c r="HU5" s="1"/>
     </row>
-    <row r="6" spans="2:229" ht="37.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="47">
+    <row r="6" spans="2:229" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="29">
         <v>45937</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="30">
         <v>32</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="29">
         <v>45938</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="45">
         <v>32</v>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="H6" s="28"/>
+      <c r="H6" s="25"/>
       <c r="J6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
@@ -3798,26 +3765,26 @@
       <c r="HT6" s="1"/>
       <c r="HU6" s="1"/>
     </row>
-    <row r="7" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="47">
+    <row r="7" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="29">
         <v>45973</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="30">
         <v>14</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="29">
         <v>45975</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="45">
         <v>13</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="5">
         <v>1</v>
       </c>
-      <c r="H7" s="28"/>
+      <c r="H7" s="25"/>
       <c r="J7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
@@ -4022,26 +3989,26 @@
       <c r="HT7" s="1"/>
       <c r="HU7" s="1"/>
     </row>
-    <row r="8" spans="2:229" ht="38.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="47">
+    <row r="8" spans="2:229" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="29">
         <v>45968</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="30">
         <v>36</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="29">
         <v>45969</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="45">
         <v>33</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="5">
         <v>1</v>
       </c>
-      <c r="H8" s="28"/>
+      <c r="H8" s="25"/>
       <c r="J8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -4246,26 +4213,26 @@
       <c r="HT8" s="1"/>
       <c r="HU8" s="1"/>
     </row>
-    <row r="9" spans="2:229" ht="42.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="47">
+    <row r="9" spans="2:229" ht="42.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="29">
         <v>46007</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="30">
         <v>47</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="29">
         <v>46007</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="45">
         <v>47</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="5">
         <v>1</v>
       </c>
-      <c r="H9" s="28"/>
+      <c r="H9" s="25"/>
       <c r="J9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -4470,26 +4437,26 @@
       <c r="HT9" s="1"/>
       <c r="HU9" s="1"/>
     </row>
-    <row r="10" spans="2:229" ht="42.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="47">
+    <row r="10" spans="2:229" ht="42.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="29">
         <v>46054</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="30">
         <v>14</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="29">
         <v>46054</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="45">
         <v>14</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="5">
         <v>1</v>
       </c>
-      <c r="H10" s="28"/>
+      <c r="H10" s="25"/>
       <c r="J10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
@@ -4694,26 +4661,26 @@
       <c r="HT10" s="1"/>
       <c r="HU10" s="1"/>
     </row>
-    <row r="11" spans="2:229" ht="37.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="47">
+    <row r="11" spans="2:229" ht="37.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="29">
         <v>46068</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="30">
         <v>14</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="29">
         <v>46068</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="45">
         <v>14</v>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="5">
         <v>1</v>
       </c>
-      <c r="H11" s="28"/>
+      <c r="H11" s="25"/>
       <c r="J11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
@@ -4918,26 +4885,26 @@
       <c r="HT11" s="1"/>
       <c r="HU11" s="1"/>
     </row>
-    <row r="12" spans="2:229" ht="35.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="47">
+    <row r="12" spans="2:229" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="29">
         <v>46083</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="30">
         <v>7</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="29">
         <v>46083</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="45">
         <v>7</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="5">
         <v>1</v>
       </c>
-      <c r="H12" s="28"/>
+      <c r="H12" s="25"/>
       <c r="J12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
@@ -5142,16 +5109,26 @@
       <c r="HT12" s="1"/>
       <c r="HU12" s="1"/>
     </row>
-    <row r="13" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="44"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="49">
-        <v>0</v>
-      </c>
-      <c r="H13" s="28"/>
+    <row r="13" spans="2:229" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="48">
+        <v>46091</v>
+      </c>
+      <c r="D13" s="45">
+        <v>14</v>
+      </c>
+      <c r="E13" s="48">
+        <v>46091</v>
+      </c>
+      <c r="F13" s="45">
+        <v>10</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="25"/>
       <c r="J13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
@@ -5356,16 +5333,26 @@
       <c r="HT13" s="1"/>
       <c r="HU13" s="1"/>
     </row>
-    <row r="14" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="45"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="49">
-        <v>0</v>
-      </c>
-      <c r="H14" s="28"/>
+    <row r="14" spans="2:229" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="48">
+        <v>46105</v>
+      </c>
+      <c r="D14" s="45">
+        <v>7</v>
+      </c>
+      <c r="E14" s="48">
+        <v>46105</v>
+      </c>
+      <c r="F14" s="45">
+        <v>6</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="25"/>
       <c r="J14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -5570,2176 +5557,1996 @@
       <c r="HT14" s="1"/>
       <c r="HU14" s="1"/>
     </row>
-    <row r="15" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="28"/>
-      <c r="BQ15" s="29"/>
-      <c r="BS15" s="29"/>
-      <c r="BU15" s="29"/>
-      <c r="BW15" s="29"/>
-      <c r="BY15" s="29"/>
-      <c r="CA15" s="29"/>
-      <c r="CC15" s="29"/>
-      <c r="CE15" s="29"/>
-      <c r="CG15" s="29"/>
-      <c r="CI15" s="29"/>
-      <c r="CK15" s="29"/>
-      <c r="CL15" s="29"/>
-      <c r="CM15" s="29"/>
-      <c r="CN15" s="29"/>
-      <c r="CO15" s="29"/>
-      <c r="CP15" s="29"/>
-      <c r="CQ15" s="29"/>
-      <c r="CR15" s="29"/>
-      <c r="CS15" s="29"/>
-      <c r="CT15" s="29"/>
-      <c r="CU15" s="29"/>
-      <c r="CV15" s="29"/>
-      <c r="CW15" s="29"/>
-      <c r="CX15" s="29"/>
-      <c r="CY15" s="29"/>
-      <c r="CZ15" s="29"/>
-      <c r="DA15" s="29"/>
-      <c r="DB15" s="29"/>
-      <c r="DC15" s="29"/>
-      <c r="DD15" s="29"/>
-      <c r="DE15" s="29"/>
-      <c r="DF15" s="29"/>
-      <c r="DG15" s="29"/>
-      <c r="DH15" s="29"/>
-      <c r="DI15" s="29"/>
-      <c r="DJ15" s="29"/>
-      <c r="DK15" s="29"/>
-      <c r="DL15" s="29"/>
-      <c r="DM15" s="29"/>
-      <c r="DN15" s="29"/>
-      <c r="DO15" s="29"/>
-      <c r="DP15" s="29"/>
-      <c r="DQ15" s="29"/>
-      <c r="DR15" s="29"/>
-      <c r="DS15" s="29"/>
-      <c r="DT15" s="29"/>
-      <c r="DU15" s="29"/>
-      <c r="DV15" s="29"/>
-      <c r="DW15" s="29"/>
-      <c r="DX15" s="29"/>
-      <c r="DY15" s="29"/>
-      <c r="DZ15" s="29"/>
-      <c r="EA15" s="29"/>
-      <c r="EB15" s="29"/>
-      <c r="EC15" s="29"/>
-      <c r="ED15" s="29"/>
-      <c r="EE15" s="29"/>
-      <c r="EF15" s="29"/>
-      <c r="EG15" s="29"/>
-      <c r="EH15" s="29"/>
-      <c r="EI15" s="29"/>
-      <c r="EJ15" s="29"/>
-      <c r="EK15" s="29"/>
-      <c r="EL15" s="29"/>
-      <c r="EM15" s="29"/>
-      <c r="EN15" s="29"/>
-      <c r="EO15" s="29"/>
-      <c r="EP15" s="29"/>
-      <c r="EQ15" s="29"/>
-      <c r="ER15" s="29"/>
-      <c r="ES15" s="29"/>
-      <c r="ET15" s="29"/>
-      <c r="EU15" s="29"/>
-      <c r="EV15" s="29"/>
-      <c r="EW15" s="29"/>
-      <c r="EX15" s="29"/>
-      <c r="EY15" s="29"/>
-      <c r="EZ15" s="29"/>
-      <c r="FA15" s="29"/>
-      <c r="FB15" s="29"/>
-      <c r="FC15" s="29"/>
-      <c r="FD15" s="29"/>
-      <c r="FE15" s="29"/>
-      <c r="FF15" s="29"/>
-      <c r="FG15" s="29"/>
-      <c r="FH15" s="29"/>
-      <c r="FI15" s="29"/>
-      <c r="FJ15" s="29"/>
-      <c r="FK15" s="29"/>
-      <c r="FL15" s="29"/>
-      <c r="FM15" s="29"/>
-      <c r="FN15" s="29"/>
-      <c r="FO15" s="29"/>
-      <c r="FP15" s="29"/>
-      <c r="FQ15" s="29"/>
-      <c r="FR15" s="29"/>
-      <c r="FS15" s="29"/>
-      <c r="FT15" s="29"/>
-      <c r="FU15" s="29"/>
-      <c r="FV15" s="29"/>
-      <c r="FW15" s="29"/>
-      <c r="FX15" s="29"/>
-      <c r="FY15" s="29"/>
-      <c r="FZ15" s="29"/>
-      <c r="GA15" s="29"/>
-      <c r="GB15" s="29"/>
-      <c r="GC15" s="29"/>
-      <c r="GD15" s="29"/>
-      <c r="GE15" s="29"/>
-      <c r="GF15" s="29"/>
-      <c r="GG15" s="29"/>
-      <c r="GH15" s="29"/>
-      <c r="GI15" s="29"/>
-      <c r="GJ15" s="29"/>
-      <c r="GK15" s="29"/>
-      <c r="GL15" s="29"/>
-      <c r="GM15" s="29"/>
-      <c r="GN15" s="29"/>
-      <c r="GO15" s="29"/>
-      <c r="GP15" s="29"/>
-      <c r="GQ15" s="29"/>
-      <c r="GR15" s="29"/>
-      <c r="GS15" s="29"/>
-      <c r="GT15" s="29"/>
-      <c r="GU15" s="29"/>
-      <c r="GV15" s="29"/>
-      <c r="GW15" s="29"/>
-      <c r="GX15" s="29"/>
-      <c r="GY15" s="29"/>
-      <c r="GZ15" s="29"/>
-      <c r="HA15" s="29"/>
-      <c r="HB15" s="29"/>
-      <c r="HC15" s="29"/>
-      <c r="HD15" s="29"/>
-      <c r="HE15" s="29"/>
-      <c r="HF15" s="29"/>
-      <c r="HG15" s="29"/>
-      <c r="HH15" s="29"/>
-      <c r="HI15" s="29"/>
-      <c r="HJ15" s="29"/>
-      <c r="HK15" s="29"/>
-      <c r="HL15" s="29"/>
-      <c r="HM15" s="29"/>
-      <c r="HN15" s="29"/>
-      <c r="HO15" s="29"/>
-      <c r="HP15" s="29"/>
-      <c r="HQ15" s="29"/>
-      <c r="HR15" s="29"/>
-      <c r="HS15" s="29"/>
-      <c r="HT15" s="29"/>
-      <c r="HU15" s="29"/>
+    <row r="15" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="47">
+        <v>46113</v>
+      </c>
+      <c r="D15" s="45">
+        <v>10</v>
+      </c>
+      <c r="E15" s="48">
+        <v>46113</v>
+      </c>
+      <c r="F15" s="45">
+        <v>10</v>
+      </c>
+      <c r="G15" s="46">
+        <v>1</v>
+      </c>
+      <c r="H15" s="25"/>
+      <c r="BQ15" s="26"/>
+      <c r="BS15" s="26"/>
+      <c r="BU15" s="26"/>
+      <c r="BW15" s="26"/>
+      <c r="BY15" s="26"/>
+      <c r="CA15" s="26"/>
+      <c r="CC15" s="26"/>
+      <c r="CE15" s="26"/>
+      <c r="CG15" s="26"/>
+      <c r="CI15" s="26"/>
+      <c r="CK15" s="26"/>
+      <c r="CL15" s="26"/>
+      <c r="CM15" s="26"/>
+      <c r="CN15" s="26"/>
+      <c r="CO15" s="26"/>
+      <c r="CP15" s="26"/>
+      <c r="CQ15" s="26"/>
+      <c r="CR15" s="26"/>
+      <c r="CS15" s="26"/>
+      <c r="CT15" s="26"/>
+      <c r="CU15" s="26"/>
+      <c r="CV15" s="26"/>
+      <c r="CW15" s="26"/>
+      <c r="CX15" s="26"/>
+      <c r="CY15" s="26"/>
+      <c r="CZ15" s="26"/>
+      <c r="DA15" s="26"/>
+      <c r="DB15" s="26"/>
+      <c r="DC15" s="26"/>
+      <c r="DD15" s="26"/>
+      <c r="DE15" s="26"/>
+      <c r="DF15" s="26"/>
+      <c r="DG15" s="26"/>
+      <c r="DH15" s="26"/>
+      <c r="DI15" s="26"/>
+      <c r="DJ15" s="26"/>
+      <c r="DK15" s="26"/>
+      <c r="DL15" s="26"/>
+      <c r="DM15" s="26"/>
+      <c r="DN15" s="26"/>
+      <c r="DO15" s="26"/>
+      <c r="DP15" s="26"/>
+      <c r="DQ15" s="26"/>
+      <c r="DR15" s="26"/>
+      <c r="DS15" s="26"/>
+      <c r="DT15" s="26"/>
+      <c r="DU15" s="26"/>
+      <c r="DV15" s="26"/>
+      <c r="DW15" s="26"/>
+      <c r="DX15" s="26"/>
+      <c r="DY15" s="26"/>
+      <c r="DZ15" s="26"/>
+      <c r="EA15" s="26"/>
+      <c r="EB15" s="26"/>
+      <c r="EC15" s="26"/>
+      <c r="ED15" s="26"/>
+      <c r="EE15" s="26"/>
+      <c r="EF15" s="26"/>
+      <c r="EG15" s="26"/>
+      <c r="EH15" s="26"/>
+      <c r="EI15" s="26"/>
+      <c r="EJ15" s="26"/>
+      <c r="EK15" s="26"/>
+      <c r="EL15" s="26"/>
+      <c r="EM15" s="26"/>
+      <c r="EN15" s="26"/>
+      <c r="EO15" s="26"/>
+      <c r="EP15" s="26"/>
+      <c r="EQ15" s="26"/>
+      <c r="ER15" s="26"/>
+      <c r="ES15" s="26"/>
+      <c r="ET15" s="26"/>
+      <c r="EU15" s="26"/>
+      <c r="EV15" s="26"/>
+      <c r="EW15" s="26"/>
+      <c r="EX15" s="26"/>
+      <c r="EY15" s="26"/>
+      <c r="EZ15" s="26"/>
+      <c r="FA15" s="26"/>
+      <c r="FB15" s="26"/>
+      <c r="FC15" s="26"/>
+      <c r="FD15" s="26"/>
+      <c r="FE15" s="26"/>
+      <c r="FF15" s="26"/>
+      <c r="FG15" s="26"/>
+      <c r="FH15" s="26"/>
+      <c r="FI15" s="26"/>
+      <c r="FJ15" s="26"/>
+      <c r="FK15" s="26"/>
+      <c r="FL15" s="26"/>
+      <c r="FM15" s="26"/>
+      <c r="FN15" s="26"/>
+      <c r="FO15" s="26"/>
+      <c r="FP15" s="26"/>
+      <c r="FQ15" s="26"/>
+      <c r="FR15" s="26"/>
+      <c r="FS15" s="26"/>
+      <c r="FT15" s="26"/>
+      <c r="FU15" s="26"/>
+      <c r="FV15" s="26"/>
+      <c r="FW15" s="26"/>
+      <c r="FX15" s="26"/>
+      <c r="FY15" s="26"/>
+      <c r="FZ15" s="26"/>
+      <c r="GA15" s="26"/>
+      <c r="GB15" s="26"/>
+      <c r="GC15" s="26"/>
+      <c r="GD15" s="26"/>
+      <c r="GE15" s="26"/>
+      <c r="GF15" s="26"/>
+      <c r="GG15" s="26"/>
+      <c r="GH15" s="26"/>
+      <c r="GI15" s="26"/>
+      <c r="GJ15" s="26"/>
+      <c r="GK15" s="26"/>
+      <c r="GL15" s="26"/>
+      <c r="GM15" s="26"/>
+      <c r="GN15" s="26"/>
+      <c r="GO15" s="26"/>
+      <c r="GP15" s="26"/>
+      <c r="GQ15" s="26"/>
+      <c r="GR15" s="26"/>
+      <c r="GS15" s="26"/>
+      <c r="GT15" s="26"/>
+      <c r="GU15" s="26"/>
+      <c r="GV15" s="26"/>
+      <c r="GW15" s="26"/>
+      <c r="GX15" s="26"/>
+      <c r="GY15" s="26"/>
+      <c r="GZ15" s="26"/>
+      <c r="HA15" s="26"/>
+      <c r="HB15" s="26"/>
+      <c r="HC15" s="26"/>
+      <c r="HD15" s="26"/>
+      <c r="HE15" s="26"/>
+      <c r="HF15" s="26"/>
+      <c r="HG15" s="26"/>
+      <c r="HH15" s="26"/>
+      <c r="HI15" s="26"/>
+      <c r="HJ15" s="26"/>
+      <c r="HK15" s="26"/>
+      <c r="HL15" s="26"/>
+      <c r="HM15" s="26"/>
+      <c r="HN15" s="26"/>
+      <c r="HO15" s="26"/>
+      <c r="HP15" s="26"/>
+      <c r="HQ15" s="26"/>
+      <c r="HR15" s="26"/>
+      <c r="HS15" s="26"/>
+      <c r="HT15" s="26"/>
+      <c r="HU15" s="26"/>
     </row>
-    <row r="16" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="28"/>
-      <c r="BQ16" s="29"/>
-      <c r="BS16" s="29"/>
-      <c r="BU16" s="29"/>
-      <c r="BW16" s="29"/>
-      <c r="BY16" s="29"/>
-      <c r="CA16" s="29"/>
-      <c r="CC16" s="29"/>
-      <c r="CE16" s="29"/>
-      <c r="CG16" s="29"/>
-      <c r="CI16" s="29"/>
-      <c r="CK16" s="29"/>
-      <c r="CL16" s="29"/>
-      <c r="CM16" s="29"/>
-      <c r="CN16" s="29"/>
-      <c r="CO16" s="29"/>
-      <c r="CP16" s="29"/>
-      <c r="CQ16" s="29"/>
-      <c r="CR16" s="29"/>
-      <c r="CS16" s="29"/>
-      <c r="CT16" s="29"/>
-      <c r="CU16" s="29"/>
-      <c r="CV16" s="29"/>
-      <c r="CW16" s="29"/>
-      <c r="CX16" s="29"/>
-      <c r="CY16" s="29"/>
-      <c r="CZ16" s="29"/>
-      <c r="DA16" s="29"/>
-      <c r="DB16" s="29"/>
-      <c r="DC16" s="29"/>
-      <c r="DD16" s="29"/>
-      <c r="DE16" s="29"/>
-      <c r="DF16" s="29"/>
-      <c r="DG16" s="29"/>
-      <c r="DH16" s="29"/>
-      <c r="DI16" s="29"/>
-      <c r="DJ16" s="29"/>
-      <c r="DK16" s="29"/>
-      <c r="DL16" s="29"/>
-      <c r="DM16" s="29"/>
-      <c r="DN16" s="29"/>
-      <c r="DO16" s="29"/>
-      <c r="DP16" s="29"/>
-      <c r="DQ16" s="29"/>
-      <c r="DR16" s="29"/>
-      <c r="DS16" s="29"/>
-      <c r="DT16" s="29"/>
-      <c r="DU16" s="29"/>
-      <c r="DV16" s="29"/>
-      <c r="DW16" s="29"/>
-      <c r="DX16" s="29"/>
-      <c r="DY16" s="29"/>
-      <c r="DZ16" s="29"/>
-      <c r="EA16" s="29"/>
-      <c r="EB16" s="29"/>
-      <c r="EC16" s="29"/>
-      <c r="ED16" s="29"/>
-      <c r="EE16" s="29"/>
-      <c r="EF16" s="29"/>
-      <c r="EG16" s="29"/>
-      <c r="EH16" s="29"/>
-      <c r="EI16" s="29"/>
-      <c r="EJ16" s="29"/>
-      <c r="EK16" s="29"/>
-      <c r="EL16" s="29"/>
-      <c r="EM16" s="29"/>
-      <c r="EN16" s="29"/>
-      <c r="EO16" s="29"/>
-      <c r="EP16" s="29"/>
-      <c r="EQ16" s="29"/>
-      <c r="ER16" s="29"/>
-      <c r="ES16" s="29"/>
-      <c r="ET16" s="29"/>
-      <c r="EU16" s="29"/>
-      <c r="EV16" s="29"/>
-      <c r="EW16" s="29"/>
-      <c r="EX16" s="29"/>
-      <c r="EY16" s="29"/>
-      <c r="EZ16" s="29"/>
-      <c r="FA16" s="29"/>
-      <c r="FB16" s="29"/>
-      <c r="FC16" s="29"/>
-      <c r="FD16" s="29"/>
-      <c r="FE16" s="29"/>
-      <c r="FF16" s="29"/>
-      <c r="FG16" s="29"/>
-      <c r="FH16" s="29"/>
-      <c r="FI16" s="29"/>
-      <c r="FJ16" s="29"/>
-      <c r="FK16" s="29"/>
-      <c r="FL16" s="29"/>
-      <c r="FM16" s="29"/>
-      <c r="FN16" s="29"/>
-      <c r="FO16" s="29"/>
-      <c r="FP16" s="29"/>
-      <c r="FQ16" s="29"/>
-      <c r="FR16" s="29"/>
-      <c r="FS16" s="29"/>
-      <c r="FT16" s="29"/>
-      <c r="FU16" s="29"/>
-      <c r="FV16" s="29"/>
-      <c r="FW16" s="29"/>
-      <c r="FX16" s="29"/>
-      <c r="FY16" s="29"/>
-      <c r="FZ16" s="29"/>
-      <c r="GA16" s="29"/>
-      <c r="GB16" s="29"/>
-      <c r="GC16" s="29"/>
-      <c r="GD16" s="29"/>
-      <c r="GE16" s="29"/>
-      <c r="GF16" s="29"/>
-      <c r="GG16" s="29"/>
-      <c r="GH16" s="29"/>
-      <c r="GI16" s="29"/>
-      <c r="GJ16" s="29"/>
-      <c r="GK16" s="29"/>
-      <c r="GL16" s="29"/>
-      <c r="GM16" s="29"/>
-      <c r="GN16" s="29"/>
-      <c r="GO16" s="29"/>
-      <c r="GP16" s="29"/>
-      <c r="GQ16" s="29"/>
-      <c r="GR16" s="29"/>
-      <c r="GS16" s="29"/>
-      <c r="GT16" s="29"/>
-      <c r="GU16" s="29"/>
-      <c r="GV16" s="29"/>
-      <c r="GW16" s="29"/>
-      <c r="GX16" s="29"/>
-      <c r="GY16" s="29"/>
-      <c r="GZ16" s="29"/>
-      <c r="HA16" s="29"/>
-      <c r="HB16" s="29"/>
-      <c r="HC16" s="29"/>
-      <c r="HD16" s="29"/>
-      <c r="HE16" s="29"/>
-      <c r="HF16" s="29"/>
-      <c r="HG16" s="29"/>
-      <c r="HH16" s="29"/>
-      <c r="HI16" s="29"/>
-      <c r="HJ16" s="29"/>
-      <c r="HK16" s="29"/>
-      <c r="HL16" s="29"/>
-      <c r="HM16" s="29"/>
-      <c r="HN16" s="29"/>
-      <c r="HO16" s="29"/>
-      <c r="HP16" s="29"/>
-      <c r="HQ16" s="29"/>
-      <c r="HR16" s="29"/>
-      <c r="HS16" s="29"/>
-      <c r="HT16" s="29"/>
-      <c r="HU16" s="29"/>
+    <row r="16" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="27"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="25"/>
+      <c r="BQ16" s="26"/>
+      <c r="BS16" s="26"/>
+      <c r="BU16" s="26"/>
+      <c r="BW16" s="26"/>
+      <c r="BY16" s="26"/>
+      <c r="CA16" s="26"/>
+      <c r="CC16" s="26"/>
+      <c r="CE16" s="26"/>
+      <c r="CG16" s="26"/>
+      <c r="CI16" s="26"/>
+      <c r="CK16" s="26"/>
+      <c r="CL16" s="26"/>
+      <c r="CM16" s="26"/>
+      <c r="CN16" s="26"/>
+      <c r="CO16" s="26"/>
+      <c r="CP16" s="26"/>
+      <c r="CQ16" s="26"/>
+      <c r="CR16" s="26"/>
+      <c r="CS16" s="26"/>
+      <c r="CT16" s="26"/>
+      <c r="CU16" s="26"/>
+      <c r="CV16" s="26"/>
+      <c r="CW16" s="26"/>
+      <c r="CX16" s="26"/>
+      <c r="CY16" s="26"/>
+      <c r="CZ16" s="26"/>
+      <c r="DA16" s="26"/>
+      <c r="DB16" s="26"/>
+      <c r="DC16" s="26"/>
+      <c r="DD16" s="26"/>
+      <c r="DE16" s="26"/>
+      <c r="DF16" s="26"/>
+      <c r="DG16" s="26"/>
+      <c r="DH16" s="26"/>
+      <c r="DI16" s="26"/>
+      <c r="DJ16" s="26"/>
+      <c r="DK16" s="26"/>
+      <c r="DL16" s="26"/>
+      <c r="DM16" s="26"/>
+      <c r="DN16" s="26"/>
+      <c r="DO16" s="26"/>
+      <c r="DP16" s="26"/>
+      <c r="DQ16" s="26"/>
+      <c r="DR16" s="26"/>
+      <c r="DS16" s="26"/>
+      <c r="DT16" s="26"/>
+      <c r="DU16" s="26"/>
+      <c r="DV16" s="26"/>
+      <c r="DW16" s="26"/>
+      <c r="DX16" s="26"/>
+      <c r="DY16" s="26"/>
+      <c r="DZ16" s="26"/>
+      <c r="EA16" s="26"/>
+      <c r="EB16" s="26"/>
+      <c r="EC16" s="26"/>
+      <c r="ED16" s="26"/>
+      <c r="EE16" s="26"/>
+      <c r="EF16" s="26"/>
+      <c r="EG16" s="26"/>
+      <c r="EH16" s="26"/>
+      <c r="EI16" s="26"/>
+      <c r="EJ16" s="26"/>
+      <c r="EK16" s="26"/>
+      <c r="EL16" s="26"/>
+      <c r="EM16" s="26"/>
+      <c r="EN16" s="26"/>
+      <c r="EO16" s="26"/>
+      <c r="EP16" s="26"/>
+      <c r="EQ16" s="26"/>
+      <c r="ER16" s="26"/>
+      <c r="ES16" s="26"/>
+      <c r="ET16" s="26"/>
+      <c r="EU16" s="26"/>
+      <c r="EV16" s="26"/>
+      <c r="EW16" s="26"/>
+      <c r="EX16" s="26"/>
+      <c r="EY16" s="26"/>
+      <c r="EZ16" s="26"/>
+      <c r="FA16" s="26"/>
+      <c r="FB16" s="26"/>
+      <c r="FC16" s="26"/>
+      <c r="FD16" s="26"/>
+      <c r="FE16" s="26"/>
+      <c r="FF16" s="26"/>
+      <c r="FG16" s="26"/>
+      <c r="FH16" s="26"/>
+      <c r="FI16" s="26"/>
+      <c r="FJ16" s="26"/>
+      <c r="FK16" s="26"/>
+      <c r="FL16" s="26"/>
+      <c r="FM16" s="26"/>
+      <c r="FN16" s="26"/>
+      <c r="FO16" s="26"/>
+      <c r="FP16" s="26"/>
+      <c r="FQ16" s="26"/>
+      <c r="FR16" s="26"/>
+      <c r="FS16" s="26"/>
+      <c r="FT16" s="26"/>
+      <c r="FU16" s="26"/>
+      <c r="FV16" s="26"/>
+      <c r="FW16" s="26"/>
+      <c r="FX16" s="26"/>
+      <c r="FY16" s="26"/>
+      <c r="FZ16" s="26"/>
+      <c r="GA16" s="26"/>
+      <c r="GB16" s="26"/>
+      <c r="GC16" s="26"/>
+      <c r="GD16" s="26"/>
+      <c r="GE16" s="26"/>
+      <c r="GF16" s="26"/>
+      <c r="GG16" s="26"/>
+      <c r="GH16" s="26"/>
+      <c r="GI16" s="26"/>
+      <c r="GJ16" s="26"/>
+      <c r="GK16" s="26"/>
+      <c r="GL16" s="26"/>
+      <c r="GM16" s="26"/>
+      <c r="GN16" s="26"/>
+      <c r="GO16" s="26"/>
+      <c r="GP16" s="26"/>
+      <c r="GQ16" s="26"/>
+      <c r="GR16" s="26"/>
+      <c r="GS16" s="26"/>
+      <c r="GT16" s="26"/>
+      <c r="GU16" s="26"/>
+      <c r="GV16" s="26"/>
+      <c r="GW16" s="26"/>
+      <c r="GX16" s="26"/>
+      <c r="GY16" s="26"/>
+      <c r="GZ16" s="26"/>
+      <c r="HA16" s="26"/>
+      <c r="HB16" s="26"/>
+      <c r="HC16" s="26"/>
+      <c r="HD16" s="26"/>
+      <c r="HE16" s="26"/>
+      <c r="HF16" s="26"/>
+      <c r="HG16" s="26"/>
+      <c r="HH16" s="26"/>
+      <c r="HI16" s="26"/>
+      <c r="HJ16" s="26"/>
+      <c r="HK16" s="26"/>
+      <c r="HL16" s="26"/>
+      <c r="HM16" s="26"/>
+      <c r="HN16" s="26"/>
+      <c r="HO16" s="26"/>
+      <c r="HP16" s="26"/>
+      <c r="HQ16" s="26"/>
+      <c r="HR16" s="26"/>
+      <c r="HS16" s="26"/>
+      <c r="HT16" s="26"/>
+      <c r="HU16" s="26"/>
     </row>
-    <row r="17" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="28"/>
-      <c r="BQ17" s="29"/>
-      <c r="BS17" s="29"/>
-      <c r="BU17" s="29"/>
-      <c r="BW17" s="29"/>
-      <c r="BY17" s="29"/>
-      <c r="CA17" s="29"/>
-      <c r="CC17" s="29"/>
-      <c r="CE17" s="29"/>
-      <c r="CG17" s="29"/>
-      <c r="CI17" s="29"/>
-      <c r="CK17" s="29"/>
-      <c r="CL17" s="29"/>
-      <c r="CM17" s="29"/>
-      <c r="CN17" s="29"/>
-      <c r="CO17" s="29"/>
-      <c r="CP17" s="29"/>
-      <c r="CQ17" s="29"/>
-      <c r="CR17" s="29"/>
-      <c r="CS17" s="29"/>
-      <c r="CT17" s="29"/>
-      <c r="CU17" s="29"/>
-      <c r="CV17" s="29"/>
-      <c r="CW17" s="29"/>
-      <c r="CX17" s="29"/>
-      <c r="CY17" s="29"/>
-      <c r="CZ17" s="29"/>
-      <c r="DA17" s="29"/>
-      <c r="DB17" s="29"/>
-      <c r="DC17" s="29"/>
-      <c r="DD17" s="29"/>
-      <c r="DE17" s="29"/>
-      <c r="DF17" s="29"/>
-      <c r="DG17" s="29"/>
-      <c r="DH17" s="29"/>
-      <c r="DI17" s="29"/>
-      <c r="DJ17" s="29"/>
-      <c r="DK17" s="29"/>
-      <c r="DL17" s="29"/>
-      <c r="DM17" s="29"/>
-      <c r="DN17" s="29"/>
-      <c r="DO17" s="29"/>
-      <c r="DP17" s="29"/>
-      <c r="DQ17" s="29"/>
-      <c r="DR17" s="29"/>
-      <c r="DS17" s="29"/>
-      <c r="DT17" s="29"/>
-      <c r="DU17" s="29"/>
-      <c r="DV17" s="29"/>
-      <c r="DW17" s="29"/>
-      <c r="DX17" s="29"/>
-      <c r="DY17" s="29"/>
-      <c r="DZ17" s="29"/>
-      <c r="EA17" s="29"/>
-      <c r="EB17" s="29"/>
-      <c r="EC17" s="29"/>
-      <c r="ED17" s="29"/>
-      <c r="EE17" s="29"/>
-      <c r="EF17" s="29"/>
-      <c r="EG17" s="29"/>
-      <c r="EH17" s="29"/>
-      <c r="EI17" s="29"/>
-      <c r="EJ17" s="29"/>
-      <c r="EK17" s="29"/>
-      <c r="EL17" s="29"/>
-      <c r="EM17" s="29"/>
-      <c r="EN17" s="29"/>
-      <c r="EO17" s="29"/>
-      <c r="EP17" s="29"/>
-      <c r="EQ17" s="29"/>
-      <c r="ER17" s="29"/>
-      <c r="ES17" s="29"/>
-      <c r="ET17" s="29"/>
-      <c r="EU17" s="29"/>
-      <c r="EV17" s="29"/>
-      <c r="EW17" s="29"/>
-      <c r="EX17" s="29"/>
-      <c r="EY17" s="29"/>
-      <c r="EZ17" s="29"/>
-      <c r="FA17" s="29"/>
-      <c r="FB17" s="29"/>
-      <c r="FC17" s="29"/>
-      <c r="FD17" s="29"/>
-      <c r="FE17" s="29"/>
-      <c r="FF17" s="29"/>
-      <c r="FG17" s="29"/>
-      <c r="FH17" s="29"/>
-      <c r="FI17" s="29"/>
-      <c r="FJ17" s="29"/>
-      <c r="FK17" s="29"/>
-      <c r="FL17" s="29"/>
-      <c r="FM17" s="29"/>
-      <c r="FN17" s="29"/>
-      <c r="FO17" s="29"/>
-      <c r="FP17" s="29"/>
-      <c r="FQ17" s="29"/>
-      <c r="FR17" s="29"/>
-      <c r="FS17" s="29"/>
-      <c r="FT17" s="29"/>
-      <c r="FU17" s="29"/>
-      <c r="FV17" s="29"/>
-      <c r="FW17" s="29"/>
-      <c r="FX17" s="29"/>
-      <c r="FY17" s="29"/>
-      <c r="FZ17" s="29"/>
-      <c r="GA17" s="29"/>
-      <c r="GB17" s="29"/>
-      <c r="GC17" s="29"/>
-      <c r="GD17" s="29"/>
-      <c r="GE17" s="29"/>
-      <c r="GF17" s="29"/>
-      <c r="GG17" s="29"/>
-      <c r="GH17" s="29"/>
-      <c r="GI17" s="29"/>
-      <c r="GJ17" s="29"/>
-      <c r="GK17" s="29"/>
-      <c r="GL17" s="29"/>
-      <c r="GM17" s="29"/>
-      <c r="GN17" s="29"/>
-      <c r="GO17" s="29"/>
-      <c r="GP17" s="29"/>
-      <c r="GQ17" s="29"/>
-      <c r="GR17" s="29"/>
-      <c r="GS17" s="29"/>
-      <c r="GT17" s="29"/>
-      <c r="GU17" s="29"/>
-      <c r="GV17" s="29"/>
-      <c r="GW17" s="29"/>
-      <c r="GX17" s="29"/>
-      <c r="GY17" s="29"/>
-      <c r="GZ17" s="29"/>
-      <c r="HA17" s="29"/>
-      <c r="HB17" s="29"/>
-      <c r="HC17" s="29"/>
-      <c r="HD17" s="29"/>
-      <c r="HE17" s="29"/>
-      <c r="HF17" s="29"/>
-      <c r="HG17" s="29"/>
-      <c r="HH17" s="29"/>
-      <c r="HI17" s="29"/>
-      <c r="HJ17" s="29"/>
-      <c r="HK17" s="29"/>
-      <c r="HL17" s="29"/>
-      <c r="HM17" s="29"/>
-      <c r="HN17" s="29"/>
-      <c r="HO17" s="29"/>
-      <c r="HP17" s="29"/>
-      <c r="HQ17" s="29"/>
-      <c r="HR17" s="29"/>
-      <c r="HS17" s="29"/>
-      <c r="HT17" s="29"/>
-      <c r="HU17" s="29"/>
+    <row r="17" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="27"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="25"/>
+      <c r="BQ17" s="26"/>
+      <c r="BS17" s="26"/>
+      <c r="BU17" s="26"/>
+      <c r="BW17" s="26"/>
+      <c r="BY17" s="26"/>
+      <c r="CA17" s="26"/>
+      <c r="CC17" s="26"/>
+      <c r="CE17" s="26"/>
+      <c r="CG17" s="26"/>
+      <c r="CI17" s="26"/>
+      <c r="CK17" s="26"/>
+      <c r="CL17" s="26"/>
+      <c r="CM17" s="26"/>
+      <c r="CN17" s="26"/>
+      <c r="CO17" s="26"/>
+      <c r="CP17" s="26"/>
+      <c r="CQ17" s="26"/>
+      <c r="CR17" s="26"/>
+      <c r="CS17" s="26"/>
+      <c r="CT17" s="26"/>
+      <c r="CU17" s="26"/>
+      <c r="CV17" s="26"/>
+      <c r="CW17" s="26"/>
+      <c r="CX17" s="26"/>
+      <c r="CY17" s="26"/>
+      <c r="CZ17" s="26"/>
+      <c r="DA17" s="26"/>
+      <c r="DB17" s="26"/>
+      <c r="DC17" s="26"/>
+      <c r="DD17" s="26"/>
+      <c r="DE17" s="26"/>
+      <c r="DF17" s="26"/>
+      <c r="DG17" s="26"/>
+      <c r="DH17" s="26"/>
+      <c r="DI17" s="26"/>
+      <c r="DJ17" s="26"/>
+      <c r="DK17" s="26"/>
+      <c r="DL17" s="26"/>
+      <c r="DM17" s="26"/>
+      <c r="DN17" s="26"/>
+      <c r="DO17" s="26"/>
+      <c r="DP17" s="26"/>
+      <c r="DQ17" s="26"/>
+      <c r="DR17" s="26"/>
+      <c r="DS17" s="26"/>
+      <c r="DT17" s="26"/>
+      <c r="DU17" s="26"/>
+      <c r="DV17" s="26"/>
+      <c r="DW17" s="26"/>
+      <c r="DX17" s="26"/>
+      <c r="DY17" s="26"/>
+      <c r="DZ17" s="26"/>
+      <c r="EA17" s="26"/>
+      <c r="EB17" s="26"/>
+      <c r="EC17" s="26"/>
+      <c r="ED17" s="26"/>
+      <c r="EE17" s="26"/>
+      <c r="EF17" s="26"/>
+      <c r="EG17" s="26"/>
+      <c r="EH17" s="26"/>
+      <c r="EI17" s="26"/>
+      <c r="EJ17" s="26"/>
+      <c r="EK17" s="26"/>
+      <c r="EL17" s="26"/>
+      <c r="EM17" s="26"/>
+      <c r="EN17" s="26"/>
+      <c r="EO17" s="26"/>
+      <c r="EP17" s="26"/>
+      <c r="EQ17" s="26"/>
+      <c r="ER17" s="26"/>
+      <c r="ES17" s="26"/>
+      <c r="ET17" s="26"/>
+      <c r="EU17" s="26"/>
+      <c r="EV17" s="26"/>
+      <c r="EW17" s="26"/>
+      <c r="EX17" s="26"/>
+      <c r="EY17" s="26"/>
+      <c r="EZ17" s="26"/>
+      <c r="FA17" s="26"/>
+      <c r="FB17" s="26"/>
+      <c r="FC17" s="26"/>
+      <c r="FD17" s="26"/>
+      <c r="FE17" s="26"/>
+      <c r="FF17" s="26"/>
+      <c r="FG17" s="26"/>
+      <c r="FH17" s="26"/>
+      <c r="FI17" s="26"/>
+      <c r="FJ17" s="26"/>
+      <c r="FK17" s="26"/>
+      <c r="FL17" s="26"/>
+      <c r="FM17" s="26"/>
+      <c r="FN17" s="26"/>
+      <c r="FO17" s="26"/>
+      <c r="FP17" s="26"/>
+      <c r="FQ17" s="26"/>
+      <c r="FR17" s="26"/>
+      <c r="FS17" s="26"/>
+      <c r="FT17" s="26"/>
+      <c r="FU17" s="26"/>
+      <c r="FV17" s="26"/>
+      <c r="FW17" s="26"/>
+      <c r="FX17" s="26"/>
+      <c r="FY17" s="26"/>
+      <c r="FZ17" s="26"/>
+      <c r="GA17" s="26"/>
+      <c r="GB17" s="26"/>
+      <c r="GC17" s="26"/>
+      <c r="GD17" s="26"/>
+      <c r="GE17" s="26"/>
+      <c r="GF17" s="26"/>
+      <c r="GG17" s="26"/>
+      <c r="GH17" s="26"/>
+      <c r="GI17" s="26"/>
+      <c r="GJ17" s="26"/>
+      <c r="GK17" s="26"/>
+      <c r="GL17" s="26"/>
+      <c r="GM17" s="26"/>
+      <c r="GN17" s="26"/>
+      <c r="GO17" s="26"/>
+      <c r="GP17" s="26"/>
+      <c r="GQ17" s="26"/>
+      <c r="GR17" s="26"/>
+      <c r="GS17" s="26"/>
+      <c r="GT17" s="26"/>
+      <c r="GU17" s="26"/>
+      <c r="GV17" s="26"/>
+      <c r="GW17" s="26"/>
+      <c r="GX17" s="26"/>
+      <c r="GY17" s="26"/>
+      <c r="GZ17" s="26"/>
+      <c r="HA17" s="26"/>
+      <c r="HB17" s="26"/>
+      <c r="HC17" s="26"/>
+      <c r="HD17" s="26"/>
+      <c r="HE17" s="26"/>
+      <c r="HF17" s="26"/>
+      <c r="HG17" s="26"/>
+      <c r="HH17" s="26"/>
+      <c r="HI17" s="26"/>
+      <c r="HJ17" s="26"/>
+      <c r="HK17" s="26"/>
+      <c r="HL17" s="26"/>
+      <c r="HM17" s="26"/>
+      <c r="HN17" s="26"/>
+      <c r="HO17" s="26"/>
+      <c r="HP17" s="26"/>
+      <c r="HQ17" s="26"/>
+      <c r="HR17" s="26"/>
+      <c r="HS17" s="26"/>
+      <c r="HT17" s="26"/>
+      <c r="HU17" s="26"/>
     </row>
-    <row r="18" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="28"/>
-      <c r="BQ18" s="29"/>
-      <c r="BS18" s="29"/>
-      <c r="BU18" s="29"/>
-      <c r="BW18" s="29"/>
-      <c r="BY18" s="29"/>
-      <c r="CA18" s="29"/>
-      <c r="CC18" s="29"/>
-      <c r="CE18" s="29"/>
-      <c r="CG18" s="29"/>
-      <c r="CI18" s="29"/>
-      <c r="CK18" s="29"/>
-      <c r="CL18" s="29"/>
-      <c r="CM18" s="29"/>
-      <c r="CN18" s="29"/>
-      <c r="CO18" s="29"/>
-      <c r="CP18" s="29"/>
-      <c r="CQ18" s="29"/>
-      <c r="CR18" s="29"/>
-      <c r="CS18" s="29"/>
-      <c r="CT18" s="29"/>
-      <c r="CU18" s="29"/>
-      <c r="CV18" s="29"/>
-      <c r="CW18" s="29"/>
-      <c r="CX18" s="29"/>
-      <c r="CY18" s="29"/>
-      <c r="CZ18" s="29"/>
-      <c r="DA18" s="29"/>
-      <c r="DB18" s="29"/>
-      <c r="DC18" s="29"/>
-      <c r="DD18" s="29"/>
-      <c r="DE18" s="29"/>
-      <c r="DF18" s="29"/>
-      <c r="DG18" s="29"/>
-      <c r="DH18" s="29"/>
-      <c r="DI18" s="29"/>
-      <c r="DJ18" s="29"/>
-      <c r="DK18" s="29"/>
-      <c r="DL18" s="29"/>
-      <c r="DM18" s="29"/>
-      <c r="DN18" s="29"/>
-      <c r="DO18" s="29"/>
-      <c r="DP18" s="29"/>
-      <c r="DQ18" s="29"/>
-      <c r="DR18" s="29"/>
-      <c r="DS18" s="29"/>
-      <c r="DT18" s="29"/>
-      <c r="DU18" s="29"/>
-      <c r="DV18" s="29"/>
-      <c r="DW18" s="29"/>
-      <c r="DX18" s="29"/>
-      <c r="DY18" s="29"/>
-      <c r="DZ18" s="29"/>
-      <c r="EA18" s="29"/>
-      <c r="EB18" s="29"/>
-      <c r="EC18" s="29"/>
-      <c r="ED18" s="29"/>
-      <c r="EE18" s="29"/>
-      <c r="EF18" s="29"/>
-      <c r="EG18" s="29"/>
-      <c r="EH18" s="29"/>
-      <c r="EI18" s="29"/>
-      <c r="EJ18" s="29"/>
-      <c r="EK18" s="29"/>
-      <c r="EL18" s="29"/>
-      <c r="EM18" s="29"/>
-      <c r="EN18" s="29"/>
-      <c r="EO18" s="29"/>
-      <c r="EP18" s="29"/>
-      <c r="EQ18" s="29"/>
-      <c r="ER18" s="29"/>
-      <c r="ES18" s="29"/>
-      <c r="ET18" s="29"/>
-      <c r="EU18" s="29"/>
-      <c r="EV18" s="29"/>
-      <c r="EW18" s="29"/>
-      <c r="EX18" s="29"/>
-      <c r="EY18" s="29"/>
-      <c r="EZ18" s="29"/>
-      <c r="FA18" s="29"/>
-      <c r="FB18" s="29"/>
-      <c r="FC18" s="29"/>
-      <c r="FD18" s="29"/>
-      <c r="FE18" s="29"/>
-      <c r="FF18" s="29"/>
-      <c r="FG18" s="29"/>
-      <c r="FH18" s="29"/>
-      <c r="FI18" s="29"/>
-      <c r="FJ18" s="29"/>
-      <c r="FK18" s="29"/>
-      <c r="FL18" s="29"/>
-      <c r="FM18" s="29"/>
-      <c r="FN18" s="29"/>
-      <c r="FO18" s="29"/>
-      <c r="FP18" s="29"/>
-      <c r="FQ18" s="29"/>
-      <c r="FR18" s="29"/>
-      <c r="FS18" s="29"/>
-      <c r="FT18" s="29"/>
-      <c r="FU18" s="29"/>
-      <c r="FV18" s="29"/>
-      <c r="FW18" s="29"/>
-      <c r="FX18" s="29"/>
-      <c r="FY18" s="29"/>
-      <c r="FZ18" s="29"/>
-      <c r="GA18" s="29"/>
-      <c r="GB18" s="29"/>
-      <c r="GC18" s="29"/>
-      <c r="GD18" s="29"/>
-      <c r="GE18" s="29"/>
-      <c r="GF18" s="29"/>
-      <c r="GG18" s="29"/>
-      <c r="GH18" s="29"/>
-      <c r="GI18" s="29"/>
-      <c r="GJ18" s="29"/>
-      <c r="GK18" s="29"/>
-      <c r="GL18" s="29"/>
-      <c r="GM18" s="29"/>
-      <c r="GN18" s="29"/>
-      <c r="GO18" s="29"/>
-      <c r="GP18" s="29"/>
-      <c r="GQ18" s="29"/>
-      <c r="GR18" s="29"/>
-      <c r="GS18" s="29"/>
-      <c r="GT18" s="29"/>
-      <c r="GU18" s="29"/>
-      <c r="GV18" s="29"/>
-      <c r="GW18" s="29"/>
-      <c r="GX18" s="29"/>
-      <c r="GY18" s="29"/>
-      <c r="GZ18" s="29"/>
-      <c r="HA18" s="29"/>
-      <c r="HB18" s="29"/>
-      <c r="HC18" s="29"/>
-      <c r="HD18" s="29"/>
-      <c r="HE18" s="29"/>
-      <c r="HF18" s="29"/>
-      <c r="HG18" s="29"/>
-      <c r="HH18" s="29"/>
-      <c r="HI18" s="29"/>
-      <c r="HJ18" s="29"/>
-      <c r="HK18" s="29"/>
-      <c r="HL18" s="29"/>
-      <c r="HM18" s="29"/>
-      <c r="HN18" s="29"/>
-      <c r="HO18" s="29"/>
-      <c r="HP18" s="29"/>
-      <c r="HQ18" s="29"/>
-      <c r="HR18" s="29"/>
-      <c r="HS18" s="29"/>
-      <c r="HT18" s="29"/>
-      <c r="HU18" s="29"/>
+    <row r="18" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="27"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="25"/>
+      <c r="BQ18" s="26"/>
+      <c r="BS18" s="26"/>
+      <c r="BU18" s="26"/>
+      <c r="BW18" s="26"/>
+      <c r="BY18" s="26"/>
+      <c r="CA18" s="26"/>
+      <c r="CC18" s="26"/>
+      <c r="CE18" s="26"/>
+      <c r="CG18" s="26"/>
+      <c r="CI18" s="26"/>
+      <c r="CK18" s="26"/>
+      <c r="CL18" s="26"/>
+      <c r="CM18" s="26"/>
+      <c r="CN18" s="26"/>
+      <c r="CO18" s="26"/>
+      <c r="CP18" s="26"/>
+      <c r="CQ18" s="26"/>
+      <c r="CR18" s="26"/>
+      <c r="CS18" s="26"/>
+      <c r="CT18" s="26"/>
+      <c r="CU18" s="26"/>
+      <c r="CV18" s="26"/>
+      <c r="CW18" s="26"/>
+      <c r="CX18" s="26"/>
+      <c r="CY18" s="26"/>
+      <c r="CZ18" s="26"/>
+      <c r="DA18" s="26"/>
+      <c r="DB18" s="26"/>
+      <c r="DC18" s="26"/>
+      <c r="DD18" s="26"/>
+      <c r="DE18" s="26"/>
+      <c r="DF18" s="26"/>
+      <c r="DG18" s="26"/>
+      <c r="DH18" s="26"/>
+      <c r="DI18" s="26"/>
+      <c r="DJ18" s="26"/>
+      <c r="DK18" s="26"/>
+      <c r="DL18" s="26"/>
+      <c r="DM18" s="26"/>
+      <c r="DN18" s="26"/>
+      <c r="DO18" s="26"/>
+      <c r="DP18" s="26"/>
+      <c r="DQ18" s="26"/>
+      <c r="DR18" s="26"/>
+      <c r="DS18" s="26"/>
+      <c r="DT18" s="26"/>
+      <c r="DU18" s="26"/>
+      <c r="DV18" s="26"/>
+      <c r="DW18" s="26"/>
+      <c r="DX18" s="26"/>
+      <c r="DY18" s="26"/>
+      <c r="DZ18" s="26"/>
+      <c r="EA18" s="26"/>
+      <c r="EB18" s="26"/>
+      <c r="EC18" s="26"/>
+      <c r="ED18" s="26"/>
+      <c r="EE18" s="26"/>
+      <c r="EF18" s="26"/>
+      <c r="EG18" s="26"/>
+      <c r="EH18" s="26"/>
+      <c r="EI18" s="26"/>
+      <c r="EJ18" s="26"/>
+      <c r="EK18" s="26"/>
+      <c r="EL18" s="26"/>
+      <c r="EM18" s="26"/>
+      <c r="EN18" s="26"/>
+      <c r="EO18" s="26"/>
+      <c r="EP18" s="26"/>
+      <c r="EQ18" s="26"/>
+      <c r="ER18" s="26"/>
+      <c r="ES18" s="26"/>
+      <c r="ET18" s="26"/>
+      <c r="EU18" s="26"/>
+      <c r="EV18" s="26"/>
+      <c r="EW18" s="26"/>
+      <c r="EX18" s="26"/>
+      <c r="EY18" s="26"/>
+      <c r="EZ18" s="26"/>
+      <c r="FA18" s="26"/>
+      <c r="FB18" s="26"/>
+      <c r="FC18" s="26"/>
+      <c r="FD18" s="26"/>
+      <c r="FE18" s="26"/>
+      <c r="FF18" s="26"/>
+      <c r="FG18" s="26"/>
+      <c r="FH18" s="26"/>
+      <c r="FI18" s="26"/>
+      <c r="FJ18" s="26"/>
+      <c r="FK18" s="26"/>
+      <c r="FL18" s="26"/>
+      <c r="FM18" s="26"/>
+      <c r="FN18" s="26"/>
+      <c r="FO18" s="26"/>
+      <c r="FP18" s="26"/>
+      <c r="FQ18" s="26"/>
+      <c r="FR18" s="26"/>
+      <c r="FS18" s="26"/>
+      <c r="FT18" s="26"/>
+      <c r="FU18" s="26"/>
+      <c r="FV18" s="26"/>
+      <c r="FW18" s="26"/>
+      <c r="FX18" s="26"/>
+      <c r="FY18" s="26"/>
+      <c r="FZ18" s="26"/>
+      <c r="GA18" s="26"/>
+      <c r="GB18" s="26"/>
+      <c r="GC18" s="26"/>
+      <c r="GD18" s="26"/>
+      <c r="GE18" s="26"/>
+      <c r="GF18" s="26"/>
+      <c r="GG18" s="26"/>
+      <c r="GH18" s="26"/>
+      <c r="GI18" s="26"/>
+      <c r="GJ18" s="26"/>
+      <c r="GK18" s="26"/>
+      <c r="GL18" s="26"/>
+      <c r="GM18" s="26"/>
+      <c r="GN18" s="26"/>
+      <c r="GO18" s="26"/>
+      <c r="GP18" s="26"/>
+      <c r="GQ18" s="26"/>
+      <c r="GR18" s="26"/>
+      <c r="GS18" s="26"/>
+      <c r="GT18" s="26"/>
+      <c r="GU18" s="26"/>
+      <c r="GV18" s="26"/>
+      <c r="GW18" s="26"/>
+      <c r="GX18" s="26"/>
+      <c r="GY18" s="26"/>
+      <c r="GZ18" s="26"/>
+      <c r="HA18" s="26"/>
+      <c r="HB18" s="26"/>
+      <c r="HC18" s="26"/>
+      <c r="HD18" s="26"/>
+      <c r="HE18" s="26"/>
+      <c r="HF18" s="26"/>
+      <c r="HG18" s="26"/>
+      <c r="HH18" s="26"/>
+      <c r="HI18" s="26"/>
+      <c r="HJ18" s="26"/>
+      <c r="HK18" s="26"/>
+      <c r="HL18" s="26"/>
+      <c r="HM18" s="26"/>
+      <c r="HN18" s="26"/>
+      <c r="HO18" s="26"/>
+      <c r="HP18" s="26"/>
+      <c r="HQ18" s="26"/>
+      <c r="HR18" s="26"/>
+      <c r="HS18" s="26"/>
+      <c r="HT18" s="26"/>
+      <c r="HU18" s="26"/>
     </row>
-    <row r="19" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7">
-        <v>0</v>
-      </c>
-      <c r="H19" s="28"/>
-      <c r="BQ19" s="29"/>
-      <c r="BS19" s="29"/>
-      <c r="BU19" s="29"/>
-      <c r="BW19" s="29"/>
-      <c r="BY19" s="29"/>
-      <c r="CA19" s="29"/>
-      <c r="CC19" s="29"/>
-      <c r="CE19" s="29"/>
-      <c r="CG19" s="29"/>
-      <c r="CI19" s="29"/>
-      <c r="CK19" s="29"/>
-      <c r="CL19" s="29"/>
-      <c r="CM19" s="29"/>
-      <c r="CN19" s="29"/>
-      <c r="CO19" s="29"/>
-      <c r="CP19" s="29"/>
-      <c r="CQ19" s="29"/>
-      <c r="CR19" s="29"/>
-      <c r="CS19" s="29"/>
-      <c r="CT19" s="29"/>
-      <c r="CU19" s="29"/>
-      <c r="CV19" s="29"/>
-      <c r="CW19" s="29"/>
-      <c r="CX19" s="29"/>
-      <c r="CY19" s="29"/>
-      <c r="CZ19" s="29"/>
-      <c r="DA19" s="29"/>
-      <c r="DB19" s="29"/>
-      <c r="DC19" s="29"/>
-      <c r="DD19" s="29"/>
-      <c r="DE19" s="29"/>
-      <c r="DF19" s="29"/>
-      <c r="DG19" s="29"/>
-      <c r="DH19" s="29"/>
-      <c r="DI19" s="29"/>
-      <c r="DJ19" s="29"/>
-      <c r="DK19" s="29"/>
-      <c r="DL19" s="29"/>
-      <c r="DM19" s="29"/>
-      <c r="DN19" s="29"/>
-      <c r="DO19" s="29"/>
-      <c r="DP19" s="29"/>
-      <c r="DQ19" s="29"/>
-      <c r="DR19" s="29"/>
-      <c r="DS19" s="29"/>
-      <c r="DT19" s="29"/>
-      <c r="DU19" s="29"/>
-      <c r="DV19" s="29"/>
-      <c r="DW19" s="29"/>
-      <c r="DX19" s="29"/>
-      <c r="DY19" s="29"/>
-      <c r="DZ19" s="29"/>
-      <c r="EA19" s="29"/>
-      <c r="EB19" s="29"/>
-      <c r="EC19" s="29"/>
-      <c r="ED19" s="29"/>
-      <c r="EE19" s="29"/>
-      <c r="EF19" s="29"/>
-      <c r="EG19" s="29"/>
-      <c r="EH19" s="29"/>
-      <c r="EI19" s="29"/>
-      <c r="EJ19" s="29"/>
-      <c r="EK19" s="29"/>
-      <c r="EL19" s="29"/>
-      <c r="EM19" s="29"/>
-      <c r="EN19" s="29"/>
-      <c r="EO19" s="29"/>
-      <c r="EP19" s="29"/>
-      <c r="EQ19" s="29"/>
-      <c r="ER19" s="29"/>
-      <c r="ES19" s="29"/>
-      <c r="ET19" s="29"/>
-      <c r="EU19" s="29"/>
-      <c r="EV19" s="29"/>
-      <c r="EW19" s="29"/>
-      <c r="EX19" s="29"/>
-      <c r="EY19" s="29"/>
-      <c r="EZ19" s="29"/>
-      <c r="FA19" s="29"/>
-      <c r="FB19" s="29"/>
-      <c r="FC19" s="29"/>
-      <c r="FD19" s="29"/>
-      <c r="FE19" s="29"/>
-      <c r="FF19" s="29"/>
-      <c r="FG19" s="29"/>
-      <c r="FH19" s="29"/>
-      <c r="FI19" s="29"/>
-      <c r="FJ19" s="29"/>
-      <c r="FK19" s="29"/>
-      <c r="FL19" s="29"/>
-      <c r="FM19" s="29"/>
-      <c r="FN19" s="29"/>
-      <c r="FO19" s="29"/>
-      <c r="FP19" s="29"/>
-      <c r="FQ19" s="29"/>
-      <c r="FR19" s="29"/>
-      <c r="FS19" s="29"/>
-      <c r="FT19" s="29"/>
-      <c r="FU19" s="29"/>
-      <c r="FV19" s="29"/>
-      <c r="FW19" s="29"/>
-      <c r="FX19" s="29"/>
-      <c r="FY19" s="29"/>
-      <c r="FZ19" s="29"/>
-      <c r="GA19" s="29"/>
-      <c r="GB19" s="29"/>
-      <c r="GC19" s="29"/>
-      <c r="GD19" s="29"/>
-      <c r="GE19" s="29"/>
-      <c r="GF19" s="29"/>
-      <c r="GG19" s="29"/>
-      <c r="GH19" s="29"/>
-      <c r="GI19" s="29"/>
-      <c r="GJ19" s="29"/>
-      <c r="GK19" s="29"/>
-      <c r="GL19" s="29"/>
-      <c r="GM19" s="29"/>
-      <c r="GN19" s="29"/>
-      <c r="GO19" s="29"/>
-      <c r="GP19" s="29"/>
-      <c r="GQ19" s="29"/>
-      <c r="GR19" s="29"/>
-      <c r="GS19" s="29"/>
-      <c r="GT19" s="29"/>
-      <c r="GU19" s="29"/>
-      <c r="GV19" s="29"/>
-      <c r="GW19" s="29"/>
-      <c r="GX19" s="29"/>
-      <c r="GY19" s="29"/>
-      <c r="GZ19" s="29"/>
-      <c r="HA19" s="29"/>
-      <c r="HB19" s="29"/>
-      <c r="HC19" s="29"/>
-      <c r="HD19" s="29"/>
-      <c r="HE19" s="29"/>
-      <c r="HF19" s="29"/>
-      <c r="HG19" s="29"/>
-      <c r="HH19" s="29"/>
-      <c r="HI19" s="29"/>
-      <c r="HJ19" s="29"/>
-      <c r="HK19" s="29"/>
-      <c r="HL19" s="29"/>
-      <c r="HM19" s="29"/>
-      <c r="HN19" s="29"/>
-      <c r="HO19" s="29"/>
-      <c r="HP19" s="29"/>
-      <c r="HQ19" s="29"/>
-      <c r="HR19" s="29"/>
-      <c r="HS19" s="29"/>
-      <c r="HT19" s="29"/>
-      <c r="HU19" s="29"/>
+    <row r="19" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="27"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="25"/>
+      <c r="BQ19" s="26"/>
+      <c r="BS19" s="26"/>
+      <c r="BU19" s="26"/>
+      <c r="BW19" s="26"/>
+      <c r="BY19" s="26"/>
+      <c r="CA19" s="26"/>
+      <c r="CC19" s="26"/>
+      <c r="CE19" s="26"/>
+      <c r="CG19" s="26"/>
+      <c r="CI19" s="26"/>
+      <c r="CK19" s="26"/>
+      <c r="CL19" s="26"/>
+      <c r="CM19" s="26"/>
+      <c r="CN19" s="26"/>
+      <c r="CO19" s="26"/>
+      <c r="CP19" s="26"/>
+      <c r="CQ19" s="26"/>
+      <c r="CR19" s="26"/>
+      <c r="CS19" s="26"/>
+      <c r="CT19" s="26"/>
+      <c r="CU19" s="26"/>
+      <c r="CV19" s="26"/>
+      <c r="CW19" s="26"/>
+      <c r="CX19" s="26"/>
+      <c r="CY19" s="26"/>
+      <c r="CZ19" s="26"/>
+      <c r="DA19" s="26"/>
+      <c r="DB19" s="26"/>
+      <c r="DC19" s="26"/>
+      <c r="DD19" s="26"/>
+      <c r="DE19" s="26"/>
+      <c r="DF19" s="26"/>
+      <c r="DG19" s="26"/>
+      <c r="DH19" s="26"/>
+      <c r="DI19" s="26"/>
+      <c r="DJ19" s="26"/>
+      <c r="DK19" s="26"/>
+      <c r="DL19" s="26"/>
+      <c r="DM19" s="26"/>
+      <c r="DN19" s="26"/>
+      <c r="DO19" s="26"/>
+      <c r="DP19" s="26"/>
+      <c r="DQ19" s="26"/>
+      <c r="DR19" s="26"/>
+      <c r="DS19" s="26"/>
+      <c r="DT19" s="26"/>
+      <c r="DU19" s="26"/>
+      <c r="DV19" s="26"/>
+      <c r="DW19" s="26"/>
+      <c r="DX19" s="26"/>
+      <c r="DY19" s="26"/>
+      <c r="DZ19" s="26"/>
+      <c r="EA19" s="26"/>
+      <c r="EB19" s="26"/>
+      <c r="EC19" s="26"/>
+      <c r="ED19" s="26"/>
+      <c r="EE19" s="26"/>
+      <c r="EF19" s="26"/>
+      <c r="EG19" s="26"/>
+      <c r="EH19" s="26"/>
+      <c r="EI19" s="26"/>
+      <c r="EJ19" s="26"/>
+      <c r="EK19" s="26"/>
+      <c r="EL19" s="26"/>
+      <c r="EM19" s="26"/>
+      <c r="EN19" s="26"/>
+      <c r="EO19" s="26"/>
+      <c r="EP19" s="26"/>
+      <c r="EQ19" s="26"/>
+      <c r="ER19" s="26"/>
+      <c r="ES19" s="26"/>
+      <c r="ET19" s="26"/>
+      <c r="EU19" s="26"/>
+      <c r="EV19" s="26"/>
+      <c r="EW19" s="26"/>
+      <c r="EX19" s="26"/>
+      <c r="EY19" s="26"/>
+      <c r="EZ19" s="26"/>
+      <c r="FA19" s="26"/>
+      <c r="FB19" s="26"/>
+      <c r="FC19" s="26"/>
+      <c r="FD19" s="26"/>
+      <c r="FE19" s="26"/>
+      <c r="FF19" s="26"/>
+      <c r="FG19" s="26"/>
+      <c r="FH19" s="26"/>
+      <c r="FI19" s="26"/>
+      <c r="FJ19" s="26"/>
+      <c r="FK19" s="26"/>
+      <c r="FL19" s="26"/>
+      <c r="FM19" s="26"/>
+      <c r="FN19" s="26"/>
+      <c r="FO19" s="26"/>
+      <c r="FP19" s="26"/>
+      <c r="FQ19" s="26"/>
+      <c r="FR19" s="26"/>
+      <c r="FS19" s="26"/>
+      <c r="FT19" s="26"/>
+      <c r="FU19" s="26"/>
+      <c r="FV19" s="26"/>
+      <c r="FW19" s="26"/>
+      <c r="FX19" s="26"/>
+      <c r="FY19" s="26"/>
+      <c r="FZ19" s="26"/>
+      <c r="GA19" s="26"/>
+      <c r="GB19" s="26"/>
+      <c r="GC19" s="26"/>
+      <c r="GD19" s="26"/>
+      <c r="GE19" s="26"/>
+      <c r="GF19" s="26"/>
+      <c r="GG19" s="26"/>
+      <c r="GH19" s="26"/>
+      <c r="GI19" s="26"/>
+      <c r="GJ19" s="26"/>
+      <c r="GK19" s="26"/>
+      <c r="GL19" s="26"/>
+      <c r="GM19" s="26"/>
+      <c r="GN19" s="26"/>
+      <c r="GO19" s="26"/>
+      <c r="GP19" s="26"/>
+      <c r="GQ19" s="26"/>
+      <c r="GR19" s="26"/>
+      <c r="GS19" s="26"/>
+      <c r="GT19" s="26"/>
+      <c r="GU19" s="26"/>
+      <c r="GV19" s="26"/>
+      <c r="GW19" s="26"/>
+      <c r="GX19" s="26"/>
+      <c r="GY19" s="26"/>
+      <c r="GZ19" s="26"/>
+      <c r="HA19" s="26"/>
+      <c r="HB19" s="26"/>
+      <c r="HC19" s="26"/>
+      <c r="HD19" s="26"/>
+      <c r="HE19" s="26"/>
+      <c r="HF19" s="26"/>
+      <c r="HG19" s="26"/>
+      <c r="HH19" s="26"/>
+      <c r="HI19" s="26"/>
+      <c r="HJ19" s="26"/>
+      <c r="HK19" s="26"/>
+      <c r="HL19" s="26"/>
+      <c r="HM19" s="26"/>
+      <c r="HN19" s="26"/>
+      <c r="HO19" s="26"/>
+      <c r="HP19" s="26"/>
+      <c r="HQ19" s="26"/>
+      <c r="HR19" s="26"/>
+      <c r="HS19" s="26"/>
+      <c r="HT19" s="26"/>
+      <c r="HU19" s="26"/>
     </row>
-    <row r="20" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7">
-        <v>0</v>
-      </c>
-      <c r="H20" s="28"/>
-      <c r="BQ20" s="29"/>
-      <c r="BS20" s="29"/>
-      <c r="BU20" s="29"/>
-      <c r="BW20" s="29"/>
-      <c r="BY20" s="29"/>
-      <c r="CA20" s="29"/>
-      <c r="CC20" s="29"/>
-      <c r="CE20" s="29"/>
-      <c r="CG20" s="29"/>
-      <c r="CI20" s="29"/>
-      <c r="CK20" s="29"/>
-      <c r="CL20" s="29"/>
-      <c r="CM20" s="29"/>
-      <c r="CN20" s="29"/>
-      <c r="CO20" s="29"/>
-      <c r="CP20" s="29"/>
-      <c r="CQ20" s="29"/>
-      <c r="CR20" s="29"/>
-      <c r="CS20" s="29"/>
-      <c r="CT20" s="29"/>
-      <c r="CU20" s="29"/>
-      <c r="CV20" s="29"/>
-      <c r="CW20" s="29"/>
-      <c r="CX20" s="29"/>
-      <c r="CY20" s="29"/>
-      <c r="CZ20" s="29"/>
-      <c r="DA20" s="29"/>
-      <c r="DB20" s="29"/>
-      <c r="DC20" s="29"/>
-      <c r="DD20" s="29"/>
-      <c r="DE20" s="29"/>
-      <c r="DF20" s="29"/>
-      <c r="DG20" s="29"/>
-      <c r="DH20" s="29"/>
-      <c r="DI20" s="29"/>
-      <c r="DJ20" s="29"/>
-      <c r="DK20" s="29"/>
-      <c r="DL20" s="29"/>
-      <c r="DM20" s="29"/>
-      <c r="DN20" s="29"/>
-      <c r="DO20" s="29"/>
-      <c r="DP20" s="29"/>
-      <c r="DQ20" s="29"/>
-      <c r="DR20" s="29"/>
-      <c r="DS20" s="29"/>
-      <c r="DT20" s="29"/>
-      <c r="DU20" s="29"/>
-      <c r="DV20" s="29"/>
-      <c r="DW20" s="29"/>
-      <c r="DX20" s="29"/>
-      <c r="DY20" s="29"/>
-      <c r="DZ20" s="29"/>
-      <c r="EA20" s="29"/>
-      <c r="EB20" s="29"/>
-      <c r="EC20" s="29"/>
-      <c r="ED20" s="29"/>
-      <c r="EE20" s="29"/>
-      <c r="EF20" s="29"/>
-      <c r="EG20" s="29"/>
-      <c r="EH20" s="29"/>
-      <c r="EI20" s="29"/>
-      <c r="EJ20" s="29"/>
-      <c r="EK20" s="29"/>
-      <c r="EL20" s="29"/>
-      <c r="EM20" s="29"/>
-      <c r="EN20" s="29"/>
-      <c r="EO20" s="29"/>
-      <c r="EP20" s="29"/>
-      <c r="EQ20" s="29"/>
-      <c r="ER20" s="29"/>
-      <c r="ES20" s="29"/>
-      <c r="ET20" s="29"/>
-      <c r="EU20" s="29"/>
-      <c r="EV20" s="29"/>
-      <c r="EW20" s="29"/>
-      <c r="EX20" s="29"/>
-      <c r="EY20" s="29"/>
-      <c r="EZ20" s="29"/>
-      <c r="FA20" s="29"/>
-      <c r="FB20" s="29"/>
-      <c r="FC20" s="29"/>
-      <c r="FD20" s="29"/>
-      <c r="FE20" s="29"/>
-      <c r="FF20" s="29"/>
-      <c r="FG20" s="29"/>
-      <c r="FH20" s="29"/>
-      <c r="FI20" s="29"/>
-      <c r="FJ20" s="29"/>
-      <c r="FK20" s="29"/>
-      <c r="FL20" s="29"/>
-      <c r="FM20" s="29"/>
-      <c r="FN20" s="29"/>
-      <c r="FO20" s="29"/>
-      <c r="FP20" s="29"/>
-      <c r="FQ20" s="29"/>
-      <c r="FR20" s="29"/>
-      <c r="FS20" s="29"/>
-      <c r="FT20" s="29"/>
-      <c r="FU20" s="29"/>
-      <c r="FV20" s="29"/>
-      <c r="FW20" s="29"/>
-      <c r="FX20" s="29"/>
-      <c r="FY20" s="29"/>
-      <c r="FZ20" s="29"/>
-      <c r="GA20" s="29"/>
-      <c r="GB20" s="29"/>
-      <c r="GC20" s="29"/>
-      <c r="GD20" s="29"/>
-      <c r="GE20" s="29"/>
-      <c r="GF20" s="29"/>
-      <c r="GG20" s="29"/>
-      <c r="GH20" s="29"/>
-      <c r="GI20" s="29"/>
-      <c r="GJ20" s="29"/>
-      <c r="GK20" s="29"/>
-      <c r="GL20" s="29"/>
-      <c r="GM20" s="29"/>
-      <c r="GN20" s="29"/>
-      <c r="GO20" s="29"/>
-      <c r="GP20" s="29"/>
-      <c r="GQ20" s="29"/>
-      <c r="GR20" s="29"/>
-      <c r="GS20" s="29"/>
-      <c r="GT20" s="29"/>
-      <c r="GU20" s="29"/>
-      <c r="GV20" s="29"/>
-      <c r="GW20" s="29"/>
-      <c r="GX20" s="29"/>
-      <c r="GY20" s="29"/>
-      <c r="GZ20" s="29"/>
-      <c r="HA20" s="29"/>
-      <c r="HB20" s="29"/>
-      <c r="HC20" s="29"/>
-      <c r="HD20" s="29"/>
-      <c r="HE20" s="29"/>
-      <c r="HF20" s="29"/>
-      <c r="HG20" s="29"/>
-      <c r="HH20" s="29"/>
-      <c r="HI20" s="29"/>
-      <c r="HJ20" s="29"/>
-      <c r="HK20" s="29"/>
-      <c r="HL20" s="29"/>
-      <c r="HM20" s="29"/>
-      <c r="HN20" s="29"/>
-      <c r="HO20" s="29"/>
-      <c r="HP20" s="29"/>
-      <c r="HQ20" s="29"/>
-      <c r="HR20" s="29"/>
-      <c r="HS20" s="29"/>
-      <c r="HT20" s="29"/>
-      <c r="HU20" s="29"/>
+    <row r="20" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="27"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="25"/>
+      <c r="BQ20" s="26"/>
+      <c r="BS20" s="26"/>
+      <c r="BU20" s="26"/>
+      <c r="BW20" s="26"/>
+      <c r="BY20" s="26"/>
+      <c r="CA20" s="26"/>
+      <c r="CC20" s="26"/>
+      <c r="CE20" s="26"/>
+      <c r="CG20" s="26"/>
+      <c r="CI20" s="26"/>
+      <c r="CK20" s="26"/>
+      <c r="CL20" s="26"/>
+      <c r="CM20" s="26"/>
+      <c r="CN20" s="26"/>
+      <c r="CO20" s="26"/>
+      <c r="CP20" s="26"/>
+      <c r="CQ20" s="26"/>
+      <c r="CR20" s="26"/>
+      <c r="CS20" s="26"/>
+      <c r="CT20" s="26"/>
+      <c r="CU20" s="26"/>
+      <c r="CV20" s="26"/>
+      <c r="CW20" s="26"/>
+      <c r="CX20" s="26"/>
+      <c r="CY20" s="26"/>
+      <c r="CZ20" s="26"/>
+      <c r="DA20" s="26"/>
+      <c r="DB20" s="26"/>
+      <c r="DC20" s="26"/>
+      <c r="DD20" s="26"/>
+      <c r="DE20" s="26"/>
+      <c r="DF20" s="26"/>
+      <c r="DG20" s="26"/>
+      <c r="DH20" s="26"/>
+      <c r="DI20" s="26"/>
+      <c r="DJ20" s="26"/>
+      <c r="DK20" s="26"/>
+      <c r="DL20" s="26"/>
+      <c r="DM20" s="26"/>
+      <c r="DN20" s="26"/>
+      <c r="DO20" s="26"/>
+      <c r="DP20" s="26"/>
+      <c r="DQ20" s="26"/>
+      <c r="DR20" s="26"/>
+      <c r="DS20" s="26"/>
+      <c r="DT20" s="26"/>
+      <c r="DU20" s="26"/>
+      <c r="DV20" s="26"/>
+      <c r="DW20" s="26"/>
+      <c r="DX20" s="26"/>
+      <c r="DY20" s="26"/>
+      <c r="DZ20" s="26"/>
+      <c r="EA20" s="26"/>
+      <c r="EB20" s="26"/>
+      <c r="EC20" s="26"/>
+      <c r="ED20" s="26"/>
+      <c r="EE20" s="26"/>
+      <c r="EF20" s="26"/>
+      <c r="EG20" s="26"/>
+      <c r="EH20" s="26"/>
+      <c r="EI20" s="26"/>
+      <c r="EJ20" s="26"/>
+      <c r="EK20" s="26"/>
+      <c r="EL20" s="26"/>
+      <c r="EM20" s="26"/>
+      <c r="EN20" s="26"/>
+      <c r="EO20" s="26"/>
+      <c r="EP20" s="26"/>
+      <c r="EQ20" s="26"/>
+      <c r="ER20" s="26"/>
+      <c r="ES20" s="26"/>
+      <c r="ET20" s="26"/>
+      <c r="EU20" s="26"/>
+      <c r="EV20" s="26"/>
+      <c r="EW20" s="26"/>
+      <c r="EX20" s="26"/>
+      <c r="EY20" s="26"/>
+      <c r="EZ20" s="26"/>
+      <c r="FA20" s="26"/>
+      <c r="FB20" s="26"/>
+      <c r="FC20" s="26"/>
+      <c r="FD20" s="26"/>
+      <c r="FE20" s="26"/>
+      <c r="FF20" s="26"/>
+      <c r="FG20" s="26"/>
+      <c r="FH20" s="26"/>
+      <c r="FI20" s="26"/>
+      <c r="FJ20" s="26"/>
+      <c r="FK20" s="26"/>
+      <c r="FL20" s="26"/>
+      <c r="FM20" s="26"/>
+      <c r="FN20" s="26"/>
+      <c r="FO20" s="26"/>
+      <c r="FP20" s="26"/>
+      <c r="FQ20" s="26"/>
+      <c r="FR20" s="26"/>
+      <c r="FS20" s="26"/>
+      <c r="FT20" s="26"/>
+      <c r="FU20" s="26"/>
+      <c r="FV20" s="26"/>
+      <c r="FW20" s="26"/>
+      <c r="FX20" s="26"/>
+      <c r="FY20" s="26"/>
+      <c r="FZ20" s="26"/>
+      <c r="GA20" s="26"/>
+      <c r="GB20" s="26"/>
+      <c r="GC20" s="26"/>
+      <c r="GD20" s="26"/>
+      <c r="GE20" s="26"/>
+      <c r="GF20" s="26"/>
+      <c r="GG20" s="26"/>
+      <c r="GH20" s="26"/>
+      <c r="GI20" s="26"/>
+      <c r="GJ20" s="26"/>
+      <c r="GK20" s="26"/>
+      <c r="GL20" s="26"/>
+      <c r="GM20" s="26"/>
+      <c r="GN20" s="26"/>
+      <c r="GO20" s="26"/>
+      <c r="GP20" s="26"/>
+      <c r="GQ20" s="26"/>
+      <c r="GR20" s="26"/>
+      <c r="GS20" s="26"/>
+      <c r="GT20" s="26"/>
+      <c r="GU20" s="26"/>
+      <c r="GV20" s="26"/>
+      <c r="GW20" s="26"/>
+      <c r="GX20" s="26"/>
+      <c r="GY20" s="26"/>
+      <c r="GZ20" s="26"/>
+      <c r="HA20" s="26"/>
+      <c r="HB20" s="26"/>
+      <c r="HC20" s="26"/>
+      <c r="HD20" s="26"/>
+      <c r="HE20" s="26"/>
+      <c r="HF20" s="26"/>
+      <c r="HG20" s="26"/>
+      <c r="HH20" s="26"/>
+      <c r="HI20" s="26"/>
+      <c r="HJ20" s="26"/>
+      <c r="HK20" s="26"/>
+      <c r="HL20" s="26"/>
+      <c r="HM20" s="26"/>
+      <c r="HN20" s="26"/>
+      <c r="HO20" s="26"/>
+      <c r="HP20" s="26"/>
+      <c r="HQ20" s="26"/>
+      <c r="HR20" s="26"/>
+      <c r="HS20" s="26"/>
+      <c r="HT20" s="26"/>
+      <c r="HU20" s="26"/>
     </row>
-    <row r="21" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7">
-        <v>0</v>
-      </c>
-      <c r="H21" s="28"/>
-      <c r="BQ21" s="29"/>
-      <c r="BS21" s="29"/>
-      <c r="BU21" s="29"/>
-      <c r="BW21" s="29"/>
-      <c r="BY21" s="29"/>
-      <c r="CA21" s="29"/>
-      <c r="CC21" s="29"/>
-      <c r="CE21" s="29"/>
-      <c r="CG21" s="29"/>
-      <c r="CI21" s="29"/>
-      <c r="CK21" s="29"/>
-      <c r="CL21" s="29"/>
-      <c r="CM21" s="29"/>
-      <c r="CN21" s="29"/>
-      <c r="CO21" s="29"/>
-      <c r="CP21" s="29"/>
-      <c r="CQ21" s="29"/>
-      <c r="CR21" s="29"/>
-      <c r="CS21" s="29"/>
-      <c r="CT21" s="29"/>
-      <c r="CU21" s="29"/>
-      <c r="CV21" s="29"/>
-      <c r="CW21" s="29"/>
-      <c r="CX21" s="29"/>
-      <c r="CY21" s="29"/>
-      <c r="CZ21" s="29"/>
-      <c r="DA21" s="29"/>
-      <c r="DB21" s="29"/>
-      <c r="DC21" s="29"/>
-      <c r="DD21" s="29"/>
-      <c r="DE21" s="29"/>
-      <c r="DF21" s="29"/>
-      <c r="DG21" s="29"/>
-      <c r="DH21" s="29"/>
-      <c r="DI21" s="29"/>
-      <c r="DJ21" s="29"/>
-      <c r="DK21" s="29"/>
-      <c r="DL21" s="29"/>
-      <c r="DM21" s="29"/>
-      <c r="DN21" s="29"/>
-      <c r="DO21" s="29"/>
-      <c r="DP21" s="29"/>
-      <c r="DQ21" s="29"/>
-      <c r="DR21" s="29"/>
-      <c r="DS21" s="29"/>
-      <c r="DT21" s="29"/>
-      <c r="DU21" s="29"/>
-      <c r="DV21" s="29"/>
-      <c r="DW21" s="29"/>
-      <c r="DX21" s="29"/>
-      <c r="DY21" s="29"/>
-      <c r="DZ21" s="29"/>
-      <c r="EA21" s="29"/>
-      <c r="EB21" s="29"/>
-      <c r="EC21" s="29"/>
-      <c r="ED21" s="29"/>
-      <c r="EE21" s="29"/>
-      <c r="EF21" s="29"/>
-      <c r="EG21" s="29"/>
-      <c r="EH21" s="29"/>
-      <c r="EI21" s="29"/>
-      <c r="EJ21" s="29"/>
-      <c r="EK21" s="29"/>
-      <c r="EL21" s="29"/>
-      <c r="EM21" s="29"/>
-      <c r="EN21" s="29"/>
-      <c r="EO21" s="29"/>
-      <c r="EP21" s="29"/>
-      <c r="EQ21" s="29"/>
-      <c r="ER21" s="29"/>
-      <c r="ES21" s="29"/>
-      <c r="ET21" s="29"/>
-      <c r="EU21" s="29"/>
-      <c r="EV21" s="29"/>
-      <c r="EW21" s="29"/>
-      <c r="EX21" s="29"/>
-      <c r="EY21" s="29"/>
-      <c r="EZ21" s="29"/>
-      <c r="FA21" s="29"/>
-      <c r="FB21" s="29"/>
-      <c r="FC21" s="29"/>
-      <c r="FD21" s="29"/>
-      <c r="FE21" s="29"/>
-      <c r="FF21" s="29"/>
-      <c r="FG21" s="29"/>
-      <c r="FH21" s="29"/>
-      <c r="FI21" s="29"/>
-      <c r="FJ21" s="29"/>
-      <c r="FK21" s="29"/>
-      <c r="FL21" s="29"/>
-      <c r="FM21" s="29"/>
-      <c r="FN21" s="29"/>
-      <c r="FO21" s="29"/>
-      <c r="FP21" s="29"/>
-      <c r="FQ21" s="29"/>
-      <c r="FR21" s="29"/>
-      <c r="FS21" s="29"/>
-      <c r="FT21" s="29"/>
-      <c r="FU21" s="29"/>
-      <c r="FV21" s="29"/>
-      <c r="FW21" s="29"/>
-      <c r="FX21" s="29"/>
-      <c r="FY21" s="29"/>
-      <c r="FZ21" s="29"/>
-      <c r="GA21" s="29"/>
-      <c r="GB21" s="29"/>
-      <c r="GC21" s="29"/>
-      <c r="GD21" s="29"/>
-      <c r="GE21" s="29"/>
-      <c r="GF21" s="29"/>
-      <c r="GG21" s="29"/>
-      <c r="GH21" s="29"/>
-      <c r="GI21" s="29"/>
-      <c r="GJ21" s="29"/>
-      <c r="GK21" s="29"/>
-      <c r="GL21" s="29"/>
-      <c r="GM21" s="29"/>
-      <c r="GN21" s="29"/>
-      <c r="GO21" s="29"/>
-      <c r="GP21" s="29"/>
-      <c r="GQ21" s="29"/>
-      <c r="GR21" s="29"/>
-      <c r="GS21" s="29"/>
-      <c r="GT21" s="29"/>
-      <c r="GU21" s="29"/>
-      <c r="GV21" s="29"/>
-      <c r="GW21" s="29"/>
-      <c r="GX21" s="29"/>
-      <c r="GY21" s="29"/>
-      <c r="GZ21" s="29"/>
-      <c r="HA21" s="29"/>
-      <c r="HB21" s="29"/>
-      <c r="HC21" s="29"/>
-      <c r="HD21" s="29"/>
-      <c r="HE21" s="29"/>
-      <c r="HF21" s="29"/>
-      <c r="HG21" s="29"/>
-      <c r="HH21" s="29"/>
-      <c r="HI21" s="29"/>
-      <c r="HJ21" s="29"/>
-      <c r="HK21" s="29"/>
-      <c r="HL21" s="29"/>
-      <c r="HM21" s="29"/>
-      <c r="HN21" s="29"/>
-      <c r="HO21" s="29"/>
-      <c r="HP21" s="29"/>
-      <c r="HQ21" s="29"/>
-      <c r="HR21" s="29"/>
-      <c r="HS21" s="29"/>
-      <c r="HT21" s="29"/>
-      <c r="HU21" s="29"/>
+    <row r="21" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="27"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="25"/>
+      <c r="BQ21" s="26"/>
+      <c r="BS21" s="26"/>
+      <c r="BU21" s="26"/>
+      <c r="BW21" s="26"/>
+      <c r="BY21" s="26"/>
+      <c r="CA21" s="26"/>
+      <c r="CC21" s="26"/>
+      <c r="CE21" s="26"/>
+      <c r="CG21" s="26"/>
+      <c r="CI21" s="26"/>
+      <c r="CK21" s="26"/>
+      <c r="CL21" s="26"/>
+      <c r="CM21" s="26"/>
+      <c r="CN21" s="26"/>
+      <c r="CO21" s="26"/>
+      <c r="CP21" s="26"/>
+      <c r="CQ21" s="26"/>
+      <c r="CR21" s="26"/>
+      <c r="CS21" s="26"/>
+      <c r="CT21" s="26"/>
+      <c r="CU21" s="26"/>
+      <c r="CV21" s="26"/>
+      <c r="CW21" s="26"/>
+      <c r="CX21" s="26"/>
+      <c r="CY21" s="26"/>
+      <c r="CZ21" s="26"/>
+      <c r="DA21" s="26"/>
+      <c r="DB21" s="26"/>
+      <c r="DC21" s="26"/>
+      <c r="DD21" s="26"/>
+      <c r="DE21" s="26"/>
+      <c r="DF21" s="26"/>
+      <c r="DG21" s="26"/>
+      <c r="DH21" s="26"/>
+      <c r="DI21" s="26"/>
+      <c r="DJ21" s="26"/>
+      <c r="DK21" s="26"/>
+      <c r="DL21" s="26"/>
+      <c r="DM21" s="26"/>
+      <c r="DN21" s="26"/>
+      <c r="DO21" s="26"/>
+      <c r="DP21" s="26"/>
+      <c r="DQ21" s="26"/>
+      <c r="DR21" s="26"/>
+      <c r="DS21" s="26"/>
+      <c r="DT21" s="26"/>
+      <c r="DU21" s="26"/>
+      <c r="DV21" s="26"/>
+      <c r="DW21" s="26"/>
+      <c r="DX21" s="26"/>
+      <c r="DY21" s="26"/>
+      <c r="DZ21" s="26"/>
+      <c r="EA21" s="26"/>
+      <c r="EB21" s="26"/>
+      <c r="EC21" s="26"/>
+      <c r="ED21" s="26"/>
+      <c r="EE21" s="26"/>
+      <c r="EF21" s="26"/>
+      <c r="EG21" s="26"/>
+      <c r="EH21" s="26"/>
+      <c r="EI21" s="26"/>
+      <c r="EJ21" s="26"/>
+      <c r="EK21" s="26"/>
+      <c r="EL21" s="26"/>
+      <c r="EM21" s="26"/>
+      <c r="EN21" s="26"/>
+      <c r="EO21" s="26"/>
+      <c r="EP21" s="26"/>
+      <c r="EQ21" s="26"/>
+      <c r="ER21" s="26"/>
+      <c r="ES21" s="26"/>
+      <c r="ET21" s="26"/>
+      <c r="EU21" s="26"/>
+      <c r="EV21" s="26"/>
+      <c r="EW21" s="26"/>
+      <c r="EX21" s="26"/>
+      <c r="EY21" s="26"/>
+      <c r="EZ21" s="26"/>
+      <c r="FA21" s="26"/>
+      <c r="FB21" s="26"/>
+      <c r="FC21" s="26"/>
+      <c r="FD21" s="26"/>
+      <c r="FE21" s="26"/>
+      <c r="FF21" s="26"/>
+      <c r="FG21" s="26"/>
+      <c r="FH21" s="26"/>
+      <c r="FI21" s="26"/>
+      <c r="FJ21" s="26"/>
+      <c r="FK21" s="26"/>
+      <c r="FL21" s="26"/>
+      <c r="FM21" s="26"/>
+      <c r="FN21" s="26"/>
+      <c r="FO21" s="26"/>
+      <c r="FP21" s="26"/>
+      <c r="FQ21" s="26"/>
+      <c r="FR21" s="26"/>
+      <c r="FS21" s="26"/>
+      <c r="FT21" s="26"/>
+      <c r="FU21" s="26"/>
+      <c r="FV21" s="26"/>
+      <c r="FW21" s="26"/>
+      <c r="FX21" s="26"/>
+      <c r="FY21" s="26"/>
+      <c r="FZ21" s="26"/>
+      <c r="GA21" s="26"/>
+      <c r="GB21" s="26"/>
+      <c r="GC21" s="26"/>
+      <c r="GD21" s="26"/>
+      <c r="GE21" s="26"/>
+      <c r="GF21" s="26"/>
+      <c r="GG21" s="26"/>
+      <c r="GH21" s="26"/>
+      <c r="GI21" s="26"/>
+      <c r="GJ21" s="26"/>
+      <c r="GK21" s="26"/>
+      <c r="GL21" s="26"/>
+      <c r="GM21" s="26"/>
+      <c r="GN21" s="26"/>
+      <c r="GO21" s="26"/>
+      <c r="GP21" s="26"/>
+      <c r="GQ21" s="26"/>
+      <c r="GR21" s="26"/>
+      <c r="GS21" s="26"/>
+      <c r="GT21" s="26"/>
+      <c r="GU21" s="26"/>
+      <c r="GV21" s="26"/>
+      <c r="GW21" s="26"/>
+      <c r="GX21" s="26"/>
+      <c r="GY21" s="26"/>
+      <c r="GZ21" s="26"/>
+      <c r="HA21" s="26"/>
+      <c r="HB21" s="26"/>
+      <c r="HC21" s="26"/>
+      <c r="HD21" s="26"/>
+      <c r="HE21" s="26"/>
+      <c r="HF21" s="26"/>
+      <c r="HG21" s="26"/>
+      <c r="HH21" s="26"/>
+      <c r="HI21" s="26"/>
+      <c r="HJ21" s="26"/>
+      <c r="HK21" s="26"/>
+      <c r="HL21" s="26"/>
+      <c r="HM21" s="26"/>
+      <c r="HN21" s="26"/>
+      <c r="HO21" s="26"/>
+      <c r="HP21" s="26"/>
+      <c r="HQ21" s="26"/>
+      <c r="HR21" s="26"/>
+      <c r="HS21" s="26"/>
+      <c r="HT21" s="26"/>
+      <c r="HU21" s="26"/>
     </row>
-    <row r="22" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7">
-        <v>0</v>
-      </c>
-      <c r="H22" s="28"/>
-      <c r="BQ22" s="29"/>
-      <c r="BS22" s="29"/>
-      <c r="BU22" s="29"/>
-      <c r="BW22" s="29"/>
-      <c r="BY22" s="29"/>
-      <c r="CA22" s="29"/>
-      <c r="CC22" s="29"/>
-      <c r="CE22" s="29"/>
-      <c r="CG22" s="29"/>
-      <c r="CI22" s="29"/>
-      <c r="CK22" s="29"/>
-      <c r="CL22" s="29"/>
-      <c r="CM22" s="29"/>
-      <c r="CN22" s="29"/>
-      <c r="CO22" s="29"/>
-      <c r="CP22" s="29"/>
-      <c r="CQ22" s="29"/>
-      <c r="CR22" s="29"/>
-      <c r="CS22" s="29"/>
-      <c r="CT22" s="29"/>
-      <c r="CU22" s="29"/>
-      <c r="CV22" s="29"/>
-      <c r="CW22" s="29"/>
-      <c r="CX22" s="29"/>
-      <c r="CY22" s="29"/>
-      <c r="CZ22" s="29"/>
-      <c r="DA22" s="29"/>
-      <c r="DB22" s="29"/>
-      <c r="DC22" s="29"/>
-      <c r="DD22" s="29"/>
-      <c r="DE22" s="29"/>
-      <c r="DF22" s="29"/>
-      <c r="DG22" s="29"/>
-      <c r="DH22" s="29"/>
-      <c r="DI22" s="29"/>
-      <c r="DJ22" s="29"/>
-      <c r="DK22" s="29"/>
-      <c r="DL22" s="29"/>
-      <c r="DM22" s="29"/>
-      <c r="DN22" s="29"/>
-      <c r="DO22" s="29"/>
-      <c r="DP22" s="29"/>
-      <c r="DQ22" s="29"/>
-      <c r="DR22" s="29"/>
-      <c r="DS22" s="29"/>
-      <c r="DT22" s="29"/>
-      <c r="DU22" s="29"/>
-      <c r="DV22" s="29"/>
-      <c r="DW22" s="29"/>
-      <c r="DX22" s="29"/>
-      <c r="DY22" s="29"/>
-      <c r="DZ22" s="29"/>
-      <c r="EA22" s="29"/>
-      <c r="EB22" s="29"/>
-      <c r="EC22" s="29"/>
-      <c r="ED22" s="29"/>
-      <c r="EE22" s="29"/>
-      <c r="EF22" s="29"/>
-      <c r="EG22" s="29"/>
-      <c r="EH22" s="29"/>
-      <c r="EI22" s="29"/>
-      <c r="EJ22" s="29"/>
-      <c r="EK22" s="29"/>
-      <c r="EL22" s="29"/>
-      <c r="EM22" s="29"/>
-      <c r="EN22" s="29"/>
-      <c r="EO22" s="29"/>
-      <c r="EP22" s="29"/>
-      <c r="EQ22" s="29"/>
-      <c r="ER22" s="29"/>
-      <c r="ES22" s="29"/>
-      <c r="ET22" s="29"/>
-      <c r="EU22" s="29"/>
-      <c r="EV22" s="29"/>
-      <c r="EW22" s="29"/>
-      <c r="EX22" s="29"/>
-      <c r="EY22" s="29"/>
-      <c r="EZ22" s="29"/>
-      <c r="FA22" s="29"/>
-      <c r="FB22" s="29"/>
-      <c r="FC22" s="29"/>
-      <c r="FD22" s="29"/>
-      <c r="FE22" s="29"/>
-      <c r="FF22" s="29"/>
-      <c r="FG22" s="29"/>
-      <c r="FH22" s="29"/>
-      <c r="FI22" s="29"/>
-      <c r="FJ22" s="29"/>
-      <c r="FK22" s="29"/>
-      <c r="FL22" s="29"/>
-      <c r="FM22" s="29"/>
-      <c r="FN22" s="29"/>
-      <c r="FO22" s="29"/>
-      <c r="FP22" s="29"/>
-      <c r="FQ22" s="29"/>
-      <c r="FR22" s="29"/>
-      <c r="FS22" s="29"/>
-      <c r="FT22" s="29"/>
-      <c r="FU22" s="29"/>
-      <c r="FV22" s="29"/>
-      <c r="FW22" s="29"/>
-      <c r="FX22" s="29"/>
-      <c r="FY22" s="29"/>
-      <c r="FZ22" s="29"/>
-      <c r="GA22" s="29"/>
-      <c r="GB22" s="29"/>
-      <c r="GC22" s="29"/>
-      <c r="GD22" s="29"/>
-      <c r="GE22" s="29"/>
-      <c r="GF22" s="29"/>
-      <c r="GG22" s="29"/>
-      <c r="GH22" s="29"/>
-      <c r="GI22" s="29"/>
-      <c r="GJ22" s="29"/>
-      <c r="GK22" s="29"/>
-      <c r="GL22" s="29"/>
-      <c r="GM22" s="29"/>
-      <c r="GN22" s="29"/>
-      <c r="GO22" s="29"/>
-      <c r="GP22" s="29"/>
-      <c r="GQ22" s="29"/>
-      <c r="GR22" s="29"/>
-      <c r="GS22" s="29"/>
-      <c r="GT22" s="29"/>
-      <c r="GU22" s="29"/>
-      <c r="GV22" s="29"/>
-      <c r="GW22" s="29"/>
-      <c r="GX22" s="29"/>
-      <c r="GY22" s="29"/>
-      <c r="GZ22" s="29"/>
-      <c r="HA22" s="29"/>
-      <c r="HB22" s="29"/>
-      <c r="HC22" s="29"/>
-      <c r="HD22" s="29"/>
-      <c r="HE22" s="29"/>
-      <c r="HF22" s="29"/>
-      <c r="HG22" s="29"/>
-      <c r="HH22" s="29"/>
-      <c r="HI22" s="29"/>
-      <c r="HJ22" s="29"/>
-      <c r="HK22" s="29"/>
-      <c r="HL22" s="29"/>
-      <c r="HM22" s="29"/>
-      <c r="HN22" s="29"/>
-      <c r="HO22" s="29"/>
-      <c r="HP22" s="29"/>
-      <c r="HQ22" s="29"/>
-      <c r="HR22" s="29"/>
-      <c r="HS22" s="29"/>
-      <c r="HT22" s="29"/>
-      <c r="HU22" s="29"/>
+    <row r="22" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="27"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="25"/>
+      <c r="BQ22" s="26"/>
+      <c r="BS22" s="26"/>
+      <c r="BU22" s="26"/>
+      <c r="BW22" s="26"/>
+      <c r="BY22" s="26"/>
+      <c r="CA22" s="26"/>
+      <c r="CC22" s="26"/>
+      <c r="CE22" s="26"/>
+      <c r="CG22" s="26"/>
+      <c r="CI22" s="26"/>
+      <c r="CK22" s="26"/>
+      <c r="CL22" s="26"/>
+      <c r="CM22" s="26"/>
+      <c r="CN22" s="26"/>
+      <c r="CO22" s="26"/>
+      <c r="CP22" s="26"/>
+      <c r="CQ22" s="26"/>
+      <c r="CR22" s="26"/>
+      <c r="CS22" s="26"/>
+      <c r="CT22" s="26"/>
+      <c r="CU22" s="26"/>
+      <c r="CV22" s="26"/>
+      <c r="CW22" s="26"/>
+      <c r="CX22" s="26"/>
+      <c r="CY22" s="26"/>
+      <c r="CZ22" s="26"/>
+      <c r="DA22" s="26"/>
+      <c r="DB22" s="26"/>
+      <c r="DC22" s="26"/>
+      <c r="DD22" s="26"/>
+      <c r="DE22" s="26"/>
+      <c r="DF22" s="26"/>
+      <c r="DG22" s="26"/>
+      <c r="DH22" s="26"/>
+      <c r="DI22" s="26"/>
+      <c r="DJ22" s="26"/>
+      <c r="DK22" s="26"/>
+      <c r="DL22" s="26"/>
+      <c r="DM22" s="26"/>
+      <c r="DN22" s="26"/>
+      <c r="DO22" s="26"/>
+      <c r="DP22" s="26"/>
+      <c r="DQ22" s="26"/>
+      <c r="DR22" s="26"/>
+      <c r="DS22" s="26"/>
+      <c r="DT22" s="26"/>
+      <c r="DU22" s="26"/>
+      <c r="DV22" s="26"/>
+      <c r="DW22" s="26"/>
+      <c r="DX22" s="26"/>
+      <c r="DY22" s="26"/>
+      <c r="DZ22" s="26"/>
+      <c r="EA22" s="26"/>
+      <c r="EB22" s="26"/>
+      <c r="EC22" s="26"/>
+      <c r="ED22" s="26"/>
+      <c r="EE22" s="26"/>
+      <c r="EF22" s="26"/>
+      <c r="EG22" s="26"/>
+      <c r="EH22" s="26"/>
+      <c r="EI22" s="26"/>
+      <c r="EJ22" s="26"/>
+      <c r="EK22" s="26"/>
+      <c r="EL22" s="26"/>
+      <c r="EM22" s="26"/>
+      <c r="EN22" s="26"/>
+      <c r="EO22" s="26"/>
+      <c r="EP22" s="26"/>
+      <c r="EQ22" s="26"/>
+      <c r="ER22" s="26"/>
+      <c r="ES22" s="26"/>
+      <c r="ET22" s="26"/>
+      <c r="EU22" s="26"/>
+      <c r="EV22" s="26"/>
+      <c r="EW22" s="26"/>
+      <c r="EX22" s="26"/>
+      <c r="EY22" s="26"/>
+      <c r="EZ22" s="26"/>
+      <c r="FA22" s="26"/>
+      <c r="FB22" s="26"/>
+      <c r="FC22" s="26"/>
+      <c r="FD22" s="26"/>
+      <c r="FE22" s="26"/>
+      <c r="FF22" s="26"/>
+      <c r="FG22" s="26"/>
+      <c r="FH22" s="26"/>
+      <c r="FI22" s="26"/>
+      <c r="FJ22" s="26"/>
+      <c r="FK22" s="26"/>
+      <c r="FL22" s="26"/>
+      <c r="FM22" s="26"/>
+      <c r="FN22" s="26"/>
+      <c r="FO22" s="26"/>
+      <c r="FP22" s="26"/>
+      <c r="FQ22" s="26"/>
+      <c r="FR22" s="26"/>
+      <c r="FS22" s="26"/>
+      <c r="FT22" s="26"/>
+      <c r="FU22" s="26"/>
+      <c r="FV22" s="26"/>
+      <c r="FW22" s="26"/>
+      <c r="FX22" s="26"/>
+      <c r="FY22" s="26"/>
+      <c r="FZ22" s="26"/>
+      <c r="GA22" s="26"/>
+      <c r="GB22" s="26"/>
+      <c r="GC22" s="26"/>
+      <c r="GD22" s="26"/>
+      <c r="GE22" s="26"/>
+      <c r="GF22" s="26"/>
+      <c r="GG22" s="26"/>
+      <c r="GH22" s="26"/>
+      <c r="GI22" s="26"/>
+      <c r="GJ22" s="26"/>
+      <c r="GK22" s="26"/>
+      <c r="GL22" s="26"/>
+      <c r="GM22" s="26"/>
+      <c r="GN22" s="26"/>
+      <c r="GO22" s="26"/>
+      <c r="GP22" s="26"/>
+      <c r="GQ22" s="26"/>
+      <c r="GR22" s="26"/>
+      <c r="GS22" s="26"/>
+      <c r="GT22" s="26"/>
+      <c r="GU22" s="26"/>
+      <c r="GV22" s="26"/>
+      <c r="GW22" s="26"/>
+      <c r="GX22" s="26"/>
+      <c r="GY22" s="26"/>
+      <c r="GZ22" s="26"/>
+      <c r="HA22" s="26"/>
+      <c r="HB22" s="26"/>
+      <c r="HC22" s="26"/>
+      <c r="HD22" s="26"/>
+      <c r="HE22" s="26"/>
+      <c r="HF22" s="26"/>
+      <c r="HG22" s="26"/>
+      <c r="HH22" s="26"/>
+      <c r="HI22" s="26"/>
+      <c r="HJ22" s="26"/>
+      <c r="HK22" s="26"/>
+      <c r="HL22" s="26"/>
+      <c r="HM22" s="26"/>
+      <c r="HN22" s="26"/>
+      <c r="HO22" s="26"/>
+      <c r="HP22" s="26"/>
+      <c r="HQ22" s="26"/>
+      <c r="HR22" s="26"/>
+      <c r="HS22" s="26"/>
+      <c r="HT22" s="26"/>
+      <c r="HU22" s="26"/>
     </row>
-    <row r="23" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7">
-        <v>0</v>
-      </c>
-      <c r="H23" s="28"/>
-      <c r="BQ23" s="29"/>
-      <c r="BS23" s="29"/>
-      <c r="BU23" s="29"/>
-      <c r="BW23" s="29"/>
-      <c r="BY23" s="29"/>
-      <c r="CA23" s="29"/>
-      <c r="CC23" s="29"/>
-      <c r="CE23" s="29"/>
-      <c r="CG23" s="29"/>
-      <c r="CI23" s="29"/>
-      <c r="CK23" s="29"/>
-      <c r="CL23" s="29"/>
-      <c r="CM23" s="29"/>
-      <c r="CN23" s="29"/>
-      <c r="CO23" s="29"/>
-      <c r="CP23" s="29"/>
-      <c r="CQ23" s="29"/>
-      <c r="CR23" s="29"/>
-      <c r="CS23" s="29"/>
-      <c r="CT23" s="29"/>
-      <c r="CU23" s="29"/>
-      <c r="CV23" s="29"/>
-      <c r="CW23" s="29"/>
-      <c r="CX23" s="29"/>
-      <c r="CY23" s="29"/>
-      <c r="CZ23" s="29"/>
-      <c r="DA23" s="29"/>
-      <c r="DB23" s="29"/>
-      <c r="DC23" s="29"/>
-      <c r="DD23" s="29"/>
-      <c r="DE23" s="29"/>
-      <c r="DF23" s="29"/>
-      <c r="DG23" s="29"/>
-      <c r="DH23" s="29"/>
-      <c r="DI23" s="29"/>
-      <c r="DJ23" s="29"/>
-      <c r="DK23" s="29"/>
-      <c r="DL23" s="29"/>
-      <c r="DM23" s="29"/>
-      <c r="DN23" s="29"/>
-      <c r="DO23" s="29"/>
-      <c r="DP23" s="29"/>
-      <c r="DQ23" s="29"/>
-      <c r="DR23" s="29"/>
-      <c r="DS23" s="29"/>
-      <c r="DT23" s="29"/>
-      <c r="DU23" s="29"/>
-      <c r="DV23" s="29"/>
-      <c r="DW23" s="29"/>
-      <c r="DX23" s="29"/>
-      <c r="DY23" s="29"/>
-      <c r="DZ23" s="29"/>
-      <c r="EA23" s="29"/>
-      <c r="EB23" s="29"/>
-      <c r="EC23" s="29"/>
-      <c r="ED23" s="29"/>
-      <c r="EE23" s="29"/>
-      <c r="EF23" s="29"/>
-      <c r="EG23" s="29"/>
-      <c r="EH23" s="29"/>
-      <c r="EI23" s="29"/>
-      <c r="EJ23" s="29"/>
-      <c r="EK23" s="29"/>
-      <c r="EL23" s="29"/>
-      <c r="EM23" s="29"/>
-      <c r="EN23" s="29"/>
-      <c r="EO23" s="29"/>
-      <c r="EP23" s="29"/>
-      <c r="EQ23" s="29"/>
-      <c r="ER23" s="29"/>
-      <c r="ES23" s="29"/>
-      <c r="ET23" s="29"/>
-      <c r="EU23" s="29"/>
-      <c r="EV23" s="29"/>
-      <c r="EW23" s="29"/>
-      <c r="EX23" s="29"/>
-      <c r="EY23" s="29"/>
-      <c r="EZ23" s="29"/>
-      <c r="FA23" s="29"/>
-      <c r="FB23" s="29"/>
-      <c r="FC23" s="29"/>
-      <c r="FD23" s="29"/>
-      <c r="FE23" s="29"/>
-      <c r="FF23" s="29"/>
-      <c r="FG23" s="29"/>
-      <c r="FH23" s="29"/>
-      <c r="FI23" s="29"/>
-      <c r="FJ23" s="29"/>
-      <c r="FK23" s="29"/>
-      <c r="FL23" s="29"/>
-      <c r="FM23" s="29"/>
-      <c r="FN23" s="29"/>
-      <c r="FO23" s="29"/>
-      <c r="FP23" s="29"/>
-      <c r="FQ23" s="29"/>
-      <c r="FR23" s="29"/>
-      <c r="FS23" s="29"/>
-      <c r="FT23" s="29"/>
-      <c r="FU23" s="29"/>
-      <c r="FV23" s="29"/>
-      <c r="FW23" s="29"/>
-      <c r="FX23" s="29"/>
-      <c r="FY23" s="29"/>
-      <c r="FZ23" s="29"/>
-      <c r="GA23" s="29"/>
-      <c r="GB23" s="29"/>
-      <c r="GC23" s="29"/>
-      <c r="GD23" s="29"/>
-      <c r="GE23" s="29"/>
-      <c r="GF23" s="29"/>
-      <c r="GG23" s="29"/>
-      <c r="GH23" s="29"/>
-      <c r="GI23" s="29"/>
-      <c r="GJ23" s="29"/>
-      <c r="GK23" s="29"/>
-      <c r="GL23" s="29"/>
-      <c r="GM23" s="29"/>
-      <c r="GN23" s="29"/>
-      <c r="GO23" s="29"/>
-      <c r="GP23" s="29"/>
-      <c r="GQ23" s="29"/>
-      <c r="GR23" s="29"/>
-      <c r="GS23" s="29"/>
-      <c r="GT23" s="29"/>
-      <c r="GU23" s="29"/>
-      <c r="GV23" s="29"/>
-      <c r="GW23" s="29"/>
-      <c r="GX23" s="29"/>
-      <c r="GY23" s="29"/>
-      <c r="GZ23" s="29"/>
-      <c r="HA23" s="29"/>
-      <c r="HB23" s="29"/>
-      <c r="HC23" s="29"/>
-      <c r="HD23" s="29"/>
-      <c r="HE23" s="29"/>
-      <c r="HF23" s="29"/>
-      <c r="HG23" s="29"/>
-      <c r="HH23" s="29"/>
-      <c r="HI23" s="29"/>
-      <c r="HJ23" s="29"/>
-      <c r="HK23" s="29"/>
-      <c r="HL23" s="29"/>
-      <c r="HM23" s="29"/>
-      <c r="HN23" s="29"/>
-      <c r="HO23" s="29"/>
-      <c r="HP23" s="29"/>
-      <c r="HQ23" s="29"/>
-      <c r="HR23" s="29"/>
-      <c r="HS23" s="29"/>
-      <c r="HT23" s="29"/>
-      <c r="HU23" s="29"/>
+    <row r="23" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="27"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="25"/>
+      <c r="BQ23" s="26"/>
+      <c r="BS23" s="26"/>
+      <c r="BU23" s="26"/>
+      <c r="BW23" s="26"/>
+      <c r="BY23" s="26"/>
+      <c r="CA23" s="26"/>
+      <c r="CC23" s="26"/>
+      <c r="CE23" s="26"/>
+      <c r="CG23" s="26"/>
+      <c r="CI23" s="26"/>
+      <c r="CK23" s="26"/>
+      <c r="CL23" s="26"/>
+      <c r="CM23" s="26"/>
+      <c r="CN23" s="26"/>
+      <c r="CO23" s="26"/>
+      <c r="CP23" s="26"/>
+      <c r="CQ23" s="26"/>
+      <c r="CR23" s="26"/>
+      <c r="CS23" s="26"/>
+      <c r="CT23" s="26"/>
+      <c r="CU23" s="26"/>
+      <c r="CV23" s="26"/>
+      <c r="CW23" s="26"/>
+      <c r="CX23" s="26"/>
+      <c r="CY23" s="26"/>
+      <c r="CZ23" s="26"/>
+      <c r="DA23" s="26"/>
+      <c r="DB23" s="26"/>
+      <c r="DC23" s="26"/>
+      <c r="DD23" s="26"/>
+      <c r="DE23" s="26"/>
+      <c r="DF23" s="26"/>
+      <c r="DG23" s="26"/>
+      <c r="DH23" s="26"/>
+      <c r="DI23" s="26"/>
+      <c r="DJ23" s="26"/>
+      <c r="DK23" s="26"/>
+      <c r="DL23" s="26"/>
+      <c r="DM23" s="26"/>
+      <c r="DN23" s="26"/>
+      <c r="DO23" s="26"/>
+      <c r="DP23" s="26"/>
+      <c r="DQ23" s="26"/>
+      <c r="DR23" s="26"/>
+      <c r="DS23" s="26"/>
+      <c r="DT23" s="26"/>
+      <c r="DU23" s="26"/>
+      <c r="DV23" s="26"/>
+      <c r="DW23" s="26"/>
+      <c r="DX23" s="26"/>
+      <c r="DY23" s="26"/>
+      <c r="DZ23" s="26"/>
+      <c r="EA23" s="26"/>
+      <c r="EB23" s="26"/>
+      <c r="EC23" s="26"/>
+      <c r="ED23" s="26"/>
+      <c r="EE23" s="26"/>
+      <c r="EF23" s="26"/>
+      <c r="EG23" s="26"/>
+      <c r="EH23" s="26"/>
+      <c r="EI23" s="26"/>
+      <c r="EJ23" s="26"/>
+      <c r="EK23" s="26"/>
+      <c r="EL23" s="26"/>
+      <c r="EM23" s="26"/>
+      <c r="EN23" s="26"/>
+      <c r="EO23" s="26"/>
+      <c r="EP23" s="26"/>
+      <c r="EQ23" s="26"/>
+      <c r="ER23" s="26"/>
+      <c r="ES23" s="26"/>
+      <c r="ET23" s="26"/>
+      <c r="EU23" s="26"/>
+      <c r="EV23" s="26"/>
+      <c r="EW23" s="26"/>
+      <c r="EX23" s="26"/>
+      <c r="EY23" s="26"/>
+      <c r="EZ23" s="26"/>
+      <c r="FA23" s="26"/>
+      <c r="FB23" s="26"/>
+      <c r="FC23" s="26"/>
+      <c r="FD23" s="26"/>
+      <c r="FE23" s="26"/>
+      <c r="FF23" s="26"/>
+      <c r="FG23" s="26"/>
+      <c r="FH23" s="26"/>
+      <c r="FI23" s="26"/>
+      <c r="FJ23" s="26"/>
+      <c r="FK23" s="26"/>
+      <c r="FL23" s="26"/>
+      <c r="FM23" s="26"/>
+      <c r="FN23" s="26"/>
+      <c r="FO23" s="26"/>
+      <c r="FP23" s="26"/>
+      <c r="FQ23" s="26"/>
+      <c r="FR23" s="26"/>
+      <c r="FS23" s="26"/>
+      <c r="FT23" s="26"/>
+      <c r="FU23" s="26"/>
+      <c r="FV23" s="26"/>
+      <c r="FW23" s="26"/>
+      <c r="FX23" s="26"/>
+      <c r="FY23" s="26"/>
+      <c r="FZ23" s="26"/>
+      <c r="GA23" s="26"/>
+      <c r="GB23" s="26"/>
+      <c r="GC23" s="26"/>
+      <c r="GD23" s="26"/>
+      <c r="GE23" s="26"/>
+      <c r="GF23" s="26"/>
+      <c r="GG23" s="26"/>
+      <c r="GH23" s="26"/>
+      <c r="GI23" s="26"/>
+      <c r="GJ23" s="26"/>
+      <c r="GK23" s="26"/>
+      <c r="GL23" s="26"/>
+      <c r="GM23" s="26"/>
+      <c r="GN23" s="26"/>
+      <c r="GO23" s="26"/>
+      <c r="GP23" s="26"/>
+      <c r="GQ23" s="26"/>
+      <c r="GR23" s="26"/>
+      <c r="GS23" s="26"/>
+      <c r="GT23" s="26"/>
+      <c r="GU23" s="26"/>
+      <c r="GV23" s="26"/>
+      <c r="GW23" s="26"/>
+      <c r="GX23" s="26"/>
+      <c r="GY23" s="26"/>
+      <c r="GZ23" s="26"/>
+      <c r="HA23" s="26"/>
+      <c r="HB23" s="26"/>
+      <c r="HC23" s="26"/>
+      <c r="HD23" s="26"/>
+      <c r="HE23" s="26"/>
+      <c r="HF23" s="26"/>
+      <c r="HG23" s="26"/>
+      <c r="HH23" s="26"/>
+      <c r="HI23" s="26"/>
+      <c r="HJ23" s="26"/>
+      <c r="HK23" s="26"/>
+      <c r="HL23" s="26"/>
+      <c r="HM23" s="26"/>
+      <c r="HN23" s="26"/>
+      <c r="HO23" s="26"/>
+      <c r="HP23" s="26"/>
+      <c r="HQ23" s="26"/>
+      <c r="HR23" s="26"/>
+      <c r="HS23" s="26"/>
+      <c r="HT23" s="26"/>
+      <c r="HU23" s="26"/>
     </row>
-    <row r="24" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>0</v>
-      </c>
-      <c r="H24" s="28"/>
-      <c r="BQ24" s="29"/>
-      <c r="BS24" s="29"/>
-      <c r="BU24" s="29"/>
-      <c r="BW24" s="29"/>
-      <c r="BY24" s="29"/>
-      <c r="CA24" s="29"/>
-      <c r="CC24" s="29"/>
-      <c r="CE24" s="29"/>
-      <c r="CG24" s="29"/>
-      <c r="CI24" s="29"/>
-      <c r="CK24" s="29"/>
-      <c r="CL24" s="29"/>
-      <c r="CM24" s="29"/>
-      <c r="CN24" s="29"/>
-      <c r="CO24" s="29"/>
-      <c r="CP24" s="29"/>
-      <c r="CQ24" s="29"/>
-      <c r="CR24" s="29"/>
-      <c r="CS24" s="29"/>
-      <c r="CT24" s="29"/>
-      <c r="CU24" s="29"/>
-      <c r="CV24" s="29"/>
-      <c r="CW24" s="29"/>
-      <c r="CX24" s="29"/>
-      <c r="CY24" s="29"/>
-      <c r="CZ24" s="29"/>
-      <c r="DA24" s="29"/>
-      <c r="DB24" s="29"/>
-      <c r="DC24" s="29"/>
-      <c r="DD24" s="29"/>
-      <c r="DE24" s="29"/>
-      <c r="DF24" s="29"/>
-      <c r="DG24" s="29"/>
-      <c r="DH24" s="29"/>
-      <c r="DI24" s="29"/>
-      <c r="DJ24" s="29"/>
-      <c r="DK24" s="29"/>
-      <c r="DL24" s="29"/>
-      <c r="DM24" s="29"/>
-      <c r="DN24" s="29"/>
-      <c r="DO24" s="29"/>
-      <c r="DP24" s="29"/>
-      <c r="DQ24" s="29"/>
-      <c r="DR24" s="29"/>
-      <c r="DS24" s="29"/>
-      <c r="DT24" s="29"/>
-      <c r="DU24" s="29"/>
-      <c r="DV24" s="29"/>
-      <c r="DW24" s="29"/>
-      <c r="DX24" s="29"/>
-      <c r="DY24" s="29"/>
-      <c r="DZ24" s="29"/>
-      <c r="EA24" s="29"/>
-      <c r="EB24" s="29"/>
-      <c r="EC24" s="29"/>
-      <c r="ED24" s="29"/>
-      <c r="EE24" s="29"/>
-      <c r="EF24" s="29"/>
-      <c r="EG24" s="29"/>
-      <c r="EH24" s="29"/>
-      <c r="EI24" s="29"/>
-      <c r="EJ24" s="29"/>
-      <c r="EK24" s="29"/>
-      <c r="EL24" s="29"/>
-      <c r="EM24" s="29"/>
-      <c r="EN24" s="29"/>
-      <c r="EO24" s="29"/>
-      <c r="EP24" s="29"/>
-      <c r="EQ24" s="29"/>
-      <c r="ER24" s="29"/>
-      <c r="ES24" s="29"/>
-      <c r="ET24" s="29"/>
-      <c r="EU24" s="29"/>
-      <c r="EV24" s="29"/>
-      <c r="EW24" s="29"/>
-      <c r="EX24" s="29"/>
-      <c r="EY24" s="29"/>
-      <c r="EZ24" s="29"/>
-      <c r="FA24" s="29"/>
-      <c r="FB24" s="29"/>
-      <c r="FC24" s="29"/>
-      <c r="FD24" s="29"/>
-      <c r="FE24" s="29"/>
-      <c r="FF24" s="29"/>
-      <c r="FG24" s="29"/>
-      <c r="FH24" s="29"/>
-      <c r="FI24" s="29"/>
-      <c r="FJ24" s="29"/>
-      <c r="FK24" s="29"/>
-      <c r="FL24" s="29"/>
-      <c r="FM24" s="29"/>
-      <c r="FN24" s="29"/>
-      <c r="FO24" s="29"/>
-      <c r="FP24" s="29"/>
-      <c r="FQ24" s="29"/>
-      <c r="FR24" s="29"/>
-      <c r="FS24" s="29"/>
-      <c r="FT24" s="29"/>
-      <c r="FU24" s="29"/>
-      <c r="FV24" s="29"/>
-      <c r="FW24" s="29"/>
-      <c r="FX24" s="29"/>
-      <c r="FY24" s="29"/>
-      <c r="FZ24" s="29"/>
-      <c r="GA24" s="29"/>
-      <c r="GB24" s="29"/>
-      <c r="GC24" s="29"/>
-      <c r="GD24" s="29"/>
-      <c r="GE24" s="29"/>
-      <c r="GF24" s="29"/>
-      <c r="GG24" s="29"/>
-      <c r="GH24" s="29"/>
-      <c r="GI24" s="29"/>
-      <c r="GJ24" s="29"/>
-      <c r="GK24" s="29"/>
-      <c r="GL24" s="29"/>
-      <c r="GM24" s="29"/>
-      <c r="GN24" s="29"/>
-      <c r="GO24" s="29"/>
-      <c r="GP24" s="29"/>
-      <c r="GQ24" s="29"/>
-      <c r="GR24" s="29"/>
-      <c r="GS24" s="29"/>
-      <c r="GT24" s="29"/>
-      <c r="GU24" s="29"/>
-      <c r="GV24" s="29"/>
-      <c r="GW24" s="29"/>
-      <c r="GX24" s="29"/>
-      <c r="GY24" s="29"/>
-      <c r="GZ24" s="29"/>
-      <c r="HA24" s="29"/>
-      <c r="HB24" s="29"/>
-      <c r="HC24" s="29"/>
-      <c r="HD24" s="29"/>
-      <c r="HE24" s="29"/>
-      <c r="HF24" s="29"/>
-      <c r="HG24" s="29"/>
-      <c r="HH24" s="29"/>
-      <c r="HI24" s="29"/>
-      <c r="HJ24" s="29"/>
-      <c r="HK24" s="29"/>
-      <c r="HL24" s="29"/>
-      <c r="HM24" s="29"/>
-      <c r="HN24" s="29"/>
-      <c r="HO24" s="29"/>
-      <c r="HP24" s="29"/>
-      <c r="HQ24" s="29"/>
-      <c r="HR24" s="29"/>
-      <c r="HS24" s="29"/>
-      <c r="HT24" s="29"/>
-      <c r="HU24" s="29"/>
+    <row r="24" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="27"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="25"/>
+      <c r="BQ24" s="26"/>
+      <c r="BS24" s="26"/>
+      <c r="BU24" s="26"/>
+      <c r="BW24" s="26"/>
+      <c r="BY24" s="26"/>
+      <c r="CA24" s="26"/>
+      <c r="CC24" s="26"/>
+      <c r="CE24" s="26"/>
+      <c r="CG24" s="26"/>
+      <c r="CI24" s="26"/>
+      <c r="CK24" s="26"/>
+      <c r="CL24" s="26"/>
+      <c r="CM24" s="26"/>
+      <c r="CN24" s="26"/>
+      <c r="CO24" s="26"/>
+      <c r="CP24" s="26"/>
+      <c r="CQ24" s="26"/>
+      <c r="CR24" s="26"/>
+      <c r="CS24" s="26"/>
+      <c r="CT24" s="26"/>
+      <c r="CU24" s="26"/>
+      <c r="CV24" s="26"/>
+      <c r="CW24" s="26"/>
+      <c r="CX24" s="26"/>
+      <c r="CY24" s="26"/>
+      <c r="CZ24" s="26"/>
+      <c r="DA24" s="26"/>
+      <c r="DB24" s="26"/>
+      <c r="DC24" s="26"/>
+      <c r="DD24" s="26"/>
+      <c r="DE24" s="26"/>
+      <c r="DF24" s="26"/>
+      <c r="DG24" s="26"/>
+      <c r="DH24" s="26"/>
+      <c r="DI24" s="26"/>
+      <c r="DJ24" s="26"/>
+      <c r="DK24" s="26"/>
+      <c r="DL24" s="26"/>
+      <c r="DM24" s="26"/>
+      <c r="DN24" s="26"/>
+      <c r="DO24" s="26"/>
+      <c r="DP24" s="26"/>
+      <c r="DQ24" s="26"/>
+      <c r="DR24" s="26"/>
+      <c r="DS24" s="26"/>
+      <c r="DT24" s="26"/>
+      <c r="DU24" s="26"/>
+      <c r="DV24" s="26"/>
+      <c r="DW24" s="26"/>
+      <c r="DX24" s="26"/>
+      <c r="DY24" s="26"/>
+      <c r="DZ24" s="26"/>
+      <c r="EA24" s="26"/>
+      <c r="EB24" s="26"/>
+      <c r="EC24" s="26"/>
+      <c r="ED24" s="26"/>
+      <c r="EE24" s="26"/>
+      <c r="EF24" s="26"/>
+      <c r="EG24" s="26"/>
+      <c r="EH24" s="26"/>
+      <c r="EI24" s="26"/>
+      <c r="EJ24" s="26"/>
+      <c r="EK24" s="26"/>
+      <c r="EL24" s="26"/>
+      <c r="EM24" s="26"/>
+      <c r="EN24" s="26"/>
+      <c r="EO24" s="26"/>
+      <c r="EP24" s="26"/>
+      <c r="EQ24" s="26"/>
+      <c r="ER24" s="26"/>
+      <c r="ES24" s="26"/>
+      <c r="ET24" s="26"/>
+      <c r="EU24" s="26"/>
+      <c r="EV24" s="26"/>
+      <c r="EW24" s="26"/>
+      <c r="EX24" s="26"/>
+      <c r="EY24" s="26"/>
+      <c r="EZ24" s="26"/>
+      <c r="FA24" s="26"/>
+      <c r="FB24" s="26"/>
+      <c r="FC24" s="26"/>
+      <c r="FD24" s="26"/>
+      <c r="FE24" s="26"/>
+      <c r="FF24" s="26"/>
+      <c r="FG24" s="26"/>
+      <c r="FH24" s="26"/>
+      <c r="FI24" s="26"/>
+      <c r="FJ24" s="26"/>
+      <c r="FK24" s="26"/>
+      <c r="FL24" s="26"/>
+      <c r="FM24" s="26"/>
+      <c r="FN24" s="26"/>
+      <c r="FO24" s="26"/>
+      <c r="FP24" s="26"/>
+      <c r="FQ24" s="26"/>
+      <c r="FR24" s="26"/>
+      <c r="FS24" s="26"/>
+      <c r="FT24" s="26"/>
+      <c r="FU24" s="26"/>
+      <c r="FV24" s="26"/>
+      <c r="FW24" s="26"/>
+      <c r="FX24" s="26"/>
+      <c r="FY24" s="26"/>
+      <c r="FZ24" s="26"/>
+      <c r="GA24" s="26"/>
+      <c r="GB24" s="26"/>
+      <c r="GC24" s="26"/>
+      <c r="GD24" s="26"/>
+      <c r="GE24" s="26"/>
+      <c r="GF24" s="26"/>
+      <c r="GG24" s="26"/>
+      <c r="GH24" s="26"/>
+      <c r="GI24" s="26"/>
+      <c r="GJ24" s="26"/>
+      <c r="GK24" s="26"/>
+      <c r="GL24" s="26"/>
+      <c r="GM24" s="26"/>
+      <c r="GN24" s="26"/>
+      <c r="GO24" s="26"/>
+      <c r="GP24" s="26"/>
+      <c r="GQ24" s="26"/>
+      <c r="GR24" s="26"/>
+      <c r="GS24" s="26"/>
+      <c r="GT24" s="26"/>
+      <c r="GU24" s="26"/>
+      <c r="GV24" s="26"/>
+      <c r="GW24" s="26"/>
+      <c r="GX24" s="26"/>
+      <c r="GY24" s="26"/>
+      <c r="GZ24" s="26"/>
+      <c r="HA24" s="26"/>
+      <c r="HB24" s="26"/>
+      <c r="HC24" s="26"/>
+      <c r="HD24" s="26"/>
+      <c r="HE24" s="26"/>
+      <c r="HF24" s="26"/>
+      <c r="HG24" s="26"/>
+      <c r="HH24" s="26"/>
+      <c r="HI24" s="26"/>
+      <c r="HJ24" s="26"/>
+      <c r="HK24" s="26"/>
+      <c r="HL24" s="26"/>
+      <c r="HM24" s="26"/>
+      <c r="HN24" s="26"/>
+      <c r="HO24" s="26"/>
+      <c r="HP24" s="26"/>
+      <c r="HQ24" s="26"/>
+      <c r="HR24" s="26"/>
+      <c r="HS24" s="26"/>
+      <c r="HT24" s="26"/>
+      <c r="HU24" s="26"/>
     </row>
-    <row r="25" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7">
-        <v>0</v>
-      </c>
-      <c r="H25" s="28"/>
-      <c r="BO25" s="29"/>
-      <c r="BP25" s="29"/>
-      <c r="BQ25" s="29"/>
-      <c r="BR25" s="29"/>
-      <c r="BS25" s="29"/>
-      <c r="BT25" s="29"/>
-      <c r="BU25" s="29"/>
-      <c r="BV25" s="29"/>
-      <c r="BW25" s="29"/>
-      <c r="BX25" s="29"/>
-      <c r="BY25" s="29"/>
-      <c r="BZ25" s="29"/>
-      <c r="CA25" s="29"/>
-      <c r="CB25" s="29"/>
-      <c r="CC25" s="29"/>
-      <c r="CD25" s="29"/>
-      <c r="CE25" s="29"/>
-      <c r="CF25" s="29"/>
-      <c r="CG25" s="29"/>
-      <c r="CH25" s="29"/>
-      <c r="CI25" s="29"/>
-      <c r="CJ25" s="29"/>
-      <c r="CK25" s="29"/>
-      <c r="CL25" s="29"/>
-      <c r="CM25" s="29"/>
-      <c r="CN25" s="29"/>
-      <c r="CO25" s="29"/>
-      <c r="CP25" s="29"/>
-      <c r="CQ25" s="29"/>
-      <c r="CR25" s="29"/>
-      <c r="CS25" s="29"/>
-      <c r="CT25" s="29"/>
-      <c r="CU25" s="29"/>
-      <c r="CV25" s="29"/>
-      <c r="CW25" s="29"/>
-      <c r="CX25" s="29"/>
-      <c r="CY25" s="29"/>
-      <c r="CZ25" s="29"/>
-      <c r="DA25" s="29"/>
-      <c r="DB25" s="29"/>
-      <c r="DC25" s="29"/>
-      <c r="DD25" s="29"/>
-      <c r="DE25" s="29"/>
-      <c r="DF25" s="29"/>
-      <c r="DG25" s="29"/>
-      <c r="DH25" s="29"/>
-      <c r="DI25" s="29"/>
-      <c r="DJ25" s="29"/>
-      <c r="DK25" s="29"/>
-      <c r="DL25" s="29"/>
-      <c r="DM25" s="29"/>
-      <c r="DN25" s="29"/>
-      <c r="DO25" s="29"/>
-      <c r="DP25" s="29"/>
-      <c r="DQ25" s="29"/>
-      <c r="DR25" s="29"/>
-      <c r="DS25" s="29"/>
-      <c r="DT25" s="29"/>
-      <c r="DU25" s="29"/>
-      <c r="DV25" s="29"/>
-      <c r="DW25" s="29"/>
-      <c r="DX25" s="29"/>
-      <c r="DY25" s="29"/>
-      <c r="DZ25" s="29"/>
-      <c r="EA25" s="29"/>
-      <c r="EB25" s="29"/>
-      <c r="EC25" s="29"/>
-      <c r="ED25" s="29"/>
-      <c r="EE25" s="29"/>
-      <c r="EF25" s="29"/>
-      <c r="EG25" s="29"/>
-      <c r="EH25" s="29"/>
-      <c r="EI25" s="29"/>
-      <c r="EJ25" s="29"/>
-      <c r="EK25" s="29"/>
-      <c r="EL25" s="29"/>
-      <c r="EM25" s="29"/>
-      <c r="EN25" s="29"/>
-      <c r="EO25" s="29"/>
-      <c r="EP25" s="29"/>
-      <c r="EQ25" s="29"/>
-      <c r="ER25" s="29"/>
-      <c r="ES25" s="29"/>
-      <c r="ET25" s="29"/>
-      <c r="EU25" s="29"/>
-      <c r="EV25" s="29"/>
-      <c r="EW25" s="29"/>
-      <c r="EX25" s="29"/>
-      <c r="EY25" s="29"/>
-      <c r="EZ25" s="29"/>
-      <c r="FA25" s="29"/>
-      <c r="FB25" s="29"/>
-      <c r="FC25" s="29"/>
-      <c r="FD25" s="29"/>
-      <c r="FE25" s="29"/>
-      <c r="FF25" s="29"/>
-      <c r="FG25" s="29"/>
-      <c r="FH25" s="29"/>
-      <c r="FI25" s="29"/>
-      <c r="FJ25" s="29"/>
-      <c r="FK25" s="29"/>
-      <c r="FL25" s="29"/>
-      <c r="FM25" s="29"/>
-      <c r="FN25" s="29"/>
-      <c r="FO25" s="29"/>
-      <c r="FP25" s="29"/>
-      <c r="FQ25" s="29"/>
-      <c r="FR25" s="29"/>
-      <c r="FS25" s="29"/>
-      <c r="FT25" s="29"/>
-      <c r="FU25" s="29"/>
-      <c r="FV25" s="29"/>
-      <c r="FW25" s="29"/>
-      <c r="FX25" s="29"/>
-      <c r="FY25" s="29"/>
-      <c r="FZ25" s="29"/>
-      <c r="GA25" s="29"/>
-      <c r="GB25" s="29"/>
-      <c r="GC25" s="29"/>
-      <c r="GD25" s="29"/>
-      <c r="GE25" s="29"/>
-      <c r="GF25" s="29"/>
-      <c r="GG25" s="29"/>
-      <c r="GH25" s="29"/>
-      <c r="GI25" s="29"/>
-      <c r="GJ25" s="29"/>
-      <c r="GK25" s="29"/>
-      <c r="GL25" s="29"/>
-      <c r="GM25" s="29"/>
-      <c r="GN25" s="29"/>
-      <c r="GO25" s="29"/>
-      <c r="GP25" s="29"/>
-      <c r="GQ25" s="29"/>
-      <c r="GR25" s="29"/>
-      <c r="GS25" s="29"/>
-      <c r="GT25" s="29"/>
-      <c r="GU25" s="29"/>
-      <c r="GV25" s="29"/>
-      <c r="GW25" s="29"/>
-      <c r="GX25" s="29"/>
-      <c r="GY25" s="29"/>
-      <c r="GZ25" s="29"/>
-      <c r="HA25" s="29"/>
-      <c r="HB25" s="29"/>
-      <c r="HC25" s="29"/>
-      <c r="HD25" s="29"/>
-      <c r="HE25" s="29"/>
-      <c r="HF25" s="29"/>
-      <c r="HG25" s="29"/>
-      <c r="HH25" s="29"/>
-      <c r="HI25" s="29"/>
-      <c r="HJ25" s="29"/>
-      <c r="HK25" s="29"/>
-      <c r="HL25" s="29"/>
-      <c r="HM25" s="29"/>
-      <c r="HN25" s="29"/>
-      <c r="HO25" s="29"/>
-      <c r="HP25" s="29"/>
-      <c r="HQ25" s="29"/>
-      <c r="HR25" s="29"/>
-      <c r="HS25" s="29"/>
-      <c r="HT25" s="29"/>
-      <c r="HU25" s="29"/>
+    <row r="25" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="27"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="25"/>
+      <c r="BO25" s="26"/>
+      <c r="BP25" s="26"/>
+      <c r="BQ25" s="26"/>
+      <c r="BR25" s="26"/>
+      <c r="BS25" s="26"/>
+      <c r="BT25" s="26"/>
+      <c r="BU25" s="26"/>
+      <c r="BV25" s="26"/>
+      <c r="BW25" s="26"/>
+      <c r="BX25" s="26"/>
+      <c r="BY25" s="26"/>
+      <c r="BZ25" s="26"/>
+      <c r="CA25" s="26"/>
+      <c r="CB25" s="26"/>
+      <c r="CC25" s="26"/>
+      <c r="CD25" s="26"/>
+      <c r="CE25" s="26"/>
+      <c r="CF25" s="26"/>
+      <c r="CG25" s="26"/>
+      <c r="CH25" s="26"/>
+      <c r="CI25" s="26"/>
+      <c r="CJ25" s="26"/>
+      <c r="CK25" s="26"/>
+      <c r="CL25" s="26"/>
+      <c r="CM25" s="26"/>
+      <c r="CN25" s="26"/>
+      <c r="CO25" s="26"/>
+      <c r="CP25" s="26"/>
+      <c r="CQ25" s="26"/>
+      <c r="CR25" s="26"/>
+      <c r="CS25" s="26"/>
+      <c r="CT25" s="26"/>
+      <c r="CU25" s="26"/>
+      <c r="CV25" s="26"/>
+      <c r="CW25" s="26"/>
+      <c r="CX25" s="26"/>
+      <c r="CY25" s="26"/>
+      <c r="CZ25" s="26"/>
+      <c r="DA25" s="26"/>
+      <c r="DB25" s="26"/>
+      <c r="DC25" s="26"/>
+      <c r="DD25" s="26"/>
+      <c r="DE25" s="26"/>
+      <c r="DF25" s="26"/>
+      <c r="DG25" s="26"/>
+      <c r="DH25" s="26"/>
+      <c r="DI25" s="26"/>
+      <c r="DJ25" s="26"/>
+      <c r="DK25" s="26"/>
+      <c r="DL25" s="26"/>
+      <c r="DM25" s="26"/>
+      <c r="DN25" s="26"/>
+      <c r="DO25" s="26"/>
+      <c r="DP25" s="26"/>
+      <c r="DQ25" s="26"/>
+      <c r="DR25" s="26"/>
+      <c r="DS25" s="26"/>
+      <c r="DT25" s="26"/>
+      <c r="DU25" s="26"/>
+      <c r="DV25" s="26"/>
+      <c r="DW25" s="26"/>
+      <c r="DX25" s="26"/>
+      <c r="DY25" s="26"/>
+      <c r="DZ25" s="26"/>
+      <c r="EA25" s="26"/>
+      <c r="EB25" s="26"/>
+      <c r="EC25" s="26"/>
+      <c r="ED25" s="26"/>
+      <c r="EE25" s="26"/>
+      <c r="EF25" s="26"/>
+      <c r="EG25" s="26"/>
+      <c r="EH25" s="26"/>
+      <c r="EI25" s="26"/>
+      <c r="EJ25" s="26"/>
+      <c r="EK25" s="26"/>
+      <c r="EL25" s="26"/>
+      <c r="EM25" s="26"/>
+      <c r="EN25" s="26"/>
+      <c r="EO25" s="26"/>
+      <c r="EP25" s="26"/>
+      <c r="EQ25" s="26"/>
+      <c r="ER25" s="26"/>
+      <c r="ES25" s="26"/>
+      <c r="ET25" s="26"/>
+      <c r="EU25" s="26"/>
+      <c r="EV25" s="26"/>
+      <c r="EW25" s="26"/>
+      <c r="EX25" s="26"/>
+      <c r="EY25" s="26"/>
+      <c r="EZ25" s="26"/>
+      <c r="FA25" s="26"/>
+      <c r="FB25" s="26"/>
+      <c r="FC25" s="26"/>
+      <c r="FD25" s="26"/>
+      <c r="FE25" s="26"/>
+      <c r="FF25" s="26"/>
+      <c r="FG25" s="26"/>
+      <c r="FH25" s="26"/>
+      <c r="FI25" s="26"/>
+      <c r="FJ25" s="26"/>
+      <c r="FK25" s="26"/>
+      <c r="FL25" s="26"/>
+      <c r="FM25" s="26"/>
+      <c r="FN25" s="26"/>
+      <c r="FO25" s="26"/>
+      <c r="FP25" s="26"/>
+      <c r="FQ25" s="26"/>
+      <c r="FR25" s="26"/>
+      <c r="FS25" s="26"/>
+      <c r="FT25" s="26"/>
+      <c r="FU25" s="26"/>
+      <c r="FV25" s="26"/>
+      <c r="FW25" s="26"/>
+      <c r="FX25" s="26"/>
+      <c r="FY25" s="26"/>
+      <c r="FZ25" s="26"/>
+      <c r="GA25" s="26"/>
+      <c r="GB25" s="26"/>
+      <c r="GC25" s="26"/>
+      <c r="GD25" s="26"/>
+      <c r="GE25" s="26"/>
+      <c r="GF25" s="26"/>
+      <c r="GG25" s="26"/>
+      <c r="GH25" s="26"/>
+      <c r="GI25" s="26"/>
+      <c r="GJ25" s="26"/>
+      <c r="GK25" s="26"/>
+      <c r="GL25" s="26"/>
+      <c r="GM25" s="26"/>
+      <c r="GN25" s="26"/>
+      <c r="GO25" s="26"/>
+      <c r="GP25" s="26"/>
+      <c r="GQ25" s="26"/>
+      <c r="GR25" s="26"/>
+      <c r="GS25" s="26"/>
+      <c r="GT25" s="26"/>
+      <c r="GU25" s="26"/>
+      <c r="GV25" s="26"/>
+      <c r="GW25" s="26"/>
+      <c r="GX25" s="26"/>
+      <c r="GY25" s="26"/>
+      <c r="GZ25" s="26"/>
+      <c r="HA25" s="26"/>
+      <c r="HB25" s="26"/>
+      <c r="HC25" s="26"/>
+      <c r="HD25" s="26"/>
+      <c r="HE25" s="26"/>
+      <c r="HF25" s="26"/>
+      <c r="HG25" s="26"/>
+      <c r="HH25" s="26"/>
+      <c r="HI25" s="26"/>
+      <c r="HJ25" s="26"/>
+      <c r="HK25" s="26"/>
+      <c r="HL25" s="26"/>
+      <c r="HM25" s="26"/>
+      <c r="HN25" s="26"/>
+      <c r="HO25" s="26"/>
+      <c r="HP25" s="26"/>
+      <c r="HQ25" s="26"/>
+      <c r="HR25" s="26"/>
+      <c r="HS25" s="26"/>
+      <c r="HT25" s="26"/>
+      <c r="HU25" s="26"/>
     </row>
-    <row r="26" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0</v>
-      </c>
-      <c r="H26" s="28"/>
+    <row r="26" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="27"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="25"/>
     </row>
-    <row r="27" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0</v>
-      </c>
-      <c r="H27" s="28"/>
-      <c r="BP27" s="29"/>
-      <c r="BQ27" s="29"/>
-      <c r="BR27" s="29"/>
-      <c r="BS27" s="29"/>
-      <c r="BT27" s="29"/>
-      <c r="BU27" s="29"/>
-      <c r="BV27" s="29"/>
-      <c r="BW27" s="29"/>
-      <c r="BX27" s="29"/>
-      <c r="BY27" s="29"/>
-      <c r="BZ27" s="29"/>
-      <c r="CA27" s="29"/>
-      <c r="CB27" s="29"/>
-      <c r="CC27" s="29"/>
-      <c r="CD27" s="29"/>
-      <c r="CE27" s="29"/>
-      <c r="CF27" s="29"/>
-      <c r="CG27" s="29"/>
-      <c r="CH27" s="29"/>
-      <c r="CI27" s="29"/>
-      <c r="CJ27" s="29"/>
-      <c r="CK27" s="29"/>
-      <c r="CL27" s="29"/>
-      <c r="CM27" s="29"/>
-      <c r="CN27" s="29"/>
-      <c r="CO27" s="29"/>
-      <c r="CP27" s="29"/>
-      <c r="CQ27" s="29"/>
-      <c r="CR27" s="29"/>
-      <c r="CS27" s="29"/>
-      <c r="CT27" s="29"/>
-      <c r="CU27" s="29"/>
-      <c r="CV27" s="29"/>
-      <c r="CW27" s="29"/>
-      <c r="CX27" s="29"/>
-      <c r="CY27" s="29"/>
-      <c r="CZ27" s="29"/>
-      <c r="DA27" s="29"/>
-      <c r="DB27" s="29"/>
-      <c r="DC27" s="29"/>
-      <c r="DD27" s="29"/>
-      <c r="DE27" s="29"/>
-      <c r="DF27" s="29"/>
-      <c r="DG27" s="29"/>
-      <c r="DH27" s="29"/>
-      <c r="DI27" s="29"/>
-      <c r="DJ27" s="29"/>
-      <c r="DK27" s="29"/>
-      <c r="DL27" s="29"/>
-      <c r="DM27" s="29"/>
-      <c r="DN27" s="29"/>
-      <c r="DO27" s="29"/>
-      <c r="DP27" s="29"/>
-      <c r="DQ27" s="29"/>
-      <c r="DR27" s="29"/>
-      <c r="DS27" s="29"/>
-      <c r="DT27" s="29"/>
-      <c r="DU27" s="29"/>
-      <c r="DV27" s="29"/>
-      <c r="DW27" s="29"/>
-      <c r="DX27" s="29"/>
-      <c r="DY27" s="29"/>
-      <c r="DZ27" s="29"/>
-      <c r="EA27" s="29"/>
-      <c r="EB27" s="29"/>
-      <c r="EC27" s="29"/>
-      <c r="ED27" s="29"/>
-      <c r="EE27" s="29"/>
-      <c r="EF27" s="29"/>
-      <c r="EG27" s="29"/>
-      <c r="EH27" s="29"/>
-      <c r="EI27" s="29"/>
-      <c r="EJ27" s="29"/>
-      <c r="EK27" s="29"/>
-      <c r="EL27" s="29"/>
-      <c r="EM27" s="29"/>
-      <c r="EN27" s="29"/>
-      <c r="EO27" s="29"/>
-      <c r="EP27" s="29"/>
-      <c r="EQ27" s="29"/>
-      <c r="ER27" s="29"/>
-      <c r="ES27" s="29"/>
-      <c r="ET27" s="29"/>
-      <c r="EU27" s="29"/>
-      <c r="EV27" s="29"/>
-      <c r="EW27" s="29"/>
-      <c r="EX27" s="29"/>
-      <c r="EY27" s="29"/>
-      <c r="EZ27" s="29"/>
-      <c r="FA27" s="29"/>
-      <c r="FB27" s="29"/>
-      <c r="FC27" s="29"/>
-      <c r="FD27" s="29"/>
-      <c r="FE27" s="29"/>
-      <c r="FF27" s="29"/>
-      <c r="FG27" s="29"/>
-      <c r="FH27" s="29"/>
-      <c r="FI27" s="29"/>
-      <c r="FJ27" s="29"/>
-      <c r="FK27" s="29"/>
-      <c r="FL27" s="29"/>
-      <c r="FM27" s="29"/>
-      <c r="FN27" s="29"/>
-      <c r="FO27" s="29"/>
-      <c r="FP27" s="29"/>
-      <c r="FQ27" s="29"/>
-      <c r="FR27" s="29"/>
-      <c r="FS27" s="29"/>
-      <c r="FT27" s="29"/>
-      <c r="FU27" s="29"/>
-      <c r="FV27" s="29"/>
-      <c r="FW27" s="29"/>
-      <c r="FX27" s="29"/>
-      <c r="FY27" s="29"/>
-      <c r="FZ27" s="29"/>
-      <c r="GA27" s="29"/>
-      <c r="GB27" s="29"/>
-      <c r="GC27" s="29"/>
-      <c r="GD27" s="29"/>
-      <c r="GE27" s="29"/>
-      <c r="GF27" s="29"/>
-      <c r="GG27" s="29"/>
-      <c r="GH27" s="29"/>
-      <c r="GI27" s="29"/>
-      <c r="GJ27" s="29"/>
-      <c r="GK27" s="29"/>
-      <c r="GL27" s="29"/>
-      <c r="GM27" s="29"/>
-      <c r="GN27" s="29"/>
-      <c r="GO27" s="29"/>
-      <c r="GP27" s="29"/>
-      <c r="GQ27" s="29"/>
-      <c r="GR27" s="29"/>
-      <c r="GS27" s="29"/>
-      <c r="GT27" s="29"/>
-      <c r="GU27" s="29"/>
-      <c r="GV27" s="29"/>
-      <c r="GW27" s="29"/>
-      <c r="GX27" s="29"/>
-      <c r="GY27" s="29"/>
-      <c r="GZ27" s="29"/>
-      <c r="HA27" s="29"/>
-      <c r="HB27" s="29"/>
-      <c r="HC27" s="29"/>
-      <c r="HD27" s="29"/>
-      <c r="HE27" s="29"/>
-      <c r="HF27" s="29"/>
-      <c r="HG27" s="29"/>
-      <c r="HH27" s="29"/>
-      <c r="HI27" s="29"/>
-      <c r="HJ27" s="29"/>
-      <c r="HK27" s="29"/>
-      <c r="HL27" s="29"/>
-      <c r="HM27" s="29"/>
-      <c r="HN27" s="29"/>
-      <c r="HO27" s="29"/>
-      <c r="HP27" s="29"/>
-      <c r="HQ27" s="29"/>
-      <c r="HR27" s="29"/>
-      <c r="HS27" s="29"/>
-      <c r="HT27" s="29"/>
-      <c r="HU27" s="29"/>
+    <row r="27" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="27"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="25"/>
+      <c r="BP27" s="26"/>
+      <c r="BQ27" s="26"/>
+      <c r="BR27" s="26"/>
+      <c r="BS27" s="26"/>
+      <c r="BT27" s="26"/>
+      <c r="BU27" s="26"/>
+      <c r="BV27" s="26"/>
+      <c r="BW27" s="26"/>
+      <c r="BX27" s="26"/>
+      <c r="BY27" s="26"/>
+      <c r="BZ27" s="26"/>
+      <c r="CA27" s="26"/>
+      <c r="CB27" s="26"/>
+      <c r="CC27" s="26"/>
+      <c r="CD27" s="26"/>
+      <c r="CE27" s="26"/>
+      <c r="CF27" s="26"/>
+      <c r="CG27" s="26"/>
+      <c r="CH27" s="26"/>
+      <c r="CI27" s="26"/>
+      <c r="CJ27" s="26"/>
+      <c r="CK27" s="26"/>
+      <c r="CL27" s="26"/>
+      <c r="CM27" s="26"/>
+      <c r="CN27" s="26"/>
+      <c r="CO27" s="26"/>
+      <c r="CP27" s="26"/>
+      <c r="CQ27" s="26"/>
+      <c r="CR27" s="26"/>
+      <c r="CS27" s="26"/>
+      <c r="CT27" s="26"/>
+      <c r="CU27" s="26"/>
+      <c r="CV27" s="26"/>
+      <c r="CW27" s="26"/>
+      <c r="CX27" s="26"/>
+      <c r="CY27" s="26"/>
+      <c r="CZ27" s="26"/>
+      <c r="DA27" s="26"/>
+      <c r="DB27" s="26"/>
+      <c r="DC27" s="26"/>
+      <c r="DD27" s="26"/>
+      <c r="DE27" s="26"/>
+      <c r="DF27" s="26"/>
+      <c r="DG27" s="26"/>
+      <c r="DH27" s="26"/>
+      <c r="DI27" s="26"/>
+      <c r="DJ27" s="26"/>
+      <c r="DK27" s="26"/>
+      <c r="DL27" s="26"/>
+      <c r="DM27" s="26"/>
+      <c r="DN27" s="26"/>
+      <c r="DO27" s="26"/>
+      <c r="DP27" s="26"/>
+      <c r="DQ27" s="26"/>
+      <c r="DR27" s="26"/>
+      <c r="DS27" s="26"/>
+      <c r="DT27" s="26"/>
+      <c r="DU27" s="26"/>
+      <c r="DV27" s="26"/>
+      <c r="DW27" s="26"/>
+      <c r="DX27" s="26"/>
+      <c r="DY27" s="26"/>
+      <c r="DZ27" s="26"/>
+      <c r="EA27" s="26"/>
+      <c r="EB27" s="26"/>
+      <c r="EC27" s="26"/>
+      <c r="ED27" s="26"/>
+      <c r="EE27" s="26"/>
+      <c r="EF27" s="26"/>
+      <c r="EG27" s="26"/>
+      <c r="EH27" s="26"/>
+      <c r="EI27" s="26"/>
+      <c r="EJ27" s="26"/>
+      <c r="EK27" s="26"/>
+      <c r="EL27" s="26"/>
+      <c r="EM27" s="26"/>
+      <c r="EN27" s="26"/>
+      <c r="EO27" s="26"/>
+      <c r="EP27" s="26"/>
+      <c r="EQ27" s="26"/>
+      <c r="ER27" s="26"/>
+      <c r="ES27" s="26"/>
+      <c r="ET27" s="26"/>
+      <c r="EU27" s="26"/>
+      <c r="EV27" s="26"/>
+      <c r="EW27" s="26"/>
+      <c r="EX27" s="26"/>
+      <c r="EY27" s="26"/>
+      <c r="EZ27" s="26"/>
+      <c r="FA27" s="26"/>
+      <c r="FB27" s="26"/>
+      <c r="FC27" s="26"/>
+      <c r="FD27" s="26"/>
+      <c r="FE27" s="26"/>
+      <c r="FF27" s="26"/>
+      <c r="FG27" s="26"/>
+      <c r="FH27" s="26"/>
+      <c r="FI27" s="26"/>
+      <c r="FJ27" s="26"/>
+      <c r="FK27" s="26"/>
+      <c r="FL27" s="26"/>
+      <c r="FM27" s="26"/>
+      <c r="FN27" s="26"/>
+      <c r="FO27" s="26"/>
+      <c r="FP27" s="26"/>
+      <c r="FQ27" s="26"/>
+      <c r="FR27" s="26"/>
+      <c r="FS27" s="26"/>
+      <c r="FT27" s="26"/>
+      <c r="FU27" s="26"/>
+      <c r="FV27" s="26"/>
+      <c r="FW27" s="26"/>
+      <c r="FX27" s="26"/>
+      <c r="FY27" s="26"/>
+      <c r="FZ27" s="26"/>
+      <c r="GA27" s="26"/>
+      <c r="GB27" s="26"/>
+      <c r="GC27" s="26"/>
+      <c r="GD27" s="26"/>
+      <c r="GE27" s="26"/>
+      <c r="GF27" s="26"/>
+      <c r="GG27" s="26"/>
+      <c r="GH27" s="26"/>
+      <c r="GI27" s="26"/>
+      <c r="GJ27" s="26"/>
+      <c r="GK27" s="26"/>
+      <c r="GL27" s="26"/>
+      <c r="GM27" s="26"/>
+      <c r="GN27" s="26"/>
+      <c r="GO27" s="26"/>
+      <c r="GP27" s="26"/>
+      <c r="GQ27" s="26"/>
+      <c r="GR27" s="26"/>
+      <c r="GS27" s="26"/>
+      <c r="GT27" s="26"/>
+      <c r="GU27" s="26"/>
+      <c r="GV27" s="26"/>
+      <c r="GW27" s="26"/>
+      <c r="GX27" s="26"/>
+      <c r="GY27" s="26"/>
+      <c r="GZ27" s="26"/>
+      <c r="HA27" s="26"/>
+      <c r="HB27" s="26"/>
+      <c r="HC27" s="26"/>
+      <c r="HD27" s="26"/>
+      <c r="HE27" s="26"/>
+      <c r="HF27" s="26"/>
+      <c r="HG27" s="26"/>
+      <c r="HH27" s="26"/>
+      <c r="HI27" s="26"/>
+      <c r="HJ27" s="26"/>
+      <c r="HK27" s="26"/>
+      <c r="HL27" s="26"/>
+      <c r="HM27" s="26"/>
+      <c r="HN27" s="26"/>
+      <c r="HO27" s="26"/>
+      <c r="HP27" s="26"/>
+      <c r="HQ27" s="26"/>
+      <c r="HR27" s="26"/>
+      <c r="HS27" s="26"/>
+      <c r="HT27" s="26"/>
+      <c r="HU27" s="26"/>
     </row>
-    <row r="28" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7">
-        <v>0</v>
-      </c>
-      <c r="H28" s="28"/>
+    <row r="28" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="27"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="25"/>
     </row>
-    <row r="29" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7">
-        <v>0</v>
-      </c>
-      <c r="H29" s="28"/>
+    <row r="29" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="27"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="25"/>
     </row>
-    <row r="30" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7">
-        <v>0</v>
-      </c>
-      <c r="H30" s="28"/>
+    <row r="30" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="27"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="25"/>
       <c r="J30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
@@ -7944,7 +7751,7 @@
       <c r="HT30" s="1"/>
       <c r="HU30" s="1"/>
     </row>
-    <row r="31" spans="2:229" ht="30.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:229" ht="30.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -8198,205 +8005,205 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:HU14 I15:BO24">
-    <cfRule type="expression" dxfId="103" priority="127">
+    <cfRule type="expression" dxfId="103" priority="121">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="123">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="124">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="100" priority="125">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="99" priority="126">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="127">
       <formula>I$4=időszak_kiválasztva</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="126">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="125">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="100" priority="124">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="99" priority="123">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="121">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="97" priority="132">
+    <cfRule type="expression" dxfId="97" priority="131">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="132">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="131">
-      <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25:HU30">
-    <cfRule type="expression" dxfId="95" priority="120">
-      <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="94" priority="119">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="93" priority="118">
-      <formula>I$4=időszak_kiválasztva</formula>
+    <cfRule type="expression" dxfId="95" priority="113">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="94" priority="114">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="115">
+      <formula>Tényleges</formula>
     </cfRule>
     <cfRule type="expression" dxfId="92" priority="116">
       <formula>TénylegTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="115">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="90" priority="117">
+    <cfRule type="expression" dxfId="91" priority="117">
       <formula>Terv</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="114">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="113">
-      <formula>KészültségiSzint</formula>
+    <cfRule type="expression" dxfId="90" priority="118">
+      <formula>I$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="89" priority="119">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="120">
+      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ15:BQ24">
-    <cfRule type="expression" dxfId="87" priority="88">
+    <cfRule type="expression" dxfId="87" priority="81">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="82">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="83">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="84">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="85">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="86">
+      <formula>BQ$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="87">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="88">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="87">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="86">
-      <formula>BQ$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="85">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="84">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="83">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="82">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="81">
-      <formula>KészültségiSzint</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BS15:BS24">
-    <cfRule type="expression" dxfId="79" priority="78">
+    <cfRule type="expression" dxfId="79" priority="73">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="74">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="75">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="76">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="77">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="78">
       <formula>BS$4=időszak_kiválasztva</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="77">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="76">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="76" priority="75">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="75" priority="74">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="73">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="80">
+    <cfRule type="expression" dxfId="73" priority="79">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="80">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="79">
-      <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU15:BU24">
-    <cfRule type="expression" dxfId="71" priority="70">
+    <cfRule type="expression" dxfId="71" priority="65">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="66">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="67">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="68">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="69">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="70">
       <formula>BU$4=időszak_kiválasztva</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="69">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="68">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="72">
+    <cfRule type="expression" dxfId="65" priority="71">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="72">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="65">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="67">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="66">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="71">
-      <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BW15:BW24">
-    <cfRule type="expression" dxfId="63" priority="64">
-      <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="63">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="62">
-      <formula>BW$4=időszak_kiválasztva</formula>
+    <cfRule type="expression" dxfId="63" priority="57">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="58">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="59">
+      <formula>Tényleges</formula>
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="60">
       <formula>TénylegTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="59">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="58">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="57">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="61">
+    <cfRule type="expression" dxfId="59" priority="61">
       <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="62">
+      <formula>BW$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="63">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="64">
+      <formula>MOD(COLUMN(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BY15:BY24">
-    <cfRule type="expression" dxfId="55" priority="51">
+    <cfRule type="expression" dxfId="55" priority="49">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="50">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="51">
       <formula>Tényleges</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="52">
+    <cfRule type="expression" dxfId="52" priority="52">
       <formula>TénylegTervenFelül</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="53">
+    <cfRule type="expression" dxfId="51" priority="53">
       <formula>Terv</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="54">
+    <cfRule type="expression" dxfId="50" priority="54">
       <formula>BY$4=időszak_kiválasztva</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="55">
+    <cfRule type="expression" dxfId="49" priority="55">
       <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="56">
+    <cfRule type="expression" dxfId="48" priority="56">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="49">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="50">
-      <formula>KészültségiSzintTervenFelül</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CA15:CA24">
-    <cfRule type="expression" dxfId="47" priority="46">
+    <cfRule type="expression" dxfId="47" priority="41">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="42">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="43">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="44">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="45">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="46">
       <formula>CA$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="45">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="44">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="43">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="42">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="41">
-      <formula>KészültségiSzint</formula>
     </cfRule>
     <cfRule type="expression" dxfId="41" priority="47">
       <formula>MOD(COLUMN(),2)</formula>
@@ -8406,133 +8213,133 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CC15:CC24">
-    <cfRule type="expression" dxfId="39" priority="40">
+    <cfRule type="expression" dxfId="39" priority="33">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="34">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="35">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="36">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="37">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="38">
+      <formula>CC$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="39">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="40">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="39">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="38">
-      <formula>CC$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="37">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="36">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="35">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="34">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="33">
-      <formula>KészültségiSzint</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CE15:CE24">
-    <cfRule type="expression" dxfId="31" priority="32">
+    <cfRule type="expression" dxfId="31" priority="25">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="26">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="27">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="28">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="29">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="30">
+      <formula>CE$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="31">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="32">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="31">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="30">
-      <formula>CE$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="29">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="28">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="25">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="27">
-      <formula>Tényleges</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG15:CG24">
-    <cfRule type="expression" dxfId="23" priority="22">
+    <cfRule type="expression" dxfId="23" priority="17">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="18">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="19">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="20">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="21">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="22">
       <formula>CG$4=időszak_kiválasztva</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="21">
-      <formula>Terv</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="20">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="19">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="18">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="17">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="24">
+    <cfRule type="expression" dxfId="17" priority="23">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="24">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="23">
-      <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CI15:CI24">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="15" priority="9">
+      <formula>KészültségiSzint</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="10">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>Terv</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="12">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>CI$4=időszak_kiválasztva</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>KészültségiSzint</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="16">
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="16">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="15">
-      <formula>MOD(COLUMN(),2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CK15:HU24">
     <cfRule type="expression" dxfId="7" priority="1">
       <formula>KészültségiSzint</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>KészültségiSzintTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>Tényleges</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>TénylegTervenFelül</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="5">
+      <formula>Terv</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>CK$4=időszak_kiválasztva</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>MOD(COLUMN(),2)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>MOD(COLUMN(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="7">
-      <formula>MOD(COLUMN(),2)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>CK$4=időszak_kiválasztva</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>TénylegTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>Tényleges</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>KészültségiSzintTervenFelül</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>Terv</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations xWindow="1722" yWindow="207" count="16">
